--- a/data/macro/USA/ADP Nonfarm Employment changes.xlsx
+++ b/data/macro/USA/ADP Nonfarm Employment changes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D29A149-6948-44C1-B5CA-7ABA74A90491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CA3B61-BAD4-4528-8B77-C17644CE5822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ADPCHNG" sheetId="1" r:id="rId1"/>
@@ -83,8 +83,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="181" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="184" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -182,7 +182,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -191,16 +191,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="184" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="184" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1162,6 +1162,9 @@
                 <c:pt idx="296">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="297">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2061,6 +2064,9 @@
                 </c:pt>
                 <c:pt idx="296">
                   <c:v>62000</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>109000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3140,7 +3146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G298"/>
+  <dimension ref="A1:G299"/>
   <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="7" bestFit="1" customWidth="1"/>
@@ -9182,7 +9188,7 @@
         <v>0.34375</v>
       </c>
       <c r="D259" s="9" t="str">
-        <f t="shared" ref="D259:D298" si="4">IF(
+        <f t="shared" ref="D259:D299" si="4">IF(
  AND(
   B259 &gt;= IF(
          YEAR(B259)&gt;=2007,
@@ -10144,6 +10150,30 @@
       </c>
       <c r="G298" s="3">
         <v>66000</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A299" s="12">
+        <v>46113</v>
+      </c>
+      <c r="B299" s="8">
+        <v>46148</v>
+      </c>
+      <c r="C299" s="11">
+        <v>0.34375</v>
+      </c>
+      <c r="D299" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E299" s="3">
+        <v>109000</v>
+      </c>
+      <c r="F299" s="3">
+        <v>118000</v>
+      </c>
+      <c r="G299" s="3">
+        <v>61000</v>
       </c>
     </row>
   </sheetData>

--- a/data/macro/USA/ADP Nonfarm Employment changes.xlsx
+++ b/data/macro/USA/ADP Nonfarm Employment changes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CA3B61-BAD4-4528-8B77-C17644CE5822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEC348C-E8E8-44E2-9B9D-33F61082D0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ADPCHNG" sheetId="1" r:id="rId1"/>
@@ -82,28 +82,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -131,7 +131,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -169,7 +169,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -178,29 +178,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -210,9 +210,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -230,7 +230,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1172,7 +1172,7 @@
             <c:numRef>
               <c:f>ADPCHNG!$E$2:$E$1298</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="1297"/>
                 <c:pt idx="0">
                   <c:v>-175000</c:v>
@@ -2167,7 +2167,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3147,17 +3147,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G299"/>
-  <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.8984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="15.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.796875" style="2"/>
+    <col min="2" max="2" width="13.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="15.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.81640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="4" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="12">
         <v>37012</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>-175000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="12">
         <v>37043</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>-175000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="12">
         <v>37073</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>-230000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="12">
         <v>37104</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>-203000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="12">
         <v>37135</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>-246000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="12">
         <v>37165</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>-261000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="12">
         <v>37196</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>-380000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="12">
         <v>37226</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>-361000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="12">
         <v>37257</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>-223000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="12">
         <v>37288</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>-69000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="12">
         <v>37316</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>-91000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="12">
         <v>37347</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>-70000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="12">
         <v>37377</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>-70000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="12">
         <v>37408</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>-47000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="12">
         <v>37438</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>-91000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="12">
         <v>37469</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>-95000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="12">
         <v>37500</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>-22000</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="12">
         <v>37530</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>-84000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="12">
         <v>37561</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>-42000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="12">
         <v>37591</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>-18000</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="12">
         <v>37622</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>-35000</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="12">
         <v>37653</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="12">
         <v>37681</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>-68000</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="12">
         <v>37712</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>-91000</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="12">
         <v>37742</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>-86000</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="12">
         <v>37773</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="12">
         <v>37803</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="12">
         <v>37834</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="12">
         <v>37865</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="12">
         <v>37895</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>132000</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="12">
         <v>37926</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>146000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="12">
         <v>37956</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="12">
         <v>37987</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="12">
         <v>38018</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>111000</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="12">
         <v>38047</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="12">
         <v>38078</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>205000</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="12">
         <v>38108</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>224000</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="12">
         <v>38139</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7">
       <c r="A40" s="12">
         <v>38169</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>133000</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7">
       <c r="A41" s="12">
         <v>38200</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>116000</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7">
       <c r="A42" s="12">
         <v>38231</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>126000</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7">
       <c r="A43" s="12">
         <v>38261</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>119000</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7">
       <c r="A44" s="12">
         <v>38292</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>203000</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7">
       <c r="A45" s="12">
         <v>38322</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7">
       <c r="A46" s="12">
         <v>38353</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>197000</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7">
       <c r="A47" s="12">
         <v>38384</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>155000</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7">
       <c r="A48" s="12">
         <v>38412</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>174000</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7">
       <c r="A49" s="12">
         <v>38443</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>169000</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7">
       <c r="A50" s="12">
         <v>38473</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>218000</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7">
       <c r="A51" s="12">
         <v>38504</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>238000</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7">
       <c r="A52" s="12">
         <v>38534</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>253000</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7">
       <c r="A53" s="12">
         <v>38565</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>204000</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7">
       <c r="A54" s="12">
         <v>38596</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>175000</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7">
       <c r="A55" s="12">
         <v>38626</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7">
       <c r="A56" s="12">
         <v>38657</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>154000</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7">
       <c r="A57" s="12">
         <v>38687</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>343000</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7">
       <c r="A58" s="12">
         <v>38718</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7">
       <c r="A59" s="12">
         <v>38749</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>329000</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7">
       <c r="A60" s="12">
         <v>38777</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>307000</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7">
       <c r="A61" s="12">
         <v>38808</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>217000</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7">
       <c r="A62" s="12">
         <v>38838</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>148000</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7">
       <c r="A63" s="12">
         <v>38869</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>143000</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7">
       <c r="A64" s="12">
         <v>38899</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7">
       <c r="A65" s="12">
         <v>38930</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>106000</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7">
       <c r="A66" s="12">
         <v>38961</v>
       </c>
@@ -4572,7 +4572,7 @@
         <v>98000</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7">
       <c r="A67" s="12">
         <v>38991</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7">
       <c r="A68" s="12">
         <v>39022</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7">
       <c r="A69" s="12">
         <v>39052</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>193000</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7">
       <c r="A70" s="12">
         <v>39083</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7">
       <c r="A71" s="12">
         <v>39114</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>199000</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7">
       <c r="A72" s="12">
         <v>39142</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7">
       <c r="A73" s="12">
         <v>39173</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7">
       <c r="A74" s="12">
         <v>39203</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>137000</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7">
       <c r="A75" s="12">
         <v>39234</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>59000</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7">
       <c r="A76" s="12">
         <v>39264</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>97000</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7">
       <c r="A77" s="12">
         <v>39295</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>-18000</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7">
       <c r="A78" s="12">
         <v>39326</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>31000</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7">
       <c r="A79" s="12">
         <v>39356</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>-3000</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7">
       <c r="A80" s="12">
         <v>39387</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>-8000</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7">
       <c r="A81" s="12">
         <v>39417</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7">
       <c r="A82" s="12">
         <v>39448</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7">
       <c r="A83" s="12">
         <v>39479</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>126000</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7">
       <c r="A84" s="12">
         <v>39508</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>-23000</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7">
       <c r="A85" s="12">
         <v>39539</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7">
       <c r="A86" s="12">
         <v>39569</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7">
       <c r="A87" s="12">
         <v>39600</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7">
       <c r="A88" s="12">
         <v>39630</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>-79000</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7">
       <c r="A89" s="12">
         <v>39661</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7">
       <c r="A90" s="12">
         <v>39692</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>-33000</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7">
       <c r="A91" s="12">
         <v>39722</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>-8000</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7">
       <c r="A92" s="12">
         <v>39753</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>-157000</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7">
       <c r="A93" s="12">
         <v>39783</v>
       </c>
@@ -5187,7 +5187,7 @@
         <v>-476000</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7">
       <c r="A94" s="12">
         <v>39814</v>
       </c>
@@ -5211,7 +5211,7 @@
         <v>-693000</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7">
       <c r="A95" s="12">
         <v>39845</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>-614000</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7">
       <c r="A96" s="12">
         <v>39873</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>-706000</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7">
       <c r="A97" s="12">
         <v>39904</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>-708000</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7">
       <c r="A98" s="12">
         <v>39934</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>-545000</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7">
       <c r="A99" s="12">
         <v>39965</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>-485000</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7">
       <c r="A100" s="12">
         <v>39995</v>
       </c>
@@ -5355,7 +5355,7 @@
         <v>-463000</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7">
       <c r="A101" s="12">
         <v>40026</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>-360000</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7">
       <c r="A102" s="12">
         <v>40057</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>-277000</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7">
       <c r="A103" s="12">
         <v>40087</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>-227000</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7">
       <c r="A104" s="12">
         <v>40118</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>-195000</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7">
       <c r="A105" s="12">
         <v>40148</v>
       </c>
@@ -5475,7 +5475,7 @@
         <v>-145000</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7">
       <c r="A106" s="12">
         <v>40179</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>-61000</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7">
       <c r="A107" s="12">
         <v>40210</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>-60000</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7">
       <c r="A108" s="12">
         <v>40238</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>-24000</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7">
       <c r="A109" s="12">
         <v>40269</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7">
       <c r="A110" s="12">
         <v>40299</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7">
       <c r="A111" s="12">
         <v>40330</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>57000</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7">
       <c r="A112" s="12">
         <v>40360</v>
       </c>
@@ -5643,7 +5643,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7">
       <c r="A113" s="12">
         <v>40391</v>
       </c>
@@ -5667,7 +5667,7 @@
         <v>37000</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7">
       <c r="A114" s="12">
         <v>40422</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7">
       <c r="A115" s="12">
         <v>40452</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7">
       <c r="A116" s="12">
         <v>40483</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>82000</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7">
       <c r="A117" s="12">
         <v>40513</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>92000</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7">
       <c r="A118" s="12">
         <v>40544</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>247000</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7">
       <c r="A119" s="12">
         <v>40575</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>189000</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7">
       <c r="A120" s="12">
         <v>40603</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>208000</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7">
       <c r="A121" s="12">
         <v>40634</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>207000</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7">
       <c r="A122" s="12">
         <v>40664</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>177000</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7">
       <c r="A123" s="12">
         <v>40695</v>
       </c>
@@ -5907,7 +5907,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7">
       <c r="A124" s="12">
         <v>40725</v>
       </c>
@@ -5931,7 +5931,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7">
       <c r="A125" s="12">
         <v>40756</v>
       </c>
@@ -5955,7 +5955,7 @@
         <v>109000</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7">
       <c r="A126" s="12">
         <v>40787</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>89000</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7">
       <c r="A127" s="12">
         <v>40817</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>116000</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7">
       <c r="A128" s="12">
         <v>40848</v>
       </c>
@@ -6027,7 +6027,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7">
       <c r="A129" s="12">
         <v>40878</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>204000</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7">
       <c r="A130" s="12">
         <v>40909</v>
       </c>
@@ -6075,7 +6075,7 @@
         <v>292000</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7">
       <c r="A131" s="12">
         <v>40940</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>173000</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7">
       <c r="A132" s="12">
         <v>40969</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7">
       <c r="A133" s="12">
         <v>41000</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>201000</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7">
       <c r="A134" s="12">
         <v>41030</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>113000</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7">
       <c r="A135" s="12">
         <v>41061</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>136000</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7">
       <c r="A136" s="12">
         <v>41091</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>172000</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7">
       <c r="A137" s="12">
         <v>41122</v>
       </c>
@@ -6258,7 +6258,7 @@
         <v>173000</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7">
       <c r="A138" s="12">
         <v>41153</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>189000</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7">
       <c r="A139" s="12">
         <v>41183</v>
       </c>
@@ -6306,7 +6306,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7">
       <c r="A140" s="12">
         <v>41214</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7">
       <c r="A141" s="12">
         <v>41244</v>
       </c>
@@ -6354,7 +6354,7 @@
         <v>148000</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7">
       <c r="A142" s="12">
         <v>41275</v>
       </c>
@@ -6378,7 +6378,7 @@
         <v>185000</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7">
       <c r="A143" s="12">
         <v>41306</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7">
       <c r="A144" s="12">
         <v>41334</v>
       </c>
@@ -6426,7 +6426,7 @@
         <v>237000</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7">
       <c r="A145" s="12">
         <v>41365</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>131000</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7">
       <c r="A146" s="12">
         <v>41395</v>
       </c>
@@ -6474,7 +6474,7 @@
         <v>113000</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7">
       <c r="A147" s="12">
         <v>41426</v>
       </c>
@@ -6498,7 +6498,7 @@
         <v>134000</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7">
       <c r="A148" s="12">
         <v>41456</v>
       </c>
@@ -6522,7 +6522,7 @@
         <v>198000</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7">
       <c r="A149" s="12">
         <v>41487</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>198000</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7">
       <c r="A150" s="12">
         <v>41518</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>159000</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7">
       <c r="A151" s="12">
         <v>41548</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7">
       <c r="A152" s="12">
         <v>41579</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>184000</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7">
       <c r="A153" s="12">
         <v>41609</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>229000</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7">
       <c r="A154" s="12">
         <v>41640</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>227000</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7">
       <c r="A155" s="12">
         <v>41671</v>
       </c>
@@ -6690,7 +6690,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7">
       <c r="A156" s="12">
         <v>41699</v>
       </c>
@@ -6714,7 +6714,7 @@
         <v>178000</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7">
       <c r="A157" s="12">
         <v>41730</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>209000</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7">
       <c r="A158" s="12">
         <v>41760</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7">
       <c r="A159" s="12">
         <v>41791</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>179000</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7">
       <c r="A160" s="12">
         <v>41821</v>
       </c>
@@ -6810,7 +6810,7 @@
         <v>281000</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7">
       <c r="A161" s="12">
         <v>41852</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>212000</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7">
       <c r="A162" s="12">
         <v>41883</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>202000</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7">
       <c r="A163" s="12">
         <v>41913</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7">
       <c r="A164" s="12">
         <v>41944</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>233000</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7">
       <c r="A165" s="12">
         <v>41974</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>227000</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7">
       <c r="A166" s="12">
         <v>42005</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>253000</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7">
       <c r="A167" s="12">
         <v>42036</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7">
       <c r="A168" s="12">
         <v>42064</v>
       </c>
@@ -7002,7 +7002,7 @@
         <v>214000</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7">
       <c r="A169" s="12">
         <v>42095</v>
       </c>
@@ -7026,7 +7026,7 @@
         <v>175000</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7">
       <c r="A170" s="12">
         <v>42125</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7">
       <c r="A171" s="12">
         <v>42156</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>203000</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7">
       <c r="A172" s="12">
         <v>42186</v>
       </c>
@@ -7098,7 +7098,7 @@
         <v>229000</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7">
       <c r="A173" s="12">
         <v>42217</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>177000</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7">
       <c r="A174" s="12">
         <v>42248</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7">
       <c r="A175" s="12">
         <v>42278</v>
       </c>
@@ -7170,7 +7170,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7">
       <c r="A176" s="12">
         <v>42309</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>196000</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7">
       <c r="A177" s="12">
         <v>42339</v>
       </c>
@@ -7218,7 +7218,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7">
       <c r="A178" s="12">
         <v>42370</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>267000</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7">
       <c r="A179" s="12">
         <v>42401</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>193000</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7">
       <c r="A180" s="12">
         <v>42430</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>205000</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7">
       <c r="A181" s="12">
         <v>42461</v>
       </c>
@@ -7314,7 +7314,7 @@
         <v>194000</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7">
       <c r="A182" s="12">
         <v>42491</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>166000</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7">
       <c r="A183" s="12">
         <v>42522</v>
       </c>
@@ -7362,7 +7362,7 @@
         <v>168000</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7">
       <c r="A184" s="12">
         <v>42552</v>
       </c>
@@ -7386,7 +7386,7 @@
         <v>176000</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7">
       <c r="A185" s="12">
         <v>42583</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>194000</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7">
       <c r="A186" s="12">
         <v>42614</v>
       </c>
@@ -7434,7 +7434,7 @@
         <v>175000</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7">
       <c r="A187" s="12">
         <v>42644</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>202000</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7">
       <c r="A188" s="12">
         <v>42675</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>119000</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7">
       <c r="A189" s="12">
         <v>42705</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7">
       <c r="A190" s="12">
         <v>42736</v>
       </c>
@@ -7530,7 +7530,7 @@
         <v>151000</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7">
       <c r="A191" s="12">
         <v>42767</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>261000</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7">
       <c r="A192" s="12">
         <v>42795</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>245000</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7">
       <c r="A193" s="12">
         <v>42826</v>
       </c>
@@ -7602,7 +7602,7 @@
         <v>255000</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7">
       <c r="A194" s="12">
         <v>42856</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>174000</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7">
       <c r="A195" s="12">
         <v>42887</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7">
       <c r="A196" s="12">
         <v>42917</v>
       </c>
@@ -7689,7 +7689,7 @@
         <v>191000</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7">
       <c r="A197" s="12">
         <v>42948</v>
       </c>
@@ -7713,7 +7713,7 @@
         <v>201000</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7">
       <c r="A198" s="12">
         <v>42979</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>228000</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7">
       <c r="A199" s="12">
         <v>43009</v>
       </c>
@@ -7761,7 +7761,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7">
       <c r="A200" s="12">
         <v>43040</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>235000</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7">
       <c r="A201" s="12">
         <v>43070</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>185000</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7">
       <c r="A202" s="12">
         <v>43101</v>
       </c>
@@ -7833,7 +7833,7 @@
         <v>242000</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7">
       <c r="A203" s="12">
         <v>43132</v>
       </c>
@@ -7857,7 +7857,7 @@
         <v>244000</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7">
       <c r="A204" s="12">
         <v>43160</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>246000</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7">
       <c r="A205" s="12">
         <v>43191</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>228000</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7">
       <c r="A206" s="12">
         <v>43221</v>
       </c>
@@ -7929,7 +7929,7 @@
         <v>163000</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7">
       <c r="A207" s="12">
         <v>43252</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>189000</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7">
       <c r="A208" s="12">
         <v>43282</v>
       </c>
@@ -7977,7 +7977,7 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7">
       <c r="A209" s="12">
         <v>43313</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>217000</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7">
       <c r="A210" s="12">
         <v>43344</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>168000</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7">
       <c r="A211" s="12">
         <v>43374</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>218000</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7">
       <c r="A212" s="12">
         <v>43405</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7">
       <c r="A213" s="12">
         <v>43435</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7">
       <c r="A214" s="12">
         <v>43466</v>
       </c>
@@ -8121,7 +8121,7 @@
         <v>263000</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7">
       <c r="A215" s="12">
         <v>43497</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7">
       <c r="A216" s="12">
         <v>43525</v>
       </c>
@@ -8169,7 +8169,7 @@
         <v>197000</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7">
       <c r="A217" s="12">
         <v>43556</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>151000</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7">
       <c r="A218" s="12">
         <v>43586</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>271000</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7">
       <c r="A219" s="12">
         <v>43617</v>
       </c>
@@ -8241,7 +8241,7 @@
         <v>41000</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7">
       <c r="A220" s="12">
         <v>43647</v>
       </c>
@@ -8265,7 +8265,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7">
       <c r="A221" s="12">
         <v>43678</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>142000</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7">
       <c r="A222" s="12">
         <v>43709</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7">
       <c r="A223" s="12">
         <v>43739</v>
       </c>
@@ -8337,7 +8337,7 @@
         <v>93000</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7">
       <c r="A224" s="12">
         <v>43770</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>121000</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7">
       <c r="A225" s="12">
         <v>43800</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7">
       <c r="A226" s="12">
         <v>43831</v>
       </c>
@@ -8409,7 +8409,7 @@
         <v>199000</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7">
       <c r="A227" s="12">
         <v>43862</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>209000</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7">
       <c r="A228" s="12">
         <v>43891</v>
       </c>
@@ -8457,7 +8457,7 @@
         <v>183000</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7">
       <c r="A229" s="12">
         <v>43922</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>-149000</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7">
       <c r="A230" s="12">
         <v>43952</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>-19557000</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7">
       <c r="A231" s="12">
         <v>43983</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>3065000</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7">
       <c r="A232" s="12">
         <v>44013</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>4314000</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7">
       <c r="A233" s="12">
         <v>44044</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>212000</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7">
       <c r="A234" s="12">
         <v>44075</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>481000</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7">
       <c r="A235" s="12">
         <v>44105</v>
       </c>
@@ -8625,7 +8625,7 @@
         <v>749000</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7">
       <c r="A236" s="12">
         <v>44136</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>404000</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7">
       <c r="A237" s="12">
         <v>44166</v>
       </c>
@@ -8673,7 +8673,7 @@
         <v>304000</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7">
       <c r="A238" s="12">
         <v>44197</v>
       </c>
@@ -8697,7 +8697,7 @@
         <v>-78000</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7">
       <c r="A239" s="12">
         <v>44228</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>195000</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7">
       <c r="A240" s="12">
         <v>44256</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>176000</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7">
       <c r="A241" s="12">
         <v>44287</v>
       </c>
@@ -8769,7 +8769,7 @@
         <v>565000</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7">
       <c r="A242" s="12">
         <v>44317</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>654000</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7">
       <c r="A243" s="12">
         <v>44348</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>886000</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7">
       <c r="A244" s="12">
         <v>44378</v>
       </c>
@@ -8841,7 +8841,7 @@
         <v>680000</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7">
       <c r="A245" s="12">
         <v>44409</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>326000</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7">
       <c r="A246" s="12">
         <v>44440</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7">
       <c r="A247" s="12">
         <v>44470</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>523000</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7">
       <c r="A248" s="12">
         <v>44501</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>570000</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7">
       <c r="A249" s="12">
         <v>44531</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>505000</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7">
       <c r="A250" s="12">
         <v>44562</v>
       </c>
@@ -8985,7 +8985,7 @@
         <v>776000</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7">
       <c r="A251" s="12">
         <v>44593</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>509000</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7">
       <c r="A252" s="12">
         <v>44621</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7">
       <c r="A253" s="12">
         <v>44652</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>479000</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7">
       <c r="A254" s="12">
         <v>44682</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>202000</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7">
       <c r="A255" s="12">
         <v>44774</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>268000</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7">
       <c r="A256" s="12">
         <v>44805</v>
       </c>
@@ -9129,7 +9129,7 @@
         <v>185000</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7">
       <c r="A257" s="12">
         <v>44835</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>192000</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7">
       <c r="A258" s="12">
         <v>44866</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>239000</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7">
       <c r="A259" s="12">
         <v>44896</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>182000</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7">
       <c r="A260" s="12">
         <v>44927</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>253000</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7">
       <c r="A261" s="12">
         <v>44958</v>
       </c>
@@ -9264,7 +9264,7 @@
         <v>119000</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7">
       <c r="A262" s="12">
         <v>44986</v>
       </c>
@@ -9288,7 +9288,7 @@
         <v>261000</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7">
       <c r="A263" s="12">
         <v>45017</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>142000</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7">
       <c r="A264" s="12">
         <v>45047</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>291000</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7">
       <c r="A265" s="12">
         <v>45078</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>267000</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7">
       <c r="A266" s="12">
         <v>45108</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>455000</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7">
       <c r="A267" s="12">
         <v>45139</v>
       </c>
@@ -9408,7 +9408,7 @@
         <v>371000</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7">
       <c r="A268" s="12">
         <v>45170</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7">
       <c r="A269" s="12">
         <v>45200</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>89000</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7">
       <c r="A270" s="12">
         <v>45231</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>106000</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7">
       <c r="A271" s="12">
         <v>45261</v>
       </c>
@@ -9504,7 +9504,7 @@
         <v>101000</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7">
       <c r="A272" s="12">
         <v>45292</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>158000</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7">
       <c r="A273" s="12">
         <v>45323</v>
       </c>
@@ -9552,7 +9552,7 @@
         <v>111000</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7">
       <c r="A274" s="12">
         <v>45352</v>
       </c>
@@ -9576,7 +9576,7 @@
         <v>155000</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7">
       <c r="A275" s="12">
         <v>45383</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>208000</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7">
       <c r="A276" s="12">
         <v>45413</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>188000</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7">
       <c r="A277" s="12">
         <v>45444</v>
       </c>
@@ -9648,7 +9648,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7">
       <c r="A278" s="12">
         <v>45474</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>155000</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7">
       <c r="A279" s="12">
         <v>45505</v>
       </c>
@@ -9696,7 +9696,7 @@
         <v>111000</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7">
       <c r="A280" s="12">
         <v>45536</v>
       </c>
@@ -9720,7 +9720,7 @@
         <v>103000</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7">
       <c r="A281" s="12">
         <v>45566</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>159000</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7">
       <c r="A282" s="12">
         <v>45597</v>
       </c>
@@ -9768,7 +9768,7 @@
         <v>184000</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7">
       <c r="A283" s="12">
         <v>45627</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>146000</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7">
       <c r="A284" s="12">
         <v>45658</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>176000</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7">
       <c r="A285" s="12">
         <v>45689</v>
       </c>
@@ -9840,7 +9840,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7">
       <c r="A286" s="12">
         <v>45717</v>
       </c>
@@ -9864,7 +9864,7 @@
         <v>84000</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7">
       <c r="A287" s="12">
         <v>45748</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>147000</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7">
       <c r="A288" s="12">
         <v>45778</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7">
       <c r="A289" s="12">
         <v>45809</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>29000</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7">
       <c r="A290" s="12">
         <v>45839</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>-23000</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7">
       <c r="A291" s="12">
         <v>45870</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>106000</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7">
       <c r="A292" s="12">
         <v>45901</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>-3000</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7">
       <c r="A293" s="12">
         <v>45931</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>-29000</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7">
       <c r="A294" s="12">
         <v>45962</v>
       </c>
@@ -10056,7 +10056,7 @@
         <v>47000</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7">
       <c r="A295" s="12">
         <v>45992</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>-29000</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7">
       <c r="A296" s="12">
         <v>46023</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>37000</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7">
       <c r="A297" s="12">
         <v>46054</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7">
       <c r="A298" s="12">
         <v>46082</v>
       </c>
@@ -10152,7 +10152,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7">
       <c r="A299" s="12">
         <v>46113</v>
       </c>
@@ -10188,7 +10188,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABA1812-C744-4515-949A-95B6005467FB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10199,14 +10199,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0E670B-E56D-4466-88FF-6442D4BC04BB}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="1"/>
-    <col min="2" max="2" width="12.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="8.81640625" style="1"/>
+    <col min="2" max="2" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3">
       <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
@@ -10214,7 +10214,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3">
       <c r="B3" s="13" t="s">
         <v>9</v>
       </c>

--- a/data/macro/USA/ADP Nonfarm Employment changes.xlsx
+++ b/data/macro/USA/ADP Nonfarm Employment changes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEC348C-E8E8-44E2-9B9D-33F61082D0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BA06A0-6F6D-41E8-AC81-BE1D4644D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ADPCHNG" sheetId="1" r:id="rId1"/>
@@ -83,8 +83,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -174,7 +174,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -182,16 +182,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -203,16 +197,19 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -230,7 +227,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -269,7 +266,7 @@
             <c:numRef>
               <c:f>ADPCHNG!$B$2:$B$1298</c:f>
               <c:numCache>
-                <c:formatCode>yyyy/mm/dd;@</c:formatCode>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
                 <c:ptCount val="1297"/>
                 <c:pt idx="0">
                   <c:v>37043</c:v>
@@ -3147,50 +3144,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G299"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.90625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="15.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.81640625" style="2"/>
+    <col min="1" max="1" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="15.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="12">
+      <c r="A2" s="13">
         <v>37012</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="13">
         <v>37043</v>
       </c>
-      <c r="C2" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D2" s="9" t="str">
+      <c r="C2" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D2" s="7" t="str">
         <f>IF(
  AND(
   B2 &gt;= IF(
@@ -3214,16 +3211,16 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="12">
+      <c r="A3" s="13">
         <v>37043</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="13">
         <v>37073</v>
       </c>
-      <c r="C3" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D3" s="9" t="str">
+      <c r="C3" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D3" s="7" t="str">
         <f t="shared" ref="D3:D66" si="0">IF(
  AND(
   B3 &gt;= IF(
@@ -3250,16 +3247,16 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>37073</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="13">
         <v>37104</v>
       </c>
-      <c r="C4" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D4" s="9" t="str">
+      <c r="C4" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D4" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3271,16 +3268,16 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="12">
+      <c r="A5" s="13">
         <v>37104</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="13">
         <v>37135</v>
       </c>
-      <c r="C5" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D5" s="9" t="str">
+      <c r="C5" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3292,16 +3289,16 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="12">
+      <c r="A6" s="13">
         <v>37135</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="13">
         <v>37165</v>
       </c>
-      <c r="C6" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D6" s="9" t="str">
+      <c r="C6" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D6" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3313,16 +3310,16 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="12">
+      <c r="A7" s="13">
         <v>37165</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="13">
         <v>37196</v>
       </c>
-      <c r="C7" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D7" s="9" t="str">
+      <c r="C7" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D7" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3334,16 +3331,16 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="12">
+      <c r="A8" s="13">
         <v>37196</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="13">
         <v>37226</v>
       </c>
-      <c r="C8" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D8" s="9" t="str">
+      <c r="C8" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D8" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3355,16 +3352,16 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="12">
+      <c r="A9" s="13">
         <v>37226</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="13">
         <v>37257</v>
       </c>
-      <c r="C9" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D9" s="9" t="str">
+      <c r="C9" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D9" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3376,16 +3373,16 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>37257</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="13">
         <v>37288</v>
       </c>
-      <c r="C10" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D10" s="9" t="str">
+      <c r="C10" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D10" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3397,16 +3394,16 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="12">
+      <c r="A11" s="13">
         <v>37288</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="13">
         <v>37316</v>
       </c>
-      <c r="C11" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D11" s="9" t="str">
+      <c r="C11" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D11" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3418,16 +3415,16 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="12">
+      <c r="A12" s="13">
         <v>37316</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="13">
         <v>37347</v>
       </c>
-      <c r="C12" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D12" s="9" t="str">
+      <c r="C12" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D12" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3439,16 +3436,16 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="12">
+      <c r="A13" s="13">
         <v>37347</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="13">
         <v>37377</v>
       </c>
-      <c r="C13" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D13" s="9" t="str">
+      <c r="C13" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D13" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3460,16 +3457,16 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="12">
+      <c r="A14" s="13">
         <v>37377</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="13">
         <v>37408</v>
       </c>
-      <c r="C14" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D14" s="9" t="str">
+      <c r="C14" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D14" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3481,16 +3478,16 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="12">
+      <c r="A15" s="13">
         <v>37408</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="13">
         <v>37438</v>
       </c>
-      <c r="C15" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D15" s="9" t="str">
+      <c r="C15" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D15" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3502,16 +3499,16 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="12">
+      <c r="A16" s="13">
         <v>37438</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="13">
         <v>37469</v>
       </c>
-      <c r="C16" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D16" s="9" t="str">
+      <c r="C16" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D16" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3523,16 +3520,16 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="12">
+      <c r="A17" s="13">
         <v>37469</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="13">
         <v>37500</v>
       </c>
-      <c r="C17" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D17" s="9" t="str">
+      <c r="C17" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D17" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3544,16 +3541,16 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="12">
+      <c r="A18" s="13">
         <v>37500</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="13">
         <v>37530</v>
       </c>
-      <c r="C18" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D18" s="9" t="str">
+      <c r="C18" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D18" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3565,16 +3562,16 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="12">
+      <c r="A19" s="13">
         <v>37530</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="13">
         <v>37561</v>
       </c>
-      <c r="C19" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D19" s="9" t="str">
+      <c r="C19" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D19" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3586,16 +3583,16 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="12">
+      <c r="A20" s="13">
         <v>37561</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="13">
         <v>37591</v>
       </c>
-      <c r="C20" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D20" s="9" t="str">
+      <c r="C20" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D20" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3607,16 +3604,16 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="12">
+      <c r="A21" s="13">
         <v>37591</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="13">
         <v>37622</v>
       </c>
-      <c r="C21" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D21" s="9" t="str">
+      <c r="C21" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D21" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3628,16 +3625,16 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="12">
+      <c r="A22" s="13">
         <v>37622</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="13">
         <v>37653</v>
       </c>
-      <c r="C22" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D22" s="9" t="str">
+      <c r="C22" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D22" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3649,16 +3646,16 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="12">
+      <c r="A23" s="13">
         <v>37653</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="13">
         <v>37681</v>
       </c>
-      <c r="C23" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D23" s="9" t="str">
+      <c r="C23" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D23" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3670,16 +3667,16 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="12">
+      <c r="A24" s="13">
         <v>37681</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="13">
         <v>37712</v>
       </c>
-      <c r="C24" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D24" s="9" t="str">
+      <c r="C24" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D24" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3691,16 +3688,16 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="12">
+      <c r="A25" s="13">
         <v>37712</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="13">
         <v>37742</v>
       </c>
-      <c r="C25" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D25" s="9" t="str">
+      <c r="C25" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D25" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3712,16 +3709,16 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="12">
+      <c r="A26" s="13">
         <v>37742</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="13">
         <v>37773</v>
       </c>
-      <c r="C26" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D26" s="9" t="str">
+      <c r="C26" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D26" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3733,16 +3730,16 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="12">
+      <c r="A27" s="13">
         <v>37773</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="13">
         <v>37803</v>
       </c>
-      <c r="C27" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D27" s="9" t="str">
+      <c r="C27" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D27" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3754,16 +3751,16 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="12">
+      <c r="A28" s="13">
         <v>37803</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="13">
         <v>37834</v>
       </c>
-      <c r="C28" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D28" s="9" t="str">
+      <c r="C28" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D28" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3775,16 +3772,16 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="12">
+      <c r="A29" s="13">
         <v>37834</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="13">
         <v>37865</v>
       </c>
-      <c r="C29" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D29" s="9" t="str">
+      <c r="C29" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D29" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3796,16 +3793,16 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="12">
+      <c r="A30" s="13">
         <v>37865</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="13">
         <v>37895</v>
       </c>
-      <c r="C30" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D30" s="9" t="str">
+      <c r="C30" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D30" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3817,16 +3814,16 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="12">
+      <c r="A31" s="13">
         <v>37895</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="13">
         <v>37926</v>
       </c>
-      <c r="C31" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D31" s="9" t="str">
+      <c r="C31" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D31" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3838,16 +3835,16 @@
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="12">
+      <c r="A32" s="13">
         <v>37926</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="13">
         <v>37956</v>
       </c>
-      <c r="C32" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D32" s="9" t="str">
+      <c r="C32" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D32" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3859,16 +3856,16 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="12">
+      <c r="A33" s="13">
         <v>37956</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="13">
         <v>37987</v>
       </c>
-      <c r="C33" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D33" s="9" t="str">
+      <c r="C33" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D33" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3880,16 +3877,16 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="12">
+      <c r="A34" s="13">
         <v>37987</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="13">
         <v>38018</v>
       </c>
-      <c r="C34" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D34" s="9" t="str">
+      <c r="C34" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D34" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3901,16 +3898,16 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="12">
+      <c r="A35" s="13">
         <v>38018</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="13">
         <v>38047</v>
       </c>
-      <c r="C35" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D35" s="9" t="str">
+      <c r="C35" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D35" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3922,16 +3919,16 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="12">
+      <c r="A36" s="13">
         <v>38047</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="13">
         <v>38078</v>
       </c>
-      <c r="C36" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D36" s="9" t="str">
+      <c r="C36" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D36" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -3943,16 +3940,16 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="12">
+      <c r="A37" s="13">
         <v>38078</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="13">
         <v>38108</v>
       </c>
-      <c r="C37" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D37" s="9" t="str">
+      <c r="C37" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D37" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3964,16 +3961,16 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="12">
+      <c r="A38" s="13">
         <v>38108</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="13">
         <v>38139</v>
       </c>
-      <c r="C38" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D38" s="9" t="str">
+      <c r="C38" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D38" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -3985,16 +3982,16 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="12">
+      <c r="A39" s="13">
         <v>38139</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="13">
         <v>38169</v>
       </c>
-      <c r="C39" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D39" s="9" t="str">
+      <c r="C39" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D39" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4006,16 +4003,16 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="12">
+      <c r="A40" s="13">
         <v>38169</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="13">
         <v>38200</v>
       </c>
-      <c r="C40" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D40" s="9" t="str">
+      <c r="C40" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D40" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4027,16 +4024,16 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="12">
+      <c r="A41" s="13">
         <v>38200</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="13">
         <v>38231</v>
       </c>
-      <c r="C41" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D41" s="9" t="str">
+      <c r="C41" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D41" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4048,16 +4045,16 @@
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="12">
+      <c r="A42" s="13">
         <v>38231</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="13">
         <v>38261</v>
       </c>
-      <c r="C42" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D42" s="9" t="str">
+      <c r="C42" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D42" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4069,16 +4066,16 @@
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="12">
+      <c r="A43" s="13">
         <v>38261</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="13">
         <v>38292</v>
       </c>
-      <c r="C43" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D43" s="9" t="str">
+      <c r="C43" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D43" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4090,16 +4087,16 @@
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="12">
+      <c r="A44" s="13">
         <v>38292</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="13">
         <v>38322</v>
       </c>
-      <c r="C44" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D44" s="9" t="str">
+      <c r="C44" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D44" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4111,16 +4108,16 @@
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="12">
+      <c r="A45" s="13">
         <v>38322</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="13">
         <v>38353</v>
       </c>
-      <c r="C45" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D45" s="9" t="str">
+      <c r="C45" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D45" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4132,16 +4129,16 @@
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="12">
+      <c r="A46" s="13">
         <v>38353</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="13">
         <v>38384</v>
       </c>
-      <c r="C46" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D46" s="9" t="str">
+      <c r="C46" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D46" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4153,16 +4150,16 @@
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="12">
+      <c r="A47" s="13">
         <v>38384</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="13">
         <v>38412</v>
       </c>
-      <c r="C47" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D47" s="9" t="str">
+      <c r="C47" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D47" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4174,16 +4171,16 @@
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="12">
+      <c r="A48" s="13">
         <v>38412</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="13">
         <v>38443</v>
       </c>
-      <c r="C48" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D48" s="9" t="str">
+      <c r="C48" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D48" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4195,16 +4192,16 @@
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="12">
+      <c r="A49" s="13">
         <v>38443</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="13">
         <v>38473</v>
       </c>
-      <c r="C49" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D49" s="9" t="str">
+      <c r="C49" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D49" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4216,16 +4213,16 @@
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="12">
+      <c r="A50" s="13">
         <v>38473</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="13">
         <v>38504</v>
       </c>
-      <c r="C50" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D50" s="9" t="str">
+      <c r="C50" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D50" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4237,16 +4234,16 @@
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="12">
+      <c r="A51" s="13">
         <v>38504</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="13">
         <v>38534</v>
       </c>
-      <c r="C51" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D51" s="9" t="str">
+      <c r="C51" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D51" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4258,16 +4255,16 @@
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="12">
+      <c r="A52" s="13">
         <v>38534</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="13">
         <v>38565</v>
       </c>
-      <c r="C52" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D52" s="9" t="str">
+      <c r="C52" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D52" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4279,16 +4276,16 @@
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="12">
+      <c r="A53" s="13">
         <v>38565</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="13">
         <v>38596</v>
       </c>
-      <c r="C53" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D53" s="9" t="str">
+      <c r="C53" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D53" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4300,16 +4297,16 @@
       </c>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="12">
+      <c r="A54" s="13">
         <v>38596</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="13">
         <v>38626</v>
       </c>
-      <c r="C54" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D54" s="9" t="str">
+      <c r="C54" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D54" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4321,16 +4318,16 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="12">
+      <c r="A55" s="13">
         <v>38626</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="13">
         <v>38657</v>
       </c>
-      <c r="C55" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D55" s="9" t="str">
+      <c r="C55" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D55" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4342,16 +4339,16 @@
       </c>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="12">
+      <c r="A56" s="13">
         <v>38657</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="13">
         <v>38687</v>
       </c>
-      <c r="C56" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D56" s="9" t="str">
+      <c r="C56" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D56" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4363,16 +4360,16 @@
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="12">
+      <c r="A57" s="13">
         <v>38687</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="13">
         <v>38718</v>
       </c>
-      <c r="C57" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D57" s="9" t="str">
+      <c r="C57" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D57" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4384,16 +4381,16 @@
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="12">
+      <c r="A58" s="13">
         <v>38718</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="13">
         <v>38749</v>
       </c>
-      <c r="C58" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D58" s="9" t="str">
+      <c r="C58" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D58" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4405,16 +4402,16 @@
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="12">
+      <c r="A59" s="13">
         <v>38749</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="13">
         <v>38777</v>
       </c>
-      <c r="C59" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D59" s="9" t="str">
+      <c r="C59" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D59" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4426,16 +4423,16 @@
       </c>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="12">
+      <c r="A60" s="13">
         <v>38777</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="13">
         <v>38808</v>
       </c>
-      <c r="C60" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D60" s="9" t="str">
+      <c r="C60" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D60" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
@@ -4447,16 +4444,16 @@
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="12">
+      <c r="A61" s="13">
         <v>38808</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="13">
         <v>38838</v>
       </c>
-      <c r="C61" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D61" s="9" t="str">
+      <c r="C61" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D61" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4468,16 +4465,16 @@
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="12">
+      <c r="A62" s="13">
         <v>38838</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="13">
         <v>38869</v>
       </c>
-      <c r="C62" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D62" s="9" t="str">
+      <c r="C62" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D62" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4489,16 +4486,16 @@
       </c>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="12">
+      <c r="A63" s="13">
         <v>38869</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="13">
         <v>38899</v>
       </c>
-      <c r="C63" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D63" s="9" t="str">
+      <c r="C63" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D63" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4510,16 +4507,16 @@
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="12">
+      <c r="A64" s="13">
         <v>38899</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B64" s="13">
         <v>38930</v>
       </c>
-      <c r="C64" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D64" s="9" t="str">
+      <c r="C64" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D64" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4531,16 +4528,16 @@
       </c>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="12">
+      <c r="A65" s="13">
         <v>38930</v>
       </c>
-      <c r="B65" s="8">
+      <c r="B65" s="13">
         <v>38961</v>
       </c>
-      <c r="C65" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D65" s="9" t="str">
+      <c r="C65" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D65" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4552,16 +4549,16 @@
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="12">
+      <c r="A66" s="13">
         <v>38961</v>
       </c>
-      <c r="B66" s="8">
+      <c r="B66" s="13">
         <v>38991</v>
       </c>
-      <c r="C66" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D66" s="9" t="str">
+      <c r="C66" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D66" s="7" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
@@ -4573,16 +4570,16 @@
       </c>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="12">
+      <c r="A67" s="13">
         <v>38991</v>
       </c>
-      <c r="B67" s="8">
+      <c r="B67" s="13">
         <v>39022</v>
       </c>
-      <c r="C67" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D67" s="9" t="str">
+      <c r="C67" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D67" s="7" t="str">
         <f t="shared" ref="D67:D130" si="1">IF(
  AND(
   B67 &gt;= IF(
@@ -4609,16 +4606,16 @@
       </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="12">
+      <c r="A68" s="13">
         <v>39022</v>
       </c>
-      <c r="B68" s="8">
+      <c r="B68" s="13">
         <v>39052</v>
       </c>
-      <c r="C68" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D68" s="9" t="str">
+      <c r="C68" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D68" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -4630,16 +4627,16 @@
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="12">
+      <c r="A69" s="13">
         <v>39052</v>
       </c>
-      <c r="B69" s="8">
+      <c r="B69" s="13">
         <v>39083</v>
       </c>
-      <c r="C69" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D69" s="9" t="str">
+      <c r="C69" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D69" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -4651,16 +4648,16 @@
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="12">
+      <c r="A70" s="13">
         <v>39083</v>
       </c>
-      <c r="B70" s="8">
+      <c r="B70" s="13">
         <v>39114</v>
       </c>
-      <c r="C70" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D70" s="9" t="str">
+      <c r="C70" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D70" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -4672,16 +4669,16 @@
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="12">
+      <c r="A71" s="13">
         <v>39114</v>
       </c>
-      <c r="B71" s="8">
+      <c r="B71" s="13">
         <v>39142</v>
       </c>
-      <c r="C71" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D71" s="9" t="str">
+      <c r="C71" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D71" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -4693,16 +4690,16 @@
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="12">
+      <c r="A72" s="13">
         <v>39142</v>
       </c>
-      <c r="B72" s="8">
+      <c r="B72" s="13">
         <v>39173</v>
       </c>
-      <c r="C72" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D72" s="9" t="str">
+      <c r="C72" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D72" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -4714,16 +4711,16 @@
       </c>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="12">
+      <c r="A73" s="13">
         <v>39173</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="13">
         <v>39203</v>
       </c>
-      <c r="C73" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D73" s="9" t="str">
+      <c r="C73" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D73" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -4735,16 +4732,16 @@
       </c>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="12">
+      <c r="A74" s="13">
         <v>39203</v>
       </c>
-      <c r="B74" s="8">
+      <c r="B74" s="13">
         <v>39234</v>
       </c>
-      <c r="C74" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D74" s="9" t="str">
+      <c r="C74" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D74" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -4756,16 +4753,16 @@
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="12">
+      <c r="A75" s="13">
         <v>39234</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="13">
         <v>39264</v>
       </c>
-      <c r="C75" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D75" s="9" t="str">
+      <c r="C75" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D75" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -4777,16 +4774,16 @@
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="12">
+      <c r="A76" s="13">
         <v>39264</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="13">
         <v>39295</v>
       </c>
-      <c r="C76" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D76" s="9" t="str">
+      <c r="C76" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D76" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -4798,16 +4795,16 @@
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="12">
+      <c r="A77" s="13">
         <v>39295</v>
       </c>
-      <c r="B77" s="8">
+      <c r="B77" s="13">
         <v>39326</v>
       </c>
-      <c r="C77" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D77" s="9" t="str">
+      <c r="C77" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D77" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -4819,16 +4816,16 @@
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="12">
+      <c r="A78" s="13">
         <v>39326</v>
       </c>
-      <c r="B78" s="8">
+      <c r="B78" s="13">
         <v>39356</v>
       </c>
-      <c r="C78" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D78" s="9" t="str">
+      <c r="C78" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D78" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -4840,16 +4837,16 @@
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="12">
+      <c r="A79" s="13">
         <v>39356</v>
       </c>
-      <c r="B79" s="8">
+      <c r="B79" s="13">
         <v>39387</v>
       </c>
-      <c r="C79" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D79" s="9" t="str">
+      <c r="C79" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D79" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -4861,16 +4858,16 @@
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="12">
+      <c r="A80" s="13">
         <v>39387</v>
       </c>
-      <c r="B80" s="8">
+      <c r="B80" s="13">
         <v>39417</v>
       </c>
-      <c r="C80" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D80" s="9" t="str">
+      <c r="C80" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D80" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -4882,16 +4879,16 @@
       </c>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="12">
+      <c r="A81" s="13">
         <v>39417</v>
       </c>
-      <c r="B81" s="8">
+      <c r="B81" s="13">
         <v>39448</v>
       </c>
-      <c r="C81" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D81" s="9" t="str">
+      <c r="C81" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D81" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -4903,16 +4900,16 @@
       </c>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="12">
+      <c r="A82" s="13">
         <v>39448</v>
       </c>
-      <c r="B82" s="8">
+      <c r="B82" s="13">
         <v>39479</v>
       </c>
-      <c r="C82" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D82" s="9" t="str">
+      <c r="C82" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D82" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -4924,16 +4921,16 @@
       </c>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="12">
+      <c r="A83" s="13">
         <v>39479</v>
       </c>
-      <c r="B83" s="8">
+      <c r="B83" s="13">
         <v>39512</v>
       </c>
-      <c r="C83" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D83" s="9" t="str">
+      <c r="C83" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D83" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -4948,16 +4945,16 @@
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="12">
+      <c r="A84" s="13">
         <v>39508</v>
       </c>
-      <c r="B84" s="8">
+      <c r="B84" s="13">
         <v>39540</v>
       </c>
-      <c r="C84" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D84" s="9" t="str">
+      <c r="C84" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D84" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -4972,16 +4969,16 @@
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="12">
+      <c r="A85" s="13">
         <v>39539</v>
       </c>
-      <c r="B85" s="8">
+      <c r="B85" s="13">
         <v>39568</v>
       </c>
-      <c r="C85" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D85" s="9" t="str">
+      <c r="C85" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D85" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -4996,16 +4993,16 @@
       </c>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="12">
+      <c r="A86" s="13">
         <v>39569</v>
       </c>
-      <c r="B86" s="8">
+      <c r="B86" s="13">
         <v>39603</v>
       </c>
-      <c r="C86" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D86" s="9" t="str">
+      <c r="C86" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D86" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5020,16 +5017,16 @@
       </c>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="12">
+      <c r="A87" s="13">
         <v>39600</v>
       </c>
-      <c r="B87" s="8">
+      <c r="B87" s="13">
         <v>39631</v>
       </c>
-      <c r="C87" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D87" s="9" t="str">
+      <c r="C87" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D87" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5044,16 +5041,16 @@
       </c>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="12">
+      <c r="A88" s="13">
         <v>39630</v>
       </c>
-      <c r="B88" s="8">
+      <c r="B88" s="13">
         <v>39659</v>
       </c>
-      <c r="C88" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D88" s="9" t="str">
+      <c r="C88" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D88" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5068,16 +5065,16 @@
       </c>
     </row>
     <row r="89" spans="1:7">
-      <c r="A89" s="12">
+      <c r="A89" s="13">
         <v>39661</v>
       </c>
-      <c r="B89" s="8">
+      <c r="B89" s="13">
         <v>39695</v>
       </c>
-      <c r="C89" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D89" s="9" t="str">
+      <c r="C89" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D89" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5092,16 +5089,16 @@
       </c>
     </row>
     <row r="90" spans="1:7">
-      <c r="A90" s="12">
+      <c r="A90" s="13">
         <v>39692</v>
       </c>
-      <c r="B90" s="8">
+      <c r="B90" s="13">
         <v>39722</v>
       </c>
-      <c r="C90" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D90" s="9" t="str">
+      <c r="C90" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D90" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5116,16 +5113,16 @@
       </c>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="12">
+      <c r="A91" s="13">
         <v>39722</v>
       </c>
-      <c r="B91" s="8">
+      <c r="B91" s="13">
         <v>39757</v>
       </c>
-      <c r="C91" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D91" s="9" t="str">
+      <c r="C91" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D91" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5140,16 +5137,16 @@
       </c>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="12">
+      <c r="A92" s="13">
         <v>39753</v>
       </c>
-      <c r="B92" s="8">
+      <c r="B92" s="13">
         <v>39785</v>
       </c>
-      <c r="C92" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D92" s="9" t="str">
+      <c r="C92" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D92" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5164,16 +5161,16 @@
       </c>
     </row>
     <row r="93" spans="1:7">
-      <c r="A93" s="12">
+      <c r="A93" s="13">
         <v>39783</v>
       </c>
-      <c r="B93" s="8">
+      <c r="B93" s="13">
         <v>39820</v>
       </c>
-      <c r="C93" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D93" s="9" t="str">
+      <c r="C93" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D93" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5188,16 +5185,16 @@
       </c>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="12">
+      <c r="A94" s="13">
         <v>39814</v>
       </c>
-      <c r="B94" s="8">
+      <c r="B94" s="13">
         <v>39848</v>
       </c>
-      <c r="C94" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D94" s="9" t="str">
+      <c r="C94" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D94" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5212,16 +5209,16 @@
       </c>
     </row>
     <row r="95" spans="1:7">
-      <c r="A95" s="12">
+      <c r="A95" s="13">
         <v>39845</v>
       </c>
-      <c r="B95" s="8">
+      <c r="B95" s="13">
         <v>39876</v>
       </c>
-      <c r="C95" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D95" s="9" t="str">
+      <c r="C95" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D95" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5236,16 +5233,16 @@
       </c>
     </row>
     <row r="96" spans="1:7">
-      <c r="A96" s="12">
+      <c r="A96" s="13">
         <v>39873</v>
       </c>
-      <c r="B96" s="8">
+      <c r="B96" s="13">
         <v>39904</v>
       </c>
-      <c r="C96" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D96" s="9" t="str">
+      <c r="C96" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D96" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5260,16 +5257,16 @@
       </c>
     </row>
     <row r="97" spans="1:7">
-      <c r="A97" s="12">
+      <c r="A97" s="13">
         <v>39904</v>
       </c>
-      <c r="B97" s="8">
+      <c r="B97" s="13">
         <v>39939</v>
       </c>
-      <c r="C97" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D97" s="9" t="str">
+      <c r="C97" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D97" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5284,16 +5281,16 @@
       </c>
     </row>
     <row r="98" spans="1:7">
-      <c r="A98" s="12">
+      <c r="A98" s="13">
         <v>39934</v>
       </c>
-      <c r="B98" s="8">
+      <c r="B98" s="13">
         <v>39967</v>
       </c>
-      <c r="C98" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D98" s="9" t="str">
+      <c r="C98" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D98" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5308,16 +5305,16 @@
       </c>
     </row>
     <row r="99" spans="1:7">
-      <c r="A99" s="12">
+      <c r="A99" s="13">
         <v>39965</v>
       </c>
-      <c r="B99" s="8">
+      <c r="B99" s="13">
         <v>39995</v>
       </c>
-      <c r="C99" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D99" s="9" t="str">
+      <c r="C99" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D99" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5332,16 +5329,16 @@
       </c>
     </row>
     <row r="100" spans="1:7">
-      <c r="A100" s="12">
+      <c r="A100" s="13">
         <v>39995</v>
       </c>
-      <c r="B100" s="8">
+      <c r="B100" s="13">
         <v>40030</v>
       </c>
-      <c r="C100" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D100" s="9" t="str">
+      <c r="C100" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D100" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5356,16 +5353,16 @@
       </c>
     </row>
     <row r="101" spans="1:7">
-      <c r="A101" s="12">
+      <c r="A101" s="13">
         <v>40026</v>
       </c>
-      <c r="B101" s="8">
+      <c r="B101" s="13">
         <v>40058</v>
       </c>
-      <c r="C101" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D101" s="9" t="str">
+      <c r="C101" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D101" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5380,16 +5377,16 @@
       </c>
     </row>
     <row r="102" spans="1:7">
-      <c r="A102" s="12">
+      <c r="A102" s="13">
         <v>40057</v>
       </c>
-      <c r="B102" s="8">
+      <c r="B102" s="13">
         <v>40086</v>
       </c>
-      <c r="C102" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D102" s="9" t="str">
+      <c r="C102" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D102" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5404,16 +5401,16 @@
       </c>
     </row>
     <row r="103" spans="1:7">
-      <c r="A103" s="12">
+      <c r="A103" s="13">
         <v>40087</v>
       </c>
-      <c r="B103" s="8">
+      <c r="B103" s="13">
         <v>40121</v>
       </c>
-      <c r="C103" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D103" s="9" t="str">
+      <c r="C103" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D103" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5428,16 +5425,16 @@
       </c>
     </row>
     <row r="104" spans="1:7">
-      <c r="A104" s="12">
+      <c r="A104" s="13">
         <v>40118</v>
       </c>
-      <c r="B104" s="8">
+      <c r="B104" s="13">
         <v>40149</v>
       </c>
-      <c r="C104" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D104" s="9" t="str">
+      <c r="C104" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D104" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5452,16 +5449,16 @@
       </c>
     </row>
     <row r="105" spans="1:7">
-      <c r="A105" s="12">
+      <c r="A105" s="13">
         <v>40148</v>
       </c>
-      <c r="B105" s="8">
+      <c r="B105" s="13">
         <v>40184</v>
       </c>
-      <c r="C105" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D105" s="9" t="str">
+      <c r="C105" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D105" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5476,16 +5473,16 @@
       </c>
     </row>
     <row r="106" spans="1:7">
-      <c r="A106" s="12">
+      <c r="A106" s="13">
         <v>40179</v>
       </c>
-      <c r="B106" s="8">
+      <c r="B106" s="13">
         <v>40212</v>
       </c>
-      <c r="C106" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D106" s="9" t="str">
+      <c r="C106" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D106" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5500,16 +5497,16 @@
       </c>
     </row>
     <row r="107" spans="1:7">
-      <c r="A107" s="12">
+      <c r="A107" s="13">
         <v>40210</v>
       </c>
-      <c r="B107" s="8">
+      <c r="B107" s="13">
         <v>40240</v>
       </c>
-      <c r="C107" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D107" s="9" t="str">
+      <c r="C107" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D107" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5524,16 +5521,16 @@
       </c>
     </row>
     <row r="108" spans="1:7">
-      <c r="A108" s="12">
+      <c r="A108" s="13">
         <v>40238</v>
       </c>
-      <c r="B108" s="8">
+      <c r="B108" s="13">
         <v>40268</v>
       </c>
-      <c r="C108" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D108" s="9" t="str">
+      <c r="C108" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D108" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5548,16 +5545,16 @@
       </c>
     </row>
     <row r="109" spans="1:7">
-      <c r="A109" s="12">
+      <c r="A109" s="13">
         <v>40269</v>
       </c>
-      <c r="B109" s="8">
+      <c r="B109" s="13">
         <v>40303</v>
       </c>
-      <c r="C109" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D109" s="9" t="str">
+      <c r="C109" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D109" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5572,16 +5569,16 @@
       </c>
     </row>
     <row r="110" spans="1:7">
-      <c r="A110" s="12">
+      <c r="A110" s="13">
         <v>40299</v>
       </c>
-      <c r="B110" s="8">
+      <c r="B110" s="13">
         <v>40332</v>
       </c>
-      <c r="C110" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D110" s="9" t="str">
+      <c r="C110" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D110" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5596,16 +5593,16 @@
       </c>
     </row>
     <row r="111" spans="1:7">
-      <c r="A111" s="12">
+      <c r="A111" s="13">
         <v>40330</v>
       </c>
-      <c r="B111" s="8">
+      <c r="B111" s="13">
         <v>40359</v>
       </c>
-      <c r="C111" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D111" s="9" t="str">
+      <c r="C111" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D111" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5620,16 +5617,16 @@
       </c>
     </row>
     <row r="112" spans="1:7">
-      <c r="A112" s="12">
+      <c r="A112" s="13">
         <v>40360</v>
       </c>
-      <c r="B112" s="8">
+      <c r="B112" s="13">
         <v>40394</v>
       </c>
-      <c r="C112" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D112" s="9" t="str">
+      <c r="C112" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D112" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5644,16 +5641,16 @@
       </c>
     </row>
     <row r="113" spans="1:7">
-      <c r="A113" s="12">
+      <c r="A113" s="13">
         <v>40391</v>
       </c>
-      <c r="B113" s="8">
+      <c r="B113" s="13">
         <v>40422</v>
       </c>
-      <c r="C113" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D113" s="9" t="str">
+      <c r="C113" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D113" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5668,16 +5665,16 @@
       </c>
     </row>
     <row r="114" spans="1:7">
-      <c r="A114" s="12">
+      <c r="A114" s="13">
         <v>40422</v>
       </c>
-      <c r="B114" s="8">
+      <c r="B114" s="13">
         <v>40457</v>
       </c>
-      <c r="C114" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D114" s="9" t="str">
+      <c r="C114" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D114" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5692,16 +5689,16 @@
       </c>
     </row>
     <row r="115" spans="1:7">
-      <c r="A115" s="12">
+      <c r="A115" s="13">
         <v>40452</v>
       </c>
-      <c r="B115" s="8">
+      <c r="B115" s="13">
         <v>40485</v>
       </c>
-      <c r="C115" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D115" s="9" t="str">
+      <c r="C115" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D115" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5716,16 +5713,16 @@
       </c>
     </row>
     <row r="116" spans="1:7">
-      <c r="A116" s="12">
+      <c r="A116" s="13">
         <v>40483</v>
       </c>
-      <c r="B116" s="8">
+      <c r="B116" s="13">
         <v>40513</v>
       </c>
-      <c r="C116" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D116" s="9" t="str">
+      <c r="C116" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D116" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5740,16 +5737,16 @@
       </c>
     </row>
     <row r="117" spans="1:7">
-      <c r="A117" s="12">
+      <c r="A117" s="13">
         <v>40513</v>
       </c>
-      <c r="B117" s="8">
+      <c r="B117" s="13">
         <v>40548</v>
       </c>
-      <c r="C117" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D117" s="9" t="str">
+      <c r="C117" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D117" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5764,16 +5761,16 @@
       </c>
     </row>
     <row r="118" spans="1:7">
-      <c r="A118" s="12">
+      <c r="A118" s="13">
         <v>40544</v>
       </c>
-      <c r="B118" s="8">
+      <c r="B118" s="13">
         <v>40576</v>
       </c>
-      <c r="C118" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D118" s="9" t="str">
+      <c r="C118" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D118" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5788,16 +5785,16 @@
       </c>
     </row>
     <row r="119" spans="1:7">
-      <c r="A119" s="12">
+      <c r="A119" s="13">
         <v>40575</v>
       </c>
-      <c r="B119" s="8">
+      <c r="B119" s="13">
         <v>40604</v>
       </c>
-      <c r="C119" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D119" s="9" t="str">
+      <c r="C119" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D119" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -5812,16 +5809,16 @@
       </c>
     </row>
     <row r="120" spans="1:7">
-      <c r="A120" s="12">
+      <c r="A120" s="13">
         <v>40603</v>
       </c>
-      <c r="B120" s="8">
+      <c r="B120" s="13">
         <v>40632</v>
       </c>
-      <c r="C120" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D120" s="9" t="str">
+      <c r="C120" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D120" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5836,16 +5833,16 @@
       </c>
     </row>
     <row r="121" spans="1:7">
-      <c r="A121" s="12">
+      <c r="A121" s="13">
         <v>40634</v>
       </c>
-      <c r="B121" s="8">
+      <c r="B121" s="13">
         <v>40667</v>
       </c>
-      <c r="C121" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D121" s="9" t="str">
+      <c r="C121" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D121" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5860,16 +5857,16 @@
       </c>
     </row>
     <row r="122" spans="1:7">
-      <c r="A122" s="12">
+      <c r="A122" s="13">
         <v>40664</v>
       </c>
-      <c r="B122" s="8">
+      <c r="B122" s="13">
         <v>40695</v>
       </c>
-      <c r="C122" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D122" s="9" t="str">
+      <c r="C122" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D122" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5884,16 +5881,16 @@
       </c>
     </row>
     <row r="123" spans="1:7">
-      <c r="A123" s="12">
+      <c r="A123" s="13">
         <v>40695</v>
       </c>
-      <c r="B123" s="8">
+      <c r="B123" s="13">
         <v>40731</v>
       </c>
-      <c r="C123" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D123" s="9" t="str">
+      <c r="C123" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D123" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5908,16 +5905,16 @@
       </c>
     </row>
     <row r="124" spans="1:7">
-      <c r="A124" s="12">
+      <c r="A124" s="13">
         <v>40725</v>
       </c>
-      <c r="B124" s="8">
+      <c r="B124" s="13">
         <v>40758</v>
       </c>
-      <c r="C124" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D124" s="9" t="str">
+      <c r="C124" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D124" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5932,16 +5929,16 @@
       </c>
     </row>
     <row r="125" spans="1:7">
-      <c r="A125" s="12">
+      <c r="A125" s="13">
         <v>40756</v>
       </c>
-      <c r="B125" s="8">
+      <c r="B125" s="13">
         <v>40786</v>
       </c>
-      <c r="C125" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D125" s="9" t="str">
+      <c r="C125" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D125" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5956,16 +5953,16 @@
       </c>
     </row>
     <row r="126" spans="1:7">
-      <c r="A126" s="12">
+      <c r="A126" s="13">
         <v>40787</v>
       </c>
-      <c r="B126" s="8">
+      <c r="B126" s="13">
         <v>40821</v>
       </c>
-      <c r="C126" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D126" s="9" t="str">
+      <c r="C126" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D126" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -5980,16 +5977,16 @@
       </c>
     </row>
     <row r="127" spans="1:7">
-      <c r="A127" s="12">
+      <c r="A127" s="13">
         <v>40817</v>
       </c>
-      <c r="B127" s="8">
+      <c r="B127" s="13">
         <v>40849</v>
       </c>
-      <c r="C127" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D127" s="9" t="str">
+      <c r="C127" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D127" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
@@ -6004,16 +6001,16 @@
       </c>
     </row>
     <row r="128" spans="1:7">
-      <c r="A128" s="12">
+      <c r="A128" s="13">
         <v>40848</v>
       </c>
-      <c r="B128" s="8">
+      <c r="B128" s="13">
         <v>40877</v>
       </c>
-      <c r="C128" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D128" s="9" t="str">
+      <c r="C128" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D128" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -6028,16 +6025,16 @@
       </c>
     </row>
     <row r="129" spans="1:7">
-      <c r="A129" s="12">
+      <c r="A129" s="13">
         <v>40878</v>
       </c>
-      <c r="B129" s="8">
+      <c r="B129" s="13">
         <v>40913</v>
       </c>
-      <c r="C129" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D129" s="9" t="str">
+      <c r="C129" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D129" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -6052,16 +6049,16 @@
       </c>
     </row>
     <row r="130" spans="1:7">
-      <c r="A130" s="12">
+      <c r="A130" s="13">
         <v>40909</v>
       </c>
-      <c r="B130" s="8">
+      <c r="B130" s="13">
         <v>40940</v>
       </c>
-      <c r="C130" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D130" s="9" t="str">
+      <c r="C130" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D130" s="7" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
@@ -6076,16 +6073,16 @@
       </c>
     </row>
     <row r="131" spans="1:7">
-      <c r="A131" s="12">
+      <c r="A131" s="13">
         <v>40940</v>
       </c>
-      <c r="B131" s="8">
+      <c r="B131" s="13">
         <v>40975</v>
       </c>
-      <c r="C131" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D131" s="9" t="str">
+      <c r="C131" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D131" s="7" t="str">
         <f t="shared" ref="D131:D194" si="2">IF(
  AND(
   B131 &gt;= IF(
@@ -6115,16 +6112,16 @@
       </c>
     </row>
     <row r="132" spans="1:7">
-      <c r="A132" s="12">
+      <c r="A132" s="13">
         <v>40969</v>
       </c>
-      <c r="B132" s="8">
+      <c r="B132" s="13">
         <v>41003</v>
       </c>
-      <c r="C132" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D132" s="9" t="str">
+      <c r="C132" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D132" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6139,16 +6136,16 @@
       </c>
     </row>
     <row r="133" spans="1:7">
-      <c r="A133" s="12">
+      <c r="A133" s="13">
         <v>41000</v>
       </c>
-      <c r="B133" s="8">
+      <c r="B133" s="13">
         <v>41031</v>
       </c>
-      <c r="C133" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D133" s="9" t="str">
+      <c r="C133" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D133" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6163,16 +6160,16 @@
       </c>
     </row>
     <row r="134" spans="1:7">
-      <c r="A134" s="12">
+      <c r="A134" s="13">
         <v>41030</v>
       </c>
-      <c r="B134" s="8">
+      <c r="B134" s="13">
         <v>41060</v>
       </c>
-      <c r="C134" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D134" s="9" t="str">
+      <c r="C134" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D134" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6187,16 +6184,16 @@
       </c>
     </row>
     <row r="135" spans="1:7">
-      <c r="A135" s="12">
+      <c r="A135" s="13">
         <v>41061</v>
       </c>
-      <c r="B135" s="8">
+      <c r="B135" s="13">
         <v>41095</v>
       </c>
-      <c r="C135" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D135" s="9" t="str">
+      <c r="C135" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D135" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6211,16 +6208,16 @@
       </c>
     </row>
     <row r="136" spans="1:7">
-      <c r="A136" s="12">
+      <c r="A136" s="13">
         <v>41091</v>
       </c>
-      <c r="B136" s="8">
+      <c r="B136" s="13">
         <v>41122</v>
       </c>
-      <c r="C136" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D136" s="9" t="str">
+      <c r="C136" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D136" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6235,16 +6232,16 @@
       </c>
     </row>
     <row r="137" spans="1:7">
-      <c r="A137" s="12">
+      <c r="A137" s="13">
         <v>41122</v>
       </c>
-      <c r="B137" s="8">
+      <c r="B137" s="13">
         <v>41158</v>
       </c>
-      <c r="C137" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D137" s="9" t="str">
+      <c r="C137" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D137" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6259,16 +6256,16 @@
       </c>
     </row>
     <row r="138" spans="1:7">
-      <c r="A138" s="12">
+      <c r="A138" s="13">
         <v>41153</v>
       </c>
-      <c r="B138" s="8">
+      <c r="B138" s="13">
         <v>41185</v>
       </c>
-      <c r="C138" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D138" s="9" t="str">
+      <c r="C138" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D138" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6283,16 +6280,16 @@
       </c>
     </row>
     <row r="139" spans="1:7">
-      <c r="A139" s="12">
+      <c r="A139" s="13">
         <v>41183</v>
       </c>
-      <c r="B139" s="8">
+      <c r="B139" s="13">
         <v>41214</v>
       </c>
-      <c r="C139" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D139" s="9" t="str">
+      <c r="C139" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D139" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6307,16 +6304,16 @@
       </c>
     </row>
     <row r="140" spans="1:7">
-      <c r="A140" s="12">
+      <c r="A140" s="13">
         <v>41214</v>
       </c>
-      <c r="B140" s="8">
+      <c r="B140" s="13">
         <v>41248</v>
       </c>
-      <c r="C140" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D140" s="9" t="str">
+      <c r="C140" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D140" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6331,16 +6328,16 @@
       </c>
     </row>
     <row r="141" spans="1:7">
-      <c r="A141" s="12">
+      <c r="A141" s="13">
         <v>41244</v>
       </c>
-      <c r="B141" s="8">
+      <c r="B141" s="13">
         <v>41277</v>
       </c>
-      <c r="C141" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D141" s="9" t="str">
+      <c r="C141" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D141" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6355,16 +6352,16 @@
       </c>
     </row>
     <row r="142" spans="1:7">
-      <c r="A142" s="12">
+      <c r="A142" s="13">
         <v>41275</v>
       </c>
-      <c r="B142" s="8">
+      <c r="B142" s="13">
         <v>41304</v>
       </c>
-      <c r="C142" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D142" s="9" t="str">
+      <c r="C142" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D142" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6379,16 +6376,16 @@
       </c>
     </row>
     <row r="143" spans="1:7">
-      <c r="A143" s="12">
+      <c r="A143" s="13">
         <v>41306</v>
       </c>
-      <c r="B143" s="8">
+      <c r="B143" s="13">
         <v>41339</v>
       </c>
-      <c r="C143" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D143" s="9" t="str">
+      <c r="C143" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D143" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6403,16 +6400,16 @@
       </c>
     </row>
     <row r="144" spans="1:7">
-      <c r="A144" s="12">
+      <c r="A144" s="13">
         <v>41334</v>
       </c>
-      <c r="B144" s="8">
+      <c r="B144" s="13">
         <v>41367</v>
       </c>
-      <c r="C144" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D144" s="9" t="str">
+      <c r="C144" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D144" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6427,16 +6424,16 @@
       </c>
     </row>
     <row r="145" spans="1:7">
-      <c r="A145" s="12">
+      <c r="A145" s="13">
         <v>41365</v>
       </c>
-      <c r="B145" s="8">
+      <c r="B145" s="13">
         <v>41395</v>
       </c>
-      <c r="C145" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D145" s="9" t="str">
+      <c r="C145" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D145" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6451,16 +6448,16 @@
       </c>
     </row>
     <row r="146" spans="1:7">
-      <c r="A146" s="12">
+      <c r="A146" s="13">
         <v>41395</v>
       </c>
-      <c r="B146" s="8">
+      <c r="B146" s="13">
         <v>41430</v>
       </c>
-      <c r="C146" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D146" s="9" t="str">
+      <c r="C146" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D146" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6475,16 +6472,16 @@
       </c>
     </row>
     <row r="147" spans="1:7">
-      <c r="A147" s="12">
+      <c r="A147" s="13">
         <v>41426</v>
       </c>
-      <c r="B147" s="8">
+      <c r="B147" s="13">
         <v>41458</v>
       </c>
-      <c r="C147" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D147" s="9" t="str">
+      <c r="C147" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D147" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6499,16 +6496,16 @@
       </c>
     </row>
     <row r="148" spans="1:7">
-      <c r="A148" s="12">
+      <c r="A148" s="13">
         <v>41456</v>
       </c>
-      <c r="B148" s="8">
+      <c r="B148" s="13">
         <v>41486</v>
       </c>
-      <c r="C148" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D148" s="9" t="str">
+      <c r="C148" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D148" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6523,16 +6520,16 @@
       </c>
     </row>
     <row r="149" spans="1:7">
-      <c r="A149" s="12">
+      <c r="A149" s="13">
         <v>41487</v>
       </c>
-      <c r="B149" s="8">
+      <c r="B149" s="13">
         <v>41522</v>
       </c>
-      <c r="C149" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D149" s="9" t="str">
+      <c r="C149" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D149" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6547,16 +6544,16 @@
       </c>
     </row>
     <row r="150" spans="1:7">
-      <c r="A150" s="12">
+      <c r="A150" s="13">
         <v>41518</v>
       </c>
-      <c r="B150" s="8">
+      <c r="B150" s="13">
         <v>41549</v>
       </c>
-      <c r="C150" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D150" s="9" t="str">
+      <c r="C150" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D150" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6571,16 +6568,16 @@
       </c>
     </row>
     <row r="151" spans="1:7">
-      <c r="A151" s="12">
+      <c r="A151" s="13">
         <v>41548</v>
       </c>
-      <c r="B151" s="8">
+      <c r="B151" s="13">
         <v>41577</v>
       </c>
-      <c r="C151" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D151" s="9" t="str">
+      <c r="C151" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D151" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6595,16 +6592,16 @@
       </c>
     </row>
     <row r="152" spans="1:7">
-      <c r="A152" s="12">
+      <c r="A152" s="13">
         <v>41579</v>
       </c>
-      <c r="B152" s="8">
+      <c r="B152" s="13">
         <v>41612</v>
       </c>
-      <c r="C152" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D152" s="9" t="str">
+      <c r="C152" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D152" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6619,16 +6616,16 @@
       </c>
     </row>
     <row r="153" spans="1:7">
-      <c r="A153" s="12">
+      <c r="A153" s="13">
         <v>41609</v>
       </c>
-      <c r="B153" s="8">
+      <c r="B153" s="13">
         <v>41647</v>
       </c>
-      <c r="C153" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D153" s="9" t="str">
+      <c r="C153" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D153" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6643,16 +6640,16 @@
       </c>
     </row>
     <row r="154" spans="1:7">
-      <c r="A154" s="12">
+      <c r="A154" s="13">
         <v>41640</v>
       </c>
-      <c r="B154" s="8">
+      <c r="B154" s="13">
         <v>41675</v>
       </c>
-      <c r="C154" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D154" s="9" t="str">
+      <c r="C154" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D154" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6667,16 +6664,16 @@
       </c>
     </row>
     <row r="155" spans="1:7">
-      <c r="A155" s="12">
+      <c r="A155" s="13">
         <v>41671</v>
       </c>
-      <c r="B155" s="8">
+      <c r="B155" s="13">
         <v>41703</v>
       </c>
-      <c r="C155" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D155" s="9" t="str">
+      <c r="C155" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D155" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6691,16 +6688,16 @@
       </c>
     </row>
     <row r="156" spans="1:7">
-      <c r="A156" s="12">
+      <c r="A156" s="13">
         <v>41699</v>
       </c>
-      <c r="B156" s="8">
+      <c r="B156" s="13">
         <v>41731</v>
       </c>
-      <c r="C156" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D156" s="9" t="str">
+      <c r="C156" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D156" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6715,16 +6712,16 @@
       </c>
     </row>
     <row r="157" spans="1:7">
-      <c r="A157" s="12">
+      <c r="A157" s="13">
         <v>41730</v>
       </c>
-      <c r="B157" s="8">
+      <c r="B157" s="13">
         <v>41759</v>
       </c>
-      <c r="C157" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D157" s="9" t="str">
+      <c r="C157" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D157" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6739,16 +6736,16 @@
       </c>
     </row>
     <row r="158" spans="1:7">
-      <c r="A158" s="12">
+      <c r="A158" s="13">
         <v>41760</v>
       </c>
-      <c r="B158" s="8">
+      <c r="B158" s="13">
         <v>41794</v>
       </c>
-      <c r="C158" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D158" s="9" t="str">
+      <c r="C158" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D158" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6763,16 +6760,16 @@
       </c>
     </row>
     <row r="159" spans="1:7">
-      <c r="A159" s="12">
+      <c r="A159" s="13">
         <v>41791</v>
       </c>
-      <c r="B159" s="8">
+      <c r="B159" s="13">
         <v>41822</v>
       </c>
-      <c r="C159" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D159" s="9" t="str">
+      <c r="C159" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D159" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6787,16 +6784,16 @@
       </c>
     </row>
     <row r="160" spans="1:7">
-      <c r="A160" s="12">
+      <c r="A160" s="13">
         <v>41821</v>
       </c>
-      <c r="B160" s="8">
+      <c r="B160" s="13">
         <v>41850</v>
       </c>
-      <c r="C160" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D160" s="9" t="str">
+      <c r="C160" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D160" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6811,16 +6808,16 @@
       </c>
     </row>
     <row r="161" spans="1:7">
-      <c r="A161" s="12">
+      <c r="A161" s="13">
         <v>41852</v>
       </c>
-      <c r="B161" s="8">
+      <c r="B161" s="13">
         <v>41886</v>
       </c>
-      <c r="C161" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D161" s="9" t="str">
+      <c r="C161" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D161" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6835,16 +6832,16 @@
       </c>
     </row>
     <row r="162" spans="1:7">
-      <c r="A162" s="12">
+      <c r="A162" s="13">
         <v>41883</v>
       </c>
-      <c r="B162" s="8">
+      <c r="B162" s="13">
         <v>41913</v>
       </c>
-      <c r="C162" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D162" s="9" t="str">
+      <c r="C162" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D162" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -6859,16 +6856,16 @@
       </c>
     </row>
     <row r="163" spans="1:7">
-      <c r="A163" s="12">
+      <c r="A163" s="13">
         <v>41913</v>
       </c>
-      <c r="B163" s="8">
+      <c r="B163" s="13">
         <v>41948</v>
       </c>
-      <c r="C163" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D163" s="9" t="str">
+      <c r="C163" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D163" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6883,16 +6880,16 @@
       </c>
     </row>
     <row r="164" spans="1:7">
-      <c r="A164" s="12">
+      <c r="A164" s="13">
         <v>41944</v>
       </c>
-      <c r="B164" s="8">
+      <c r="B164" s="13">
         <v>41976</v>
       </c>
-      <c r="C164" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D164" s="9" t="str">
+      <c r="C164" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D164" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6907,16 +6904,16 @@
       </c>
     </row>
     <row r="165" spans="1:7">
-      <c r="A165" s="12">
+      <c r="A165" s="13">
         <v>41974</v>
       </c>
-      <c r="B165" s="8">
+      <c r="B165" s="13">
         <v>42011</v>
       </c>
-      <c r="C165" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D165" s="9" t="str">
+      <c r="C165" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D165" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6931,16 +6928,16 @@
       </c>
     </row>
     <row r="166" spans="1:7">
-      <c r="A166" s="12">
+      <c r="A166" s="13">
         <v>42005</v>
       </c>
-      <c r="B166" s="8">
+      <c r="B166" s="13">
         <v>42039</v>
       </c>
-      <c r="C166" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D166" s="9" t="str">
+      <c r="C166" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D166" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6955,16 +6952,16 @@
       </c>
     </row>
     <row r="167" spans="1:7">
-      <c r="A167" s="12">
+      <c r="A167" s="13">
         <v>42036</v>
       </c>
-      <c r="B167" s="8">
+      <c r="B167" s="13">
         <v>42067</v>
       </c>
-      <c r="C167" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D167" s="9" t="str">
+      <c r="C167" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D167" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -6979,16 +6976,16 @@
       </c>
     </row>
     <row r="168" spans="1:7">
-      <c r="A168" s="12">
+      <c r="A168" s="13">
         <v>42064</v>
       </c>
-      <c r="B168" s="8">
+      <c r="B168" s="13">
         <v>42095</v>
       </c>
-      <c r="C168" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D168" s="9" t="str">
+      <c r="C168" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D168" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7003,16 +7000,16 @@
       </c>
     </row>
     <row r="169" spans="1:7">
-      <c r="A169" s="12">
+      <c r="A169" s="13">
         <v>42095</v>
       </c>
-      <c r="B169" s="8">
+      <c r="B169" s="13">
         <v>42130</v>
       </c>
-      <c r="C169" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D169" s="9" t="str">
+      <c r="C169" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D169" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7027,16 +7024,16 @@
       </c>
     </row>
     <row r="170" spans="1:7">
-      <c r="A170" s="12">
+      <c r="A170" s="13">
         <v>42125</v>
       </c>
-      <c r="B170" s="8">
+      <c r="B170" s="13">
         <v>42158</v>
       </c>
-      <c r="C170" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D170" s="9" t="str">
+      <c r="C170" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D170" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7051,16 +7048,16 @@
       </c>
     </row>
     <row r="171" spans="1:7">
-      <c r="A171" s="12">
+      <c r="A171" s="13">
         <v>42156</v>
       </c>
-      <c r="B171" s="8">
+      <c r="B171" s="13">
         <v>42186</v>
       </c>
-      <c r="C171" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D171" s="9" t="str">
+      <c r="C171" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D171" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7075,16 +7072,16 @@
       </c>
     </row>
     <row r="172" spans="1:7">
-      <c r="A172" s="12">
+      <c r="A172" s="13">
         <v>42186</v>
       </c>
-      <c r="B172" s="8">
+      <c r="B172" s="13">
         <v>42221</v>
       </c>
-      <c r="C172" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D172" s="9" t="str">
+      <c r="C172" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D172" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7099,16 +7096,16 @@
       </c>
     </row>
     <row r="173" spans="1:7">
-      <c r="A173" s="12">
+      <c r="A173" s="13">
         <v>42217</v>
       </c>
-      <c r="B173" s="8">
+      <c r="B173" s="13">
         <v>42249</v>
       </c>
-      <c r="C173" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D173" s="9" t="str">
+      <c r="C173" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D173" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7123,16 +7120,16 @@
       </c>
     </row>
     <row r="174" spans="1:7">
-      <c r="A174" s="12">
+      <c r="A174" s="13">
         <v>42248</v>
       </c>
-      <c r="B174" s="8">
+      <c r="B174" s="13">
         <v>42277</v>
       </c>
-      <c r="C174" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D174" s="9" t="str">
+      <c r="C174" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D174" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7147,16 +7144,16 @@
       </c>
     </row>
     <row r="175" spans="1:7">
-      <c r="A175" s="12">
+      <c r="A175" s="13">
         <v>42278</v>
       </c>
-      <c r="B175" s="8">
+      <c r="B175" s="13">
         <v>42312</v>
       </c>
-      <c r="C175" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D175" s="9" t="str">
+      <c r="C175" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D175" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -7171,16 +7168,16 @@
       </c>
     </row>
     <row r="176" spans="1:7">
-      <c r="A176" s="12">
+      <c r="A176" s="13">
         <v>42309</v>
       </c>
-      <c r="B176" s="8">
+      <c r="B176" s="13">
         <v>42340</v>
       </c>
-      <c r="C176" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D176" s="9" t="str">
+      <c r="C176" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D176" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -7195,16 +7192,16 @@
       </c>
     </row>
     <row r="177" spans="1:7">
-      <c r="A177" s="12">
+      <c r="A177" s="13">
         <v>42339</v>
       </c>
-      <c r="B177" s="8">
+      <c r="B177" s="13">
         <v>42375</v>
       </c>
-      <c r="C177" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D177" s="9" t="str">
+      <c r="C177" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D177" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -7219,16 +7216,16 @@
       </c>
     </row>
     <row r="178" spans="1:7">
-      <c r="A178" s="12">
+      <c r="A178" s="13">
         <v>42370</v>
       </c>
-      <c r="B178" s="8">
+      <c r="B178" s="13">
         <v>42403</v>
       </c>
-      <c r="C178" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D178" s="9" t="str">
+      <c r="C178" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D178" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -7243,16 +7240,16 @@
       </c>
     </row>
     <row r="179" spans="1:7">
-      <c r="A179" s="12">
+      <c r="A179" s="13">
         <v>42401</v>
       </c>
-      <c r="B179" s="8">
+      <c r="B179" s="13">
         <v>42431</v>
       </c>
-      <c r="C179" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D179" s="9" t="str">
+      <c r="C179" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D179" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -7267,16 +7264,16 @@
       </c>
     </row>
     <row r="180" spans="1:7">
-      <c r="A180" s="12">
+      <c r="A180" s="13">
         <v>42430</v>
       </c>
-      <c r="B180" s="8">
+      <c r="B180" s="13">
         <v>42459</v>
       </c>
-      <c r="C180" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D180" s="9" t="str">
+      <c r="C180" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D180" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7291,16 +7288,16 @@
       </c>
     </row>
     <row r="181" spans="1:7">
-      <c r="A181" s="12">
+      <c r="A181" s="13">
         <v>42461</v>
       </c>
-      <c r="B181" s="8">
+      <c r="B181" s="13">
         <v>42494</v>
       </c>
-      <c r="C181" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D181" s="9" t="str">
+      <c r="C181" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D181" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7315,16 +7312,16 @@
       </c>
     </row>
     <row r="182" spans="1:7">
-      <c r="A182" s="12">
+      <c r="A182" s="13">
         <v>42491</v>
       </c>
-      <c r="B182" s="8">
+      <c r="B182" s="13">
         <v>42523</v>
       </c>
-      <c r="C182" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D182" s="9" t="str">
+      <c r="C182" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D182" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7339,16 +7336,16 @@
       </c>
     </row>
     <row r="183" spans="1:7">
-      <c r="A183" s="12">
+      <c r="A183" s="13">
         <v>42522</v>
       </c>
-      <c r="B183" s="8">
+      <c r="B183" s="13">
         <v>42558</v>
       </c>
-      <c r="C183" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D183" s="9" t="str">
+      <c r="C183" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D183" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7363,16 +7360,16 @@
       </c>
     </row>
     <row r="184" spans="1:7">
-      <c r="A184" s="12">
+      <c r="A184" s="13">
         <v>42552</v>
       </c>
-      <c r="B184" s="8">
+      <c r="B184" s="13">
         <v>42585</v>
       </c>
-      <c r="C184" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D184" s="9" t="str">
+      <c r="C184" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D184" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7387,16 +7384,16 @@
       </c>
     </row>
     <row r="185" spans="1:7">
-      <c r="A185" s="12">
+      <c r="A185" s="13">
         <v>42583</v>
       </c>
-      <c r="B185" s="8">
+      <c r="B185" s="13">
         <v>42613</v>
       </c>
-      <c r="C185" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D185" s="9" t="str">
+      <c r="C185" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D185" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7411,16 +7408,16 @@
       </c>
     </row>
     <row r="186" spans="1:7">
-      <c r="A186" s="12">
+      <c r="A186" s="13">
         <v>42614</v>
       </c>
-      <c r="B186" s="8">
+      <c r="B186" s="13">
         <v>42648</v>
       </c>
-      <c r="C186" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D186" s="9" t="str">
+      <c r="C186" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D186" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7435,16 +7432,16 @@
       </c>
     </row>
     <row r="187" spans="1:7">
-      <c r="A187" s="12">
+      <c r="A187" s="13">
         <v>42644</v>
       </c>
-      <c r="B187" s="8">
+      <c r="B187" s="13">
         <v>42676</v>
       </c>
-      <c r="C187" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D187" s="9" t="str">
+      <c r="C187" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D187" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7459,16 +7456,16 @@
       </c>
     </row>
     <row r="188" spans="1:7">
-      <c r="A188" s="12">
+      <c r="A188" s="13">
         <v>42675</v>
       </c>
-      <c r="B188" s="8">
+      <c r="B188" s="13">
         <v>42704</v>
       </c>
-      <c r="C188" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D188" s="9" t="str">
+      <c r="C188" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D188" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -7483,16 +7480,16 @@
       </c>
     </row>
     <row r="189" spans="1:7">
-      <c r="A189" s="12">
+      <c r="A189" s="13">
         <v>42705</v>
       </c>
-      <c r="B189" s="8">
+      <c r="B189" s="13">
         <v>42740</v>
       </c>
-      <c r="C189" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D189" s="9" t="str">
+      <c r="C189" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D189" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -7507,16 +7504,16 @@
       </c>
     </row>
     <row r="190" spans="1:7">
-      <c r="A190" s="12">
+      <c r="A190" s="13">
         <v>42736</v>
       </c>
-      <c r="B190" s="8">
+      <c r="B190" s="13">
         <v>42767</v>
       </c>
-      <c r="C190" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D190" s="9" t="str">
+      <c r="C190" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D190" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -7531,16 +7528,16 @@
       </c>
     </row>
     <row r="191" spans="1:7">
-      <c r="A191" s="12">
+      <c r="A191" s="13">
         <v>42767</v>
       </c>
-      <c r="B191" s="8">
+      <c r="B191" s="13">
         <v>42802</v>
       </c>
-      <c r="C191" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D191" s="9" t="str">
+      <c r="C191" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D191" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
@@ -7555,16 +7552,16 @@
       </c>
     </row>
     <row r="192" spans="1:7">
-      <c r="A192" s="12">
+      <c r="A192" s="13">
         <v>42795</v>
       </c>
-      <c r="B192" s="8">
+      <c r="B192" s="13">
         <v>42830</v>
       </c>
-      <c r="C192" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D192" s="9" t="str">
+      <c r="C192" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D192" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7579,16 +7576,16 @@
       </c>
     </row>
     <row r="193" spans="1:7">
-      <c r="A193" s="12">
+      <c r="A193" s="13">
         <v>42826</v>
       </c>
-      <c r="B193" s="8">
+      <c r="B193" s="13">
         <v>42858</v>
       </c>
-      <c r="C193" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D193" s="9" t="str">
+      <c r="C193" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D193" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7603,16 +7600,16 @@
       </c>
     </row>
     <row r="194" spans="1:7">
-      <c r="A194" s="12">
+      <c r="A194" s="13">
         <v>42856</v>
       </c>
-      <c r="B194" s="8">
+      <c r="B194" s="13">
         <v>42887</v>
       </c>
-      <c r="C194" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D194" s="9" t="str">
+      <c r="C194" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D194" s="7" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
@@ -7627,16 +7624,16 @@
       </c>
     </row>
     <row r="195" spans="1:7">
-      <c r="A195" s="12">
+      <c r="A195" s="13">
         <v>42887</v>
       </c>
-      <c r="B195" s="8">
+      <c r="B195" s="13">
         <v>42922</v>
       </c>
-      <c r="C195" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D195" s="9" t="str">
+      <c r="C195" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D195" s="7" t="str">
         <f t="shared" ref="D195:D258" si="3">IF(
  AND(
   B195 &gt;= IF(
@@ -7666,16 +7663,16 @@
       </c>
     </row>
     <row r="196" spans="1:7">
-      <c r="A196" s="12">
+      <c r="A196" s="13">
         <v>42917</v>
       </c>
-      <c r="B196" s="8">
+      <c r="B196" s="13">
         <v>42949</v>
       </c>
-      <c r="C196" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D196" s="9" t="str">
+      <c r="C196" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D196" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -7690,16 +7687,16 @@
       </c>
     </row>
     <row r="197" spans="1:7">
-      <c r="A197" s="12">
+      <c r="A197" s="13">
         <v>42948</v>
       </c>
-      <c r="B197" s="8">
+      <c r="B197" s="13">
         <v>42977</v>
       </c>
-      <c r="C197" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D197" s="9" t="str">
+      <c r="C197" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D197" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -7714,16 +7711,16 @@
       </c>
     </row>
     <row r="198" spans="1:7">
-      <c r="A198" s="12">
+      <c r="A198" s="13">
         <v>42979</v>
       </c>
-      <c r="B198" s="8">
+      <c r="B198" s="13">
         <v>43012</v>
       </c>
-      <c r="C198" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D198" s="9" t="str">
+      <c r="C198" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D198" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -7738,16 +7735,16 @@
       </c>
     </row>
     <row r="199" spans="1:7">
-      <c r="A199" s="12">
+      <c r="A199" s="13">
         <v>43009</v>
       </c>
-      <c r="B199" s="8">
+      <c r="B199" s="13">
         <v>43040</v>
       </c>
-      <c r="C199" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D199" s="9" t="str">
+      <c r="C199" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D199" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -7762,16 +7759,16 @@
       </c>
     </row>
     <row r="200" spans="1:7">
-      <c r="A200" s="12">
+      <c r="A200" s="13">
         <v>43040</v>
       </c>
-      <c r="B200" s="8">
+      <c r="B200" s="13">
         <v>43075</v>
       </c>
-      <c r="C200" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D200" s="9" t="str">
+      <c r="C200" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D200" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -7786,16 +7783,16 @@
       </c>
     </row>
     <row r="201" spans="1:7">
-      <c r="A201" s="12">
+      <c r="A201" s="13">
         <v>43070</v>
       </c>
-      <c r="B201" s="8">
+      <c r="B201" s="13">
         <v>43104</v>
       </c>
-      <c r="C201" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D201" s="9" t="str">
+      <c r="C201" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D201" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -7810,16 +7807,16 @@
       </c>
     </row>
     <row r="202" spans="1:7">
-      <c r="A202" s="12">
+      <c r="A202" s="13">
         <v>43101</v>
       </c>
-      <c r="B202" s="8">
+      <c r="B202" s="13">
         <v>43131</v>
       </c>
-      <c r="C202" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D202" s="9" t="str">
+      <c r="C202" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D202" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -7834,16 +7831,16 @@
       </c>
     </row>
     <row r="203" spans="1:7">
-      <c r="A203" s="12">
+      <c r="A203" s="13">
         <v>43132</v>
       </c>
-      <c r="B203" s="8">
+      <c r="B203" s="13">
         <v>43166</v>
       </c>
-      <c r="C203" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D203" s="9" t="str">
+      <c r="C203" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D203" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -7858,16 +7855,16 @@
       </c>
     </row>
     <row r="204" spans="1:7">
-      <c r="A204" s="12">
+      <c r="A204" s="13">
         <v>43160</v>
       </c>
-      <c r="B204" s="8">
+      <c r="B204" s="13">
         <v>43194</v>
       </c>
-      <c r="C204" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D204" s="9" t="str">
+      <c r="C204" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D204" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -7882,16 +7879,16 @@
       </c>
     </row>
     <row r="205" spans="1:7">
-      <c r="A205" s="12">
+      <c r="A205" s="13">
         <v>43191</v>
       </c>
-      <c r="B205" s="8">
+      <c r="B205" s="13">
         <v>43222</v>
       </c>
-      <c r="C205" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D205" s="9" t="str">
+      <c r="C205" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D205" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -7906,16 +7903,16 @@
       </c>
     </row>
     <row r="206" spans="1:7">
-      <c r="A206" s="12">
+      <c r="A206" s="13">
         <v>43221</v>
       </c>
-      <c r="B206" s="8">
+      <c r="B206" s="13">
         <v>43250</v>
       </c>
-      <c r="C206" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D206" s="9" t="str">
+      <c r="C206" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D206" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -7930,16 +7927,16 @@
       </c>
     </row>
     <row r="207" spans="1:7">
-      <c r="A207" s="12">
+      <c r="A207" s="13">
         <v>43252</v>
       </c>
-      <c r="B207" s="8">
+      <c r="B207" s="13">
         <v>43286</v>
       </c>
-      <c r="C207" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D207" s="9" t="str">
+      <c r="C207" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D207" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -7954,16 +7951,16 @@
       </c>
     </row>
     <row r="208" spans="1:7">
-      <c r="A208" s="12">
+      <c r="A208" s="13">
         <v>43282</v>
       </c>
-      <c r="B208" s="8">
+      <c r="B208" s="13">
         <v>43313</v>
       </c>
-      <c r="C208" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D208" s="9" t="str">
+      <c r="C208" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D208" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -7978,16 +7975,16 @@
       </c>
     </row>
     <row r="209" spans="1:7">
-      <c r="A209" s="12">
+      <c r="A209" s="13">
         <v>43313</v>
       </c>
-      <c r="B209" s="8">
+      <c r="B209" s="13">
         <v>43349</v>
       </c>
-      <c r="C209" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D209" s="9" t="str">
+      <c r="C209" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D209" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8002,16 +7999,16 @@
       </c>
     </row>
     <row r="210" spans="1:7">
-      <c r="A210" s="12">
+      <c r="A210" s="13">
         <v>43344</v>
       </c>
-      <c r="B210" s="8">
+      <c r="B210" s="13">
         <v>43376</v>
       </c>
-      <c r="C210" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D210" s="9" t="str">
+      <c r="C210" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D210" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8026,16 +8023,16 @@
       </c>
     </row>
     <row r="211" spans="1:7">
-      <c r="A211" s="12">
+      <c r="A211" s="13">
         <v>43374</v>
       </c>
-      <c r="B211" s="8">
+      <c r="B211" s="13">
         <v>43404</v>
       </c>
-      <c r="C211" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D211" s="9" t="str">
+      <c r="C211" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D211" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8050,16 +8047,16 @@
       </c>
     </row>
     <row r="212" spans="1:7">
-      <c r="A212" s="12">
+      <c r="A212" s="13">
         <v>43405</v>
       </c>
-      <c r="B212" s="8">
+      <c r="B212" s="13">
         <v>43440</v>
       </c>
-      <c r="C212" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D212" s="9" t="str">
+      <c r="C212" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D212" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8074,16 +8071,16 @@
       </c>
     </row>
     <row r="213" spans="1:7">
-      <c r="A213" s="12">
+      <c r="A213" s="13">
         <v>43435</v>
       </c>
-      <c r="B213" s="8">
+      <c r="B213" s="13">
         <v>43468</v>
       </c>
-      <c r="C213" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D213" s="9" t="str">
+      <c r="C213" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D213" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8098,16 +8095,16 @@
       </c>
     </row>
     <row r="214" spans="1:7">
-      <c r="A214" s="12">
+      <c r="A214" s="13">
         <v>43466</v>
       </c>
-      <c r="B214" s="8">
+      <c r="B214" s="13">
         <v>43495</v>
       </c>
-      <c r="C214" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D214" s="9" t="str">
+      <c r="C214" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D214" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8122,16 +8119,16 @@
       </c>
     </row>
     <row r="215" spans="1:7">
-      <c r="A215" s="12">
+      <c r="A215" s="13">
         <v>43497</v>
       </c>
-      <c r="B215" s="8">
+      <c r="B215" s="13">
         <v>43530</v>
       </c>
-      <c r="C215" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D215" s="9" t="str">
+      <c r="C215" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D215" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8146,16 +8143,16 @@
       </c>
     </row>
     <row r="216" spans="1:7">
-      <c r="A216" s="12">
+      <c r="A216" s="13">
         <v>43525</v>
       </c>
-      <c r="B216" s="8">
+      <c r="B216" s="13">
         <v>43558</v>
       </c>
-      <c r="C216" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D216" s="9" t="str">
+      <c r="C216" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D216" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8170,16 +8167,16 @@
       </c>
     </row>
     <row r="217" spans="1:7">
-      <c r="A217" s="12">
+      <c r="A217" s="13">
         <v>43556</v>
       </c>
-      <c r="B217" s="8">
+      <c r="B217" s="13">
         <v>43586</v>
       </c>
-      <c r="C217" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D217" s="9" t="str">
+      <c r="C217" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D217" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8194,16 +8191,16 @@
       </c>
     </row>
     <row r="218" spans="1:7">
-      <c r="A218" s="12">
+      <c r="A218" s="13">
         <v>43586</v>
       </c>
-      <c r="B218" s="8">
+      <c r="B218" s="13">
         <v>43621</v>
       </c>
-      <c r="C218" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D218" s="9" t="str">
+      <c r="C218" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D218" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8218,16 +8215,16 @@
       </c>
     </row>
     <row r="219" spans="1:7">
-      <c r="A219" s="12">
+      <c r="A219" s="13">
         <v>43617</v>
       </c>
-      <c r="B219" s="8">
+      <c r="B219" s="13">
         <v>43649</v>
       </c>
-      <c r="C219" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D219" s="9" t="str">
+      <c r="C219" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D219" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8242,16 +8239,16 @@
       </c>
     </row>
     <row r="220" spans="1:7">
-      <c r="A220" s="12">
+      <c r="A220" s="13">
         <v>43647</v>
       </c>
-      <c r="B220" s="8">
+      <c r="B220" s="13">
         <v>43677</v>
       </c>
-      <c r="C220" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D220" s="9" t="str">
+      <c r="C220" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D220" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8266,16 +8263,16 @@
       </c>
     </row>
     <row r="221" spans="1:7">
-      <c r="A221" s="12">
+      <c r="A221" s="13">
         <v>43678</v>
       </c>
-      <c r="B221" s="8">
+      <c r="B221" s="13">
         <v>43713</v>
       </c>
-      <c r="C221" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D221" s="9" t="str">
+      <c r="C221" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D221" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8290,16 +8287,16 @@
       </c>
     </row>
     <row r="222" spans="1:7">
-      <c r="A222" s="12">
+      <c r="A222" s="13">
         <v>43709</v>
       </c>
-      <c r="B222" s="8">
+      <c r="B222" s="13">
         <v>43740</v>
       </c>
-      <c r="C222" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D222" s="9" t="str">
+      <c r="C222" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D222" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8314,16 +8311,16 @@
       </c>
     </row>
     <row r="223" spans="1:7">
-      <c r="A223" s="12">
+      <c r="A223" s="13">
         <v>43739</v>
       </c>
-      <c r="B223" s="8">
+      <c r="B223" s="13">
         <v>43768</v>
       </c>
-      <c r="C223" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D223" s="9" t="str">
+      <c r="C223" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D223" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8338,16 +8335,16 @@
       </c>
     </row>
     <row r="224" spans="1:7">
-      <c r="A224" s="12">
+      <c r="A224" s="13">
         <v>43770</v>
       </c>
-      <c r="B224" s="8">
+      <c r="B224" s="13">
         <v>43803</v>
       </c>
-      <c r="C224" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D224" s="9" t="str">
+      <c r="C224" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D224" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8362,16 +8359,16 @@
       </c>
     </row>
     <row r="225" spans="1:7">
-      <c r="A225" s="12">
+      <c r="A225" s="13">
         <v>43800</v>
       </c>
-      <c r="B225" s="8">
+      <c r="B225" s="13">
         <v>43838</v>
       </c>
-      <c r="C225" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D225" s="9" t="str">
+      <c r="C225" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D225" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8386,16 +8383,16 @@
       </c>
     </row>
     <row r="226" spans="1:7">
-      <c r="A226" s="12">
+      <c r="A226" s="13">
         <v>43831</v>
       </c>
-      <c r="B226" s="8">
+      <c r="B226" s="13">
         <v>43866</v>
       </c>
-      <c r="C226" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D226" s="9" t="str">
+      <c r="C226" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D226" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8410,16 +8407,16 @@
       </c>
     </row>
     <row r="227" spans="1:7">
-      <c r="A227" s="12">
+      <c r="A227" s="13">
         <v>43862</v>
       </c>
-      <c r="B227" s="8">
+      <c r="B227" s="13">
         <v>43894</v>
       </c>
-      <c r="C227" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D227" s="9" t="str">
+      <c r="C227" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D227" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8434,16 +8431,16 @@
       </c>
     </row>
     <row r="228" spans="1:7">
-      <c r="A228" s="12">
+      <c r="A228" s="13">
         <v>43891</v>
       </c>
-      <c r="B228" s="8">
+      <c r="B228" s="13">
         <v>43922</v>
       </c>
-      <c r="C228" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D228" s="9" t="str">
+      <c r="C228" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D228" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8458,16 +8455,16 @@
       </c>
     </row>
     <row r="229" spans="1:7">
-      <c r="A229" s="12">
+      <c r="A229" s="13">
         <v>43922</v>
       </c>
-      <c r="B229" s="8">
+      <c r="B229" s="13">
         <v>43957</v>
       </c>
-      <c r="C229" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D229" s="9" t="str">
+      <c r="C229" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D229" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8482,16 +8479,16 @@
       </c>
     </row>
     <row r="230" spans="1:7">
-      <c r="A230" s="12">
+      <c r="A230" s="13">
         <v>43952</v>
       </c>
-      <c r="B230" s="8">
+      <c r="B230" s="13">
         <v>43985</v>
       </c>
-      <c r="C230" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D230" s="9" t="str">
+      <c r="C230" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D230" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8506,16 +8503,16 @@
       </c>
     </row>
     <row r="231" spans="1:7">
-      <c r="A231" s="12">
+      <c r="A231" s="13">
         <v>43983</v>
       </c>
-      <c r="B231" s="8">
+      <c r="B231" s="13">
         <v>44013</v>
       </c>
-      <c r="C231" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D231" s="9" t="str">
+      <c r="C231" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D231" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8530,16 +8527,16 @@
       </c>
     </row>
     <row r="232" spans="1:7">
-      <c r="A232" s="12">
+      <c r="A232" s="13">
         <v>44013</v>
       </c>
-      <c r="B232" s="8">
+      <c r="B232" s="13">
         <v>44048</v>
       </c>
-      <c r="C232" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D232" s="9" t="str">
+      <c r="C232" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D232" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8554,16 +8551,16 @@
       </c>
     </row>
     <row r="233" spans="1:7">
-      <c r="A233" s="12">
+      <c r="A233" s="13">
         <v>44044</v>
       </c>
-      <c r="B233" s="8">
+      <c r="B233" s="13">
         <v>44076</v>
       </c>
-      <c r="C233" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D233" s="9" t="str">
+      <c r="C233" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D233" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8578,16 +8575,16 @@
       </c>
     </row>
     <row r="234" spans="1:7">
-      <c r="A234" s="12">
+      <c r="A234" s="13">
         <v>44075</v>
       </c>
-      <c r="B234" s="8">
+      <c r="B234" s="13">
         <v>44104</v>
       </c>
-      <c r="C234" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D234" s="9" t="str">
+      <c r="C234" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D234" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8602,16 +8599,16 @@
       </c>
     </row>
     <row r="235" spans="1:7">
-      <c r="A235" s="12">
+      <c r="A235" s="13">
         <v>44105</v>
       </c>
-      <c r="B235" s="8">
+      <c r="B235" s="13">
         <v>44139</v>
       </c>
-      <c r="C235" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D235" s="9" t="str">
+      <c r="C235" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D235" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8626,16 +8623,16 @@
       </c>
     </row>
     <row r="236" spans="1:7">
-      <c r="A236" s="12">
+      <c r="A236" s="13">
         <v>44136</v>
       </c>
-      <c r="B236" s="8">
+      <c r="B236" s="13">
         <v>44167</v>
       </c>
-      <c r="C236" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D236" s="9" t="str">
+      <c r="C236" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D236" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8650,16 +8647,16 @@
       </c>
     </row>
     <row r="237" spans="1:7">
-      <c r="A237" s="12">
+      <c r="A237" s="13">
         <v>44166</v>
       </c>
-      <c r="B237" s="8">
+      <c r="B237" s="13">
         <v>44202</v>
       </c>
-      <c r="C237" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D237" s="9" t="str">
+      <c r="C237" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D237" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8674,16 +8671,16 @@
       </c>
     </row>
     <row r="238" spans="1:7">
-      <c r="A238" s="12">
+      <c r="A238" s="13">
         <v>44197</v>
       </c>
-      <c r="B238" s="8">
+      <c r="B238" s="13">
         <v>44230</v>
       </c>
-      <c r="C238" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D238" s="9" t="str">
+      <c r="C238" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D238" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8698,16 +8695,16 @@
       </c>
     </row>
     <row r="239" spans="1:7">
-      <c r="A239" s="12">
+      <c r="A239" s="13">
         <v>44228</v>
       </c>
-      <c r="B239" s="8">
+      <c r="B239" s="13">
         <v>44258</v>
       </c>
-      <c r="C239" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D239" s="9" t="str">
+      <c r="C239" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D239" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8722,16 +8719,16 @@
       </c>
     </row>
     <row r="240" spans="1:7">
-      <c r="A240" s="12">
+      <c r="A240" s="13">
         <v>44256</v>
       </c>
-      <c r="B240" s="8">
+      <c r="B240" s="13">
         <v>44286</v>
       </c>
-      <c r="C240" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D240" s="9" t="str">
+      <c r="C240" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D240" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8746,16 +8743,16 @@
       </c>
     </row>
     <row r="241" spans="1:7">
-      <c r="A241" s="12">
+      <c r="A241" s="13">
         <v>44287</v>
       </c>
-      <c r="B241" s="8">
+      <c r="B241" s="13">
         <v>44321</v>
       </c>
-      <c r="C241" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D241" s="9" t="str">
+      <c r="C241" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D241" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8770,16 +8767,16 @@
       </c>
     </row>
     <row r="242" spans="1:7">
-      <c r="A242" s="12">
+      <c r="A242" s="13">
         <v>44317</v>
       </c>
-      <c r="B242" s="8">
+      <c r="B242" s="13">
         <v>44350</v>
       </c>
-      <c r="C242" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D242" s="9" t="str">
+      <c r="C242" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D242" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8794,16 +8791,16 @@
       </c>
     </row>
     <row r="243" spans="1:7">
-      <c r="A243" s="12">
+      <c r="A243" s="13">
         <v>44348</v>
       </c>
-      <c r="B243" s="8">
+      <c r="B243" s="13">
         <v>44377</v>
       </c>
-      <c r="C243" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D243" s="9" t="str">
+      <c r="C243" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D243" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8818,16 +8815,16 @@
       </c>
     </row>
     <row r="244" spans="1:7">
-      <c r="A244" s="12">
+      <c r="A244" s="13">
         <v>44378</v>
       </c>
-      <c r="B244" s="8">
+      <c r="B244" s="13">
         <v>44412</v>
       </c>
-      <c r="C244" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D244" s="9" t="str">
+      <c r="C244" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D244" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8842,16 +8839,16 @@
       </c>
     </row>
     <row r="245" spans="1:7">
-      <c r="A245" s="12">
+      <c r="A245" s="13">
         <v>44409</v>
       </c>
-      <c r="B245" s="8">
+      <c r="B245" s="13">
         <v>44440</v>
       </c>
-      <c r="C245" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D245" s="9" t="str">
+      <c r="C245" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D245" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8866,16 +8863,16 @@
       </c>
     </row>
     <row r="246" spans="1:7">
-      <c r="A246" s="12">
+      <c r="A246" s="13">
         <v>44440</v>
       </c>
-      <c r="B246" s="8">
+      <c r="B246" s="13">
         <v>44475</v>
       </c>
-      <c r="C246" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D246" s="9" t="str">
+      <c r="C246" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D246" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8890,16 +8887,16 @@
       </c>
     </row>
     <row r="247" spans="1:7">
-      <c r="A247" s="12">
+      <c r="A247" s="13">
         <v>44470</v>
       </c>
-      <c r="B247" s="8">
+      <c r="B247" s="13">
         <v>44503</v>
       </c>
-      <c r="C247" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D247" s="9" t="str">
+      <c r="C247" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D247" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -8914,16 +8911,16 @@
       </c>
     </row>
     <row r="248" spans="1:7">
-      <c r="A248" s="12">
+      <c r="A248" s="13">
         <v>44501</v>
       </c>
-      <c r="B248" s="8">
+      <c r="B248" s="13">
         <v>44531</v>
       </c>
-      <c r="C248" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D248" s="9" t="str">
+      <c r="C248" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D248" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8938,16 +8935,16 @@
       </c>
     </row>
     <row r="249" spans="1:7">
-      <c r="A249" s="12">
+      <c r="A249" s="13">
         <v>44531</v>
       </c>
-      <c r="B249" s="8">
+      <c r="B249" s="13">
         <v>44566</v>
       </c>
-      <c r="C249" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D249" s="9" t="str">
+      <c r="C249" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D249" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8962,16 +8959,16 @@
       </c>
     </row>
     <row r="250" spans="1:7">
-      <c r="A250" s="12">
+      <c r="A250" s="13">
         <v>44562</v>
       </c>
-      <c r="B250" s="8">
+      <c r="B250" s="13">
         <v>44594</v>
       </c>
-      <c r="C250" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D250" s="9" t="str">
+      <c r="C250" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D250" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -8986,16 +8983,16 @@
       </c>
     </row>
     <row r="251" spans="1:7">
-      <c r="A251" s="12">
+      <c r="A251" s="13">
         <v>44593</v>
       </c>
-      <c r="B251" s="8">
+      <c r="B251" s="13">
         <v>44622</v>
       </c>
-      <c r="C251" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D251" s="9" t="str">
+      <c r="C251" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D251" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -9010,16 +9007,16 @@
       </c>
     </row>
     <row r="252" spans="1:7">
-      <c r="A252" s="12">
+      <c r="A252" s="13">
         <v>44621</v>
       </c>
-      <c r="B252" s="8">
+      <c r="B252" s="13">
         <v>44650</v>
       </c>
-      <c r="C252" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D252" s="9" t="str">
+      <c r="C252" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D252" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -9034,16 +9031,16 @@
       </c>
     </row>
     <row r="253" spans="1:7">
-      <c r="A253" s="12">
+      <c r="A253" s="13">
         <v>44652</v>
       </c>
-      <c r="B253" s="8">
+      <c r="B253" s="13">
         <v>44685</v>
       </c>
-      <c r="C253" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D253" s="9" t="str">
+      <c r="C253" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D253" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -9058,16 +9055,16 @@
       </c>
     </row>
     <row r="254" spans="1:7">
-      <c r="A254" s="12">
+      <c r="A254" s="13">
         <v>44682</v>
       </c>
-      <c r="B254" s="8">
+      <c r="B254" s="13">
         <v>44714</v>
       </c>
-      <c r="C254" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D254" s="9" t="str">
+      <c r="C254" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D254" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -9082,16 +9079,16 @@
       </c>
     </row>
     <row r="255" spans="1:7">
-      <c r="A255" s="12">
+      <c r="A255" s="13">
         <v>44774</v>
       </c>
-      <c r="B255" s="8">
+      <c r="B255" s="13">
         <v>44804</v>
       </c>
-      <c r="C255" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D255" s="9" t="str">
+      <c r="C255" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D255" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -9106,16 +9103,16 @@
       </c>
     </row>
     <row r="256" spans="1:7">
-      <c r="A256" s="12">
+      <c r="A256" s="13">
         <v>44805</v>
       </c>
-      <c r="B256" s="8">
+      <c r="B256" s="13">
         <v>44839</v>
       </c>
-      <c r="C256" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D256" s="9" t="str">
+      <c r="C256" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D256" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -9130,16 +9127,16 @@
       </c>
     </row>
     <row r="257" spans="1:7">
-      <c r="A257" s="12">
+      <c r="A257" s="13">
         <v>44835</v>
       </c>
-      <c r="B257" s="8">
+      <c r="B257" s="13">
         <v>44867</v>
       </c>
-      <c r="C257" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D257" s="9" t="str">
+      <c r="C257" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D257" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
@@ -9154,16 +9151,16 @@
       </c>
     </row>
     <row r="258" spans="1:7">
-      <c r="A258" s="12">
+      <c r="A258" s="13">
         <v>44866</v>
       </c>
-      <c r="B258" s="8">
+      <c r="B258" s="13">
         <v>44895</v>
       </c>
-      <c r="C258" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D258" s="9" t="str">
+      <c r="C258" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D258" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
@@ -9178,16 +9175,16 @@
       </c>
     </row>
     <row r="259" spans="1:7">
-      <c r="A259" s="12">
+      <c r="A259" s="13">
         <v>44896</v>
       </c>
-      <c r="B259" s="8">
+      <c r="B259" s="13">
         <v>44931</v>
       </c>
-      <c r="C259" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D259" s="9" t="str">
+      <c r="C259" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D259" s="7" t="str">
         <f t="shared" ref="D259:D299" si="4">IF(
  AND(
   B259 &gt;= IF(
@@ -9217,16 +9214,16 @@
       </c>
     </row>
     <row r="260" spans="1:7">
-      <c r="A260" s="12">
+      <c r="A260" s="13">
         <v>44927</v>
       </c>
-      <c r="B260" s="8">
+      <c r="B260" s="13">
         <v>44958</v>
       </c>
-      <c r="C260" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D260" s="9" t="str">
+      <c r="C260" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D260" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -9241,16 +9238,16 @@
       </c>
     </row>
     <row r="261" spans="1:7">
-      <c r="A261" s="12">
+      <c r="A261" s="13">
         <v>44958</v>
       </c>
-      <c r="B261" s="8">
+      <c r="B261" s="13">
         <v>44993</v>
       </c>
-      <c r="C261" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D261" s="9" t="str">
+      <c r="C261" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D261" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -9265,16 +9262,16 @@
       </c>
     </row>
     <row r="262" spans="1:7">
-      <c r="A262" s="12">
+      <c r="A262" s="13">
         <v>44986</v>
       </c>
-      <c r="B262" s="8">
+      <c r="B262" s="13">
         <v>45021</v>
       </c>
-      <c r="C262" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D262" s="9" t="str">
+      <c r="C262" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D262" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9289,16 +9286,16 @@
       </c>
     </row>
     <row r="263" spans="1:7">
-      <c r="A263" s="12">
+      <c r="A263" s="13">
         <v>45017</v>
       </c>
-      <c r="B263" s="8">
+      <c r="B263" s="13">
         <v>45049</v>
       </c>
-      <c r="C263" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D263" s="9" t="str">
+      <c r="C263" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D263" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9313,16 +9310,16 @@
       </c>
     </row>
     <row r="264" spans="1:7">
-      <c r="A264" s="12">
+      <c r="A264" s="13">
         <v>45047</v>
       </c>
-      <c r="B264" s="8">
+      <c r="B264" s="13">
         <v>45078</v>
       </c>
-      <c r="C264" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D264" s="9" t="str">
+      <c r="C264" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D264" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9337,16 +9334,16 @@
       </c>
     </row>
     <row r="265" spans="1:7">
-      <c r="A265" s="12">
+      <c r="A265" s="13">
         <v>45078</v>
       </c>
-      <c r="B265" s="8">
+      <c r="B265" s="13">
         <v>45113</v>
       </c>
-      <c r="C265" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D265" s="9" t="str">
+      <c r="C265" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D265" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9361,16 +9358,16 @@
       </c>
     </row>
     <row r="266" spans="1:7">
-      <c r="A266" s="12">
+      <c r="A266" s="13">
         <v>45108</v>
       </c>
-      <c r="B266" s="8">
+      <c r="B266" s="13">
         <v>45140</v>
       </c>
-      <c r="C266" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D266" s="9" t="str">
+      <c r="C266" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D266" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9385,16 +9382,16 @@
       </c>
     </row>
     <row r="267" spans="1:7">
-      <c r="A267" s="12">
+      <c r="A267" s="13">
         <v>45139</v>
       </c>
-      <c r="B267" s="8">
+      <c r="B267" s="13">
         <v>45168</v>
       </c>
-      <c r="C267" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D267" s="9" t="str">
+      <c r="C267" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D267" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9409,16 +9406,16 @@
       </c>
     </row>
     <row r="268" spans="1:7">
-      <c r="A268" s="12">
+      <c r="A268" s="13">
         <v>45170</v>
       </c>
-      <c r="B268" s="8">
+      <c r="B268" s="13">
         <v>45203</v>
       </c>
-      <c r="C268" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D268" s="9" t="str">
+      <c r="C268" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D268" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9433,16 +9430,16 @@
       </c>
     </row>
     <row r="269" spans="1:7">
-      <c r="A269" s="12">
+      <c r="A269" s="13">
         <v>45200</v>
       </c>
-      <c r="B269" s="8">
+      <c r="B269" s="13">
         <v>45231</v>
       </c>
-      <c r="C269" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D269" s="9" t="str">
+      <c r="C269" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D269" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9457,16 +9454,16 @@
       </c>
     </row>
     <row r="270" spans="1:7">
-      <c r="A270" s="12">
+      <c r="A270" s="13">
         <v>45231</v>
       </c>
-      <c r="B270" s="8">
+      <c r="B270" s="13">
         <v>45266</v>
       </c>
-      <c r="C270" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D270" s="9" t="str">
+      <c r="C270" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D270" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -9481,16 +9478,16 @@
       </c>
     </row>
     <row r="271" spans="1:7">
-      <c r="A271" s="12">
+      <c r="A271" s="13">
         <v>45261</v>
       </c>
-      <c r="B271" s="8">
+      <c r="B271" s="13">
         <v>45295</v>
       </c>
-      <c r="C271" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D271" s="9" t="str">
+      <c r="C271" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D271" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -9505,16 +9502,16 @@
       </c>
     </row>
     <row r="272" spans="1:7">
-      <c r="A272" s="12">
+      <c r="A272" s="13">
         <v>45292</v>
       </c>
-      <c r="B272" s="8">
+      <c r="B272" s="13">
         <v>45322</v>
       </c>
-      <c r="C272" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D272" s="9" t="str">
+      <c r="C272" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D272" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -9529,16 +9526,16 @@
       </c>
     </row>
     <row r="273" spans="1:7">
-      <c r="A273" s="12">
+      <c r="A273" s="13">
         <v>45323</v>
       </c>
-      <c r="B273" s="8">
+      <c r="B273" s="13">
         <v>45357</v>
       </c>
-      <c r="C273" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D273" s="9" t="str">
+      <c r="C273" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D273" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -9553,16 +9550,16 @@
       </c>
     </row>
     <row r="274" spans="1:7">
-      <c r="A274" s="12">
+      <c r="A274" s="13">
         <v>45352</v>
       </c>
-      <c r="B274" s="8">
+      <c r="B274" s="13">
         <v>45385</v>
       </c>
-      <c r="C274" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D274" s="9" t="str">
+      <c r="C274" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D274" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9577,16 +9574,16 @@
       </c>
     </row>
     <row r="275" spans="1:7">
-      <c r="A275" s="12">
+      <c r="A275" s="13">
         <v>45383</v>
       </c>
-      <c r="B275" s="8">
+      <c r="B275" s="13">
         <v>45413</v>
       </c>
-      <c r="C275" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D275" s="9" t="str">
+      <c r="C275" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D275" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9601,16 +9598,16 @@
       </c>
     </row>
     <row r="276" spans="1:7">
-      <c r="A276" s="12">
+      <c r="A276" s="13">
         <v>45413</v>
       </c>
-      <c r="B276" s="8">
+      <c r="B276" s="13">
         <v>45448</v>
       </c>
-      <c r="C276" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D276" s="9" t="str">
+      <c r="C276" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D276" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9625,16 +9622,16 @@
       </c>
     </row>
     <row r="277" spans="1:7">
-      <c r="A277" s="12">
+      <c r="A277" s="13">
         <v>45444</v>
       </c>
-      <c r="B277" s="8">
+      <c r="B277" s="13">
         <v>45476</v>
       </c>
-      <c r="C277" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D277" s="9" t="str">
+      <c r="C277" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D277" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9649,16 +9646,16 @@
       </c>
     </row>
     <row r="278" spans="1:7">
-      <c r="A278" s="12">
+      <c r="A278" s="13">
         <v>45474</v>
       </c>
-      <c r="B278" s="8">
+      <c r="B278" s="13">
         <v>45504</v>
       </c>
-      <c r="C278" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D278" s="9" t="str">
+      <c r="C278" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D278" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9673,16 +9670,16 @@
       </c>
     </row>
     <row r="279" spans="1:7">
-      <c r="A279" s="12">
+      <c r="A279" s="13">
         <v>45505</v>
       </c>
-      <c r="B279" s="8">
+      <c r="B279" s="13">
         <v>45540</v>
       </c>
-      <c r="C279" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D279" s="9" t="str">
+      <c r="C279" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D279" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9697,16 +9694,16 @@
       </c>
     </row>
     <row r="280" spans="1:7">
-      <c r="A280" s="12">
+      <c r="A280" s="13">
         <v>45536</v>
       </c>
-      <c r="B280" s="8">
+      <c r="B280" s="13">
         <v>45567</v>
       </c>
-      <c r="C280" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D280" s="9" t="str">
+      <c r="C280" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D280" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9721,16 +9718,16 @@
       </c>
     </row>
     <row r="281" spans="1:7">
-      <c r="A281" s="12">
+      <c r="A281" s="13">
         <v>45566</v>
       </c>
-      <c r="B281" s="8">
+      <c r="B281" s="13">
         <v>45595</v>
       </c>
-      <c r="C281" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D281" s="9" t="str">
+      <c r="C281" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D281" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9745,16 +9742,16 @@
       </c>
     </row>
     <row r="282" spans="1:7">
-      <c r="A282" s="12">
+      <c r="A282" s="13">
         <v>45597</v>
       </c>
-      <c r="B282" s="8">
+      <c r="B282" s="13">
         <v>45630</v>
       </c>
-      <c r="C282" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D282" s="9" t="str">
+      <c r="C282" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D282" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -9769,16 +9766,16 @@
       </c>
     </row>
     <row r="283" spans="1:7">
-      <c r="A283" s="12">
+      <c r="A283" s="13">
         <v>45627</v>
       </c>
-      <c r="B283" s="8">
+      <c r="B283" s="13">
         <v>45665</v>
       </c>
-      <c r="C283" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D283" s="9" t="str">
+      <c r="C283" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D283" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -9793,16 +9790,16 @@
       </c>
     </row>
     <row r="284" spans="1:7">
-      <c r="A284" s="12">
+      <c r="A284" s="13">
         <v>45658</v>
       </c>
-      <c r="B284" s="8">
+      <c r="B284" s="13">
         <v>45693</v>
       </c>
-      <c r="C284" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D284" s="9" t="str">
+      <c r="C284" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D284" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -9817,16 +9814,16 @@
       </c>
     </row>
     <row r="285" spans="1:7">
-      <c r="A285" s="12">
+      <c r="A285" s="13">
         <v>45689</v>
       </c>
-      <c r="B285" s="8">
+      <c r="B285" s="13">
         <v>45721</v>
       </c>
-      <c r="C285" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D285" s="9" t="str">
+      <c r="C285" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D285" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -9841,16 +9838,16 @@
       </c>
     </row>
     <row r="286" spans="1:7">
-      <c r="A286" s="12">
+      <c r="A286" s="13">
         <v>45717</v>
       </c>
-      <c r="B286" s="8">
+      <c r="B286" s="13">
         <v>45749</v>
       </c>
-      <c r="C286" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D286" s="9" t="str">
+      <c r="C286" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D286" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9865,16 +9862,16 @@
       </c>
     </row>
     <row r="287" spans="1:7">
-      <c r="A287" s="12">
+      <c r="A287" s="13">
         <v>45748</v>
       </c>
-      <c r="B287" s="8">
+      <c r="B287" s="13">
         <v>45777</v>
       </c>
-      <c r="C287" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D287" s="9" t="str">
+      <c r="C287" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D287" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9889,16 +9886,16 @@
       </c>
     </row>
     <row r="288" spans="1:7">
-      <c r="A288" s="12">
+      <c r="A288" s="13">
         <v>45778</v>
       </c>
-      <c r="B288" s="8">
+      <c r="B288" s="13">
         <v>45812</v>
       </c>
-      <c r="C288" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D288" s="9" t="str">
+      <c r="C288" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D288" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9913,16 +9910,16 @@
       </c>
     </row>
     <row r="289" spans="1:7">
-      <c r="A289" s="12">
+      <c r="A289" s="13">
         <v>45809</v>
       </c>
-      <c r="B289" s="8">
+      <c r="B289" s="13">
         <v>45840</v>
       </c>
-      <c r="C289" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D289" s="9" t="str">
+      <c r="C289" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D289" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9937,16 +9934,16 @@
       </c>
     </row>
     <row r="290" spans="1:7">
-      <c r="A290" s="12">
+      <c r="A290" s="13">
         <v>45839</v>
       </c>
-      <c r="B290" s="8">
+      <c r="B290" s="13">
         <v>45868</v>
       </c>
-      <c r="C290" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D290" s="9" t="str">
+      <c r="C290" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D290" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9961,16 +9958,16 @@
       </c>
     </row>
     <row r="291" spans="1:7">
-      <c r="A291" s="12">
+      <c r="A291" s="13">
         <v>45870</v>
       </c>
-      <c r="B291" s="8">
+      <c r="B291" s="13">
         <v>45904</v>
       </c>
-      <c r="C291" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D291" s="9" t="str">
+      <c r="C291" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D291" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -9985,16 +9982,16 @@
       </c>
     </row>
     <row r="292" spans="1:7">
-      <c r="A292" s="12">
+      <c r="A292" s="13">
         <v>45901</v>
       </c>
-      <c r="B292" s="8">
+      <c r="B292" s="13">
         <v>45931</v>
       </c>
-      <c r="C292" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D292" s="9" t="str">
+      <c r="C292" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D292" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -10009,16 +10006,16 @@
       </c>
     </row>
     <row r="293" spans="1:7">
-      <c r="A293" s="12">
+      <c r="A293" s="13">
         <v>45931</v>
       </c>
-      <c r="B293" s="8">
+      <c r="B293" s="13">
         <v>45966</v>
       </c>
-      <c r="C293" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D293" s="9" t="str">
+      <c r="C293" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D293" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -10033,16 +10030,16 @@
       </c>
     </row>
     <row r="294" spans="1:7">
-      <c r="A294" s="12">
+      <c r="A294" s="13">
         <v>45962</v>
       </c>
-      <c r="B294" s="8">
+      <c r="B294" s="13">
         <v>45994</v>
       </c>
-      <c r="C294" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D294" s="9" t="str">
+      <c r="C294" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D294" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -10057,16 +10054,16 @@
       </c>
     </row>
     <row r="295" spans="1:7">
-      <c r="A295" s="12">
+      <c r="A295" s="13">
         <v>45992</v>
       </c>
-      <c r="B295" s="8">
+      <c r="B295" s="13">
         <v>46029</v>
       </c>
-      <c r="C295" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D295" s="9" t="str">
+      <c r="C295" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D295" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -10081,16 +10078,16 @@
       </c>
     </row>
     <row r="296" spans="1:7">
-      <c r="A296" s="12">
+      <c r="A296" s="13">
         <v>46023</v>
       </c>
-      <c r="B296" s="8">
+      <c r="B296" s="13">
         <v>46057</v>
       </c>
-      <c r="C296" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D296" s="9" t="str">
+      <c r="C296" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D296" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -10105,16 +10102,16 @@
       </c>
     </row>
     <row r="297" spans="1:7">
-      <c r="A297" s="12">
+      <c r="A297" s="13">
         <v>46054</v>
       </c>
-      <c r="B297" s="8">
+      <c r="B297" s="13">
         <v>46085</v>
       </c>
-      <c r="C297" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D297" s="9" t="str">
+      <c r="C297" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D297" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
@@ -10129,16 +10126,16 @@
       </c>
     </row>
     <row r="298" spans="1:7">
-      <c r="A298" s="12">
+      <c r="A298" s="13">
         <v>46082</v>
       </c>
-      <c r="B298" s="8">
+      <c r="B298" s="13">
         <v>46113</v>
       </c>
-      <c r="C298" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D298" s="9" t="str">
+      <c r="C298" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D298" s="7" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -10153,16 +10150,16 @@
       </c>
     </row>
     <row r="299" spans="1:7">
-      <c r="A299" s="12">
+      <c r="A299" s="13">
         <v>46113</v>
       </c>
-      <c r="B299" s="8">
+      <c r="B299" s="13">
         <v>46148</v>
       </c>
-      <c r="C299" s="11">
-        <v>0.34375</v>
-      </c>
-      <c r="D299" s="7" t="str">
+      <c r="C299" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="D299" s="6" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
@@ -10188,7 +10185,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABA1812-C744-4515-949A-95B6005467FB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10199,23 +10196,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0E670B-E56D-4466-88FF-6442D4BC04BB}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="1"/>
-    <col min="2" max="2" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="8.77734375" style="1"/>
+    <col min="2" max="2" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">

--- a/data/macro/USA/ADP Nonfarm Employment changes.xlsx
+++ b/data/macro/USA/ADP Nonfarm Employment changes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BA06A0-6F6D-41E8-AC81-BE1D4644D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9F5CEC-8416-43C1-A421-51D591C9A9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ADPCHNG" sheetId="1" r:id="rId1"/>
@@ -83,10 +83,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,19 +115,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -148,6 +135,14 @@
       <color theme="10"/>
       <name val="Verdana"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -172,37 +167,37 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2125,7 +2120,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -2187,7 +2182,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -2230,7 +2225,7 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="+mn-lt"/>
               <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -2266,7 +2261,7 @@
     <a:p>
       <a:pPr>
         <a:defRPr>
-          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="+mn-lt"/>
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
@@ -3144,50 +3139,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G299"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="15.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.77734375" style="2"/>
+    <col min="4" max="4" width="11.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="15.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.77734375" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:7" s="6" customFormat="1">
+      <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
+      <c r="A2" s="8">
         <v>37012</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="8">
         <v>37043</v>
       </c>
       <c r="C2" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D2" s="7" t="str">
+      <c r="D2" s="10" t="str">
         <f>IF(
  AND(
   B2 &gt;= IF(
@@ -3206,21 +3201,21 @@
 )</f>
         <v>UTC-4</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="11">
         <v>-175000</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="13">
+      <c r="A3" s="8">
         <v>37043</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="8">
         <v>37073</v>
       </c>
       <c r="C3" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D3" s="7" t="str">
+      <c r="D3" s="10" t="str">
         <f t="shared" ref="D3:D66" si="0">IF(
  AND(
   B3 &gt;= IF(
@@ -3239,1347 +3234,1347 @@
 )</f>
         <v>UTC-4</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="11">
         <v>-230000</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="11">
         <v>-175000</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="13">
+      <c r="A4" s="8">
         <v>37073</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="8">
         <v>37104</v>
       </c>
       <c r="C4" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D4" s="7" t="str">
+      <c r="D4" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="11">
         <v>-203000</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="11">
         <v>-230000</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="13">
+      <c r="A5" s="8">
         <v>37104</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="8">
         <v>37135</v>
       </c>
       <c r="C5" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="11">
         <v>-246000</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="11">
         <v>-203000</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="13">
+      <c r="A6" s="8">
         <v>37135</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="8">
         <v>37165</v>
       </c>
       <c r="C6" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D6" s="7" t="str">
+      <c r="D6" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="11">
         <v>-261000</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="11">
         <v>-246000</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="13">
+      <c r="A7" s="8">
         <v>37165</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="8">
         <v>37196</v>
       </c>
       <c r="C7" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D7" s="7" t="str">
+      <c r="D7" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="11">
         <v>-380000</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="11">
         <v>-261000</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="13">
+      <c r="A8" s="8">
         <v>37196</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="8">
         <v>37226</v>
       </c>
       <c r="C8" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D8" s="7" t="str">
+      <c r="D8" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="11">
         <v>-361000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="11">
         <v>-380000</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="13">
+      <c r="A9" s="8">
         <v>37226</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="8">
         <v>37257</v>
       </c>
       <c r="C9" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D9" s="7" t="str">
+      <c r="D9" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="11">
         <v>-223000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="11">
         <v>-361000</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="13">
+      <c r="A10" s="8">
         <v>37257</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="8">
         <v>37288</v>
       </c>
       <c r="C10" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D10" s="7" t="str">
+      <c r="D10" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="11">
         <v>-69000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="11">
         <v>-223000</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="13">
+      <c r="A11" s="8">
         <v>37288</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="8">
         <v>37316</v>
       </c>
       <c r="C11" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D11" s="7" t="str">
+      <c r="D11" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="11">
         <v>-91000</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="11">
         <v>-69000</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="13">
+      <c r="A12" s="8">
         <v>37316</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="8">
         <v>37347</v>
       </c>
       <c r="C12" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D12" s="7" t="str">
+      <c r="D12" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="11">
         <v>-70000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="11">
         <v>-91000</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="13">
+      <c r="A13" s="8">
         <v>37347</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="8">
         <v>37377</v>
       </c>
       <c r="C13" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D13" s="7" t="str">
+      <c r="D13" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="11">
         <v>-70000</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="11">
         <v>-70000</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="13">
+      <c r="A14" s="8">
         <v>37377</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="8">
         <v>37408</v>
       </c>
       <c r="C14" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D14" s="7" t="str">
+      <c r="D14" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="11">
         <v>-47000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="11">
         <v>-70000</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="13">
+      <c r="A15" s="8">
         <v>37408</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="8">
         <v>37438</v>
       </c>
       <c r="C15" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D15" s="7" t="str">
+      <c r="D15" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="11">
         <v>-91000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="11">
         <v>-47000</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="13">
+      <c r="A16" s="8">
         <v>37438</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="8">
         <v>37469</v>
       </c>
       <c r="C16" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D16" s="7" t="str">
+      <c r="D16" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="11">
         <v>-95000</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="11">
         <v>-91000</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="13">
+      <c r="A17" s="8">
         <v>37469</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="8">
         <v>37500</v>
       </c>
       <c r="C17" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D17" s="7" t="str">
+      <c r="D17" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="11">
         <v>-22000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="11">
         <v>-95000</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="13">
+      <c r="A18" s="8">
         <v>37500</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="8">
         <v>37530</v>
       </c>
       <c r="C18" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D18" s="7" t="str">
+      <c r="D18" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="11">
         <v>-84000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="11">
         <v>-22000</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="13">
+      <c r="A19" s="8">
         <v>37530</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="8">
         <v>37561</v>
       </c>
       <c r="C19" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D19" s="7" t="str">
+      <c r="D19" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="11">
         <v>-42000</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="11">
         <v>-84000</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="13">
+      <c r="A20" s="8">
         <v>37561</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="8">
         <v>37591</v>
       </c>
       <c r="C20" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D20" s="7" t="str">
+      <c r="D20" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="11">
         <v>-18000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="11">
         <v>-42000</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="13">
+      <c r="A21" s="8">
         <v>37591</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="8">
         <v>37622</v>
       </c>
       <c r="C21" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D21" s="7" t="str">
+      <c r="D21" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="11">
         <v>-35000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="11">
         <v>-18000</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="13">
+      <c r="A22" s="8">
         <v>37622</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="8">
         <v>37653</v>
       </c>
       <c r="C22" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D22" s="7" t="str">
+      <c r="D22" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="11">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="11">
         <v>-35000</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="13">
+      <c r="A23" s="8">
         <v>37653</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="8">
         <v>37681</v>
       </c>
       <c r="C23" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D23" s="7" t="str">
+      <c r="D23" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="11">
         <v>-68000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="13">
+      <c r="A24" s="8">
         <v>37681</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="8">
         <v>37712</v>
       </c>
       <c r="C24" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D24" s="7" t="str">
+      <c r="D24" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="11">
         <v>-91000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="11">
         <v>-68000</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="13">
+      <c r="A25" s="8">
         <v>37712</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="8">
         <v>37742</v>
       </c>
       <c r="C25" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D25" s="7" t="str">
+      <c r="D25" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="11">
         <v>-86000</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="11">
         <v>-91000</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="13">
+      <c r="A26" s="8">
         <v>37742</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="8">
         <v>37773</v>
       </c>
       <c r="C26" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D26" s="7" t="str">
+      <c r="D26" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="11">
         <v>-6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="11">
         <v>-86000</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="13">
+      <c r="A27" s="8">
         <v>37773</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="8">
         <v>37803</v>
       </c>
       <c r="C27" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D27" s="7" t="str">
+      <c r="D27" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="11">
         <v>25000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="11">
         <v>-6000</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="13">
+      <c r="A28" s="8">
         <v>37803</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="8">
         <v>37834</v>
       </c>
       <c r="C28" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D28" s="7" t="str">
+      <c r="D28" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="11">
         <v>78000</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="11">
         <v>25000</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="13">
+      <c r="A29" s="8">
         <v>37834</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="8">
         <v>37865</v>
       </c>
       <c r="C29" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D29" s="7" t="str">
+      <c r="D29" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="11">
         <v>24000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="11">
         <v>78000</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="13">
+      <c r="A30" s="8">
         <v>37865</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="8">
         <v>37895</v>
       </c>
       <c r="C30" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D30" s="7" t="str">
+      <c r="D30" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="11">
         <v>132000</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="11">
         <v>24000</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="13">
+      <c r="A31" s="8">
         <v>37895</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="8">
         <v>37926</v>
       </c>
       <c r="C31" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D31" s="7" t="str">
+      <c r="D31" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="11">
         <v>146000</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="11">
         <v>132000</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="13">
+      <c r="A32" s="8">
         <v>37926</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="8">
         <v>37956</v>
       </c>
       <c r="C32" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D32" s="7" t="str">
+      <c r="D32" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="11">
         <v>105000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="11">
         <v>146000</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="13">
+      <c r="A33" s="8">
         <v>37956</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="8">
         <v>37987</v>
       </c>
       <c r="C33" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D33" s="7" t="str">
+      <c r="D33" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="11">
         <v>60000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="11">
         <v>105000</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="13">
+      <c r="A34" s="8">
         <v>37987</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="8">
         <v>38018</v>
       </c>
       <c r="C34" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D34" s="7" t="str">
+      <c r="D34" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="11">
         <v>111000</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="11">
         <v>60000</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="13">
+      <c r="A35" s="8">
         <v>38018</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="8">
         <v>38047</v>
       </c>
       <c r="C35" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D35" s="7" t="str">
+      <c r="D35" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="11">
         <v>140000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="11">
         <v>111000</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="13">
+      <c r="A36" s="8">
         <v>38047</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="8">
         <v>38078</v>
       </c>
       <c r="C36" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D36" s="7" t="str">
+      <c r="D36" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="11">
         <v>205000</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="11">
         <v>140000</v>
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="13">
+      <c r="A37" s="8">
         <v>38078</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="8">
         <v>38108</v>
       </c>
       <c r="C37" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D37" s="7" t="str">
+      <c r="D37" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="11">
         <v>224000</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="11">
         <v>205000</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="13">
+      <c r="A38" s="8">
         <v>38108</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="8">
         <v>38139</v>
       </c>
       <c r="C38" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D38" s="7" t="str">
+      <c r="D38" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="11">
         <v>165000</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="11">
         <v>224000</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="13">
+      <c r="A39" s="8">
         <v>38139</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="8">
         <v>38169</v>
       </c>
       <c r="C39" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D39" s="7" t="str">
+      <c r="D39" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="11">
         <v>133000</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="11">
         <v>165000</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="13">
+      <c r="A40" s="8">
         <v>38169</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="8">
         <v>38200</v>
       </c>
       <c r="C40" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D40" s="7" t="str">
+      <c r="D40" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="11">
         <v>116000</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="11">
         <v>133000</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="13">
+      <c r="A41" s="8">
         <v>38200</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="8">
         <v>38231</v>
       </c>
       <c r="C41" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D41" s="7" t="str">
+      <c r="D41" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="11">
         <v>126000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="11">
         <v>116000</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="13">
+      <c r="A42" s="8">
         <v>38231</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="8">
         <v>38261</v>
       </c>
       <c r="C42" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D42" s="7" t="str">
+      <c r="D42" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="11">
         <v>119000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="11">
         <v>126000</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="13">
+      <c r="A43" s="8">
         <v>38261</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="8">
         <v>38292</v>
       </c>
       <c r="C43" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D43" s="7" t="str">
+      <c r="D43" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="11">
         <v>203000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="11">
         <v>119000</v>
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="13">
+      <c r="A44" s="8">
         <v>38292</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="8">
         <v>38322</v>
       </c>
       <c r="C44" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D44" s="7" t="str">
+      <c r="D44" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="11">
         <v>70000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="11">
         <v>203000</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="13">
+      <c r="A45" s="8">
         <v>38322</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="8">
         <v>38353</v>
       </c>
       <c r="C45" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D45" s="7" t="str">
+      <c r="D45" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="11">
         <v>197000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="11">
         <v>70000</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="13">
+      <c r="A46" s="8">
         <v>38353</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="8">
         <v>38384</v>
       </c>
       <c r="C46" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D46" s="7" t="str">
+      <c r="D46" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="11">
         <v>155000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="11">
         <v>197000</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="13">
+      <c r="A47" s="8">
         <v>38384</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="8">
         <v>38412</v>
       </c>
       <c r="C47" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D47" s="7" t="str">
+      <c r="D47" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="11">
         <v>174000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="11">
         <v>155000</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="13">
+      <c r="A48" s="8">
         <v>38412</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="8">
         <v>38443</v>
       </c>
       <c r="C48" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D48" s="7" t="str">
+      <c r="D48" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="11">
         <v>169000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="11">
         <v>174000</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="13">
+      <c r="A49" s="8">
         <v>38443</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="8">
         <v>38473</v>
       </c>
       <c r="C49" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D49" s="7" t="str">
+      <c r="D49" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="11">
         <v>218000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="11">
         <v>169000</v>
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="13">
+      <c r="A50" s="8">
         <v>38473</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="8">
         <v>38504</v>
       </c>
       <c r="C50" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D50" s="7" t="str">
+      <c r="D50" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="11">
         <v>238000</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="11">
         <v>218000</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="13">
+      <c r="A51" s="8">
         <v>38504</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="8">
         <v>38534</v>
       </c>
       <c r="C51" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D51" s="7" t="str">
+      <c r="D51" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="11">
         <v>253000</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="11">
         <v>238000</v>
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="13">
+      <c r="A52" s="8">
         <v>38534</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="8">
         <v>38565</v>
       </c>
       <c r="C52" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D52" s="7" t="str">
+      <c r="D52" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="11">
         <v>204000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="11">
         <v>253000</v>
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="13">
+      <c r="A53" s="8">
         <v>38565</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="8">
         <v>38596</v>
       </c>
       <c r="C53" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D53" s="7" t="str">
+      <c r="D53" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="11">
         <v>175000</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="11">
         <v>204000</v>
       </c>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="13">
+      <c r="A54" s="8">
         <v>38596</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="8">
         <v>38626</v>
       </c>
       <c r="C54" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D54" s="7" t="str">
+      <c r="D54" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="11">
         <v>105000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="11">
         <v>175000</v>
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="13">
+      <c r="A55" s="8">
         <v>38626</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="8">
         <v>38657</v>
       </c>
       <c r="C55" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D55" s="7" t="str">
+      <c r="D55" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="11">
         <v>154000</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="11">
         <v>105000</v>
       </c>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="13">
+      <c r="A56" s="8">
         <v>38657</v>
       </c>
-      <c r="B56" s="13">
+      <c r="B56" s="8">
         <v>38687</v>
       </c>
       <c r="C56" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D56" s="7" t="str">
+      <c r="D56" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56" s="11">
         <v>343000</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="11">
         <v>154000</v>
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="13">
+      <c r="A57" s="8">
         <v>38687</v>
       </c>
-      <c r="B57" s="13">
+      <c r="B57" s="8">
         <v>38718</v>
       </c>
       <c r="C57" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D57" s="7" t="str">
+      <c r="D57" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="11">
         <v>165000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="11">
         <v>343000</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="13">
+      <c r="A58" s="8">
         <v>38718</v>
       </c>
-      <c r="B58" s="13">
+      <c r="B58" s="8">
         <v>38749</v>
       </c>
       <c r="C58" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D58" s="7" t="str">
+      <c r="D58" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="11">
         <v>329000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="11">
         <v>165000</v>
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="13">
+      <c r="A59" s="8">
         <v>38749</v>
       </c>
-      <c r="B59" s="13">
+      <c r="B59" s="8">
         <v>38777</v>
       </c>
       <c r="C59" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D59" s="7" t="str">
+      <c r="D59" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="11">
         <v>307000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="11">
         <v>329000</v>
       </c>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="13">
+      <c r="A60" s="8">
         <v>38777</v>
       </c>
-      <c r="B60" s="13">
+      <c r="B60" s="8">
         <v>38808</v>
       </c>
       <c r="C60" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D60" s="7" t="str">
+      <c r="D60" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-5</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E60" s="11">
         <v>217000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60" s="11">
         <v>307000</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="13">
+      <c r="A61" s="8">
         <v>38808</v>
       </c>
-      <c r="B61" s="13">
+      <c r="B61" s="8">
         <v>38838</v>
       </c>
       <c r="C61" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D61" s="7" t="str">
+      <c r="D61" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="11">
         <v>148000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61" s="11">
         <v>217000</v>
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="13">
+      <c r="A62" s="8">
         <v>38838</v>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="8">
         <v>38869</v>
       </c>
       <c r="C62" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D62" s="7" t="str">
+      <c r="D62" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="11">
         <v>143000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="11">
         <v>148000</v>
       </c>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="13">
+      <c r="A63" s="8">
         <v>38869</v>
       </c>
-      <c r="B63" s="13">
+      <c r="B63" s="8">
         <v>38899</v>
       </c>
       <c r="C63" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D63" s="7" t="str">
+      <c r="D63" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E63" s="3">
+      <c r="E63" s="11">
         <v>125000</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G63" s="11">
         <v>143000</v>
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="13">
+      <c r="A64" s="8">
         <v>38899</v>
       </c>
-      <c r="B64" s="13">
+      <c r="B64" s="8">
         <v>38930</v>
       </c>
       <c r="C64" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D64" s="7" t="str">
+      <c r="D64" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E64" s="3">
+      <c r="E64" s="11">
         <v>106000</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G64" s="11">
         <v>125000</v>
       </c>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="13">
+      <c r="A65" s="8">
         <v>38930</v>
       </c>
-      <c r="B65" s="13">
+      <c r="B65" s="8">
         <v>38961</v>
       </c>
       <c r="C65" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D65" s="7" t="str">
+      <c r="D65" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E65" s="3">
+      <c r="E65" s="11">
         <v>98000</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G65" s="11">
         <v>106000</v>
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="13">
+      <c r="A66" s="8">
         <v>38961</v>
       </c>
-      <c r="B66" s="13">
+      <c r="B66" s="8">
         <v>38991</v>
       </c>
       <c r="C66" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D66" s="7" t="str">
+      <c r="D66" s="10" t="str">
         <f t="shared" si="0"/>
         <v>UTC-4</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E66" s="11">
         <v>25000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G66" s="11">
         <v>98000</v>
       </c>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="13">
+      <c r="A67" s="8">
         <v>38991</v>
       </c>
-      <c r="B67" s="13">
+      <c r="B67" s="8">
         <v>39022</v>
       </c>
       <c r="C67" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D67" s="7" t="str">
+      <c r="D67" s="10" t="str">
         <f t="shared" ref="D67:D130" si="1">IF(
  AND(
   B67 &gt;= IF(
@@ -4598,1491 +4593,1491 @@
 )</f>
         <v>UTC-5</v>
       </c>
-      <c r="E67" s="3">
+      <c r="E67" s="11">
         <v>90000</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G67" s="11">
         <v>25000</v>
       </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="13">
+      <c r="A68" s="8">
         <v>39022</v>
       </c>
-      <c r="B68" s="13">
+      <c r="B68" s="8">
         <v>39052</v>
       </c>
       <c r="C68" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D68" s="7" t="str">
+      <c r="D68" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E68" s="11">
         <v>193000</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G68" s="11">
         <v>90000</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="13">
+      <c r="A69" s="8">
         <v>39052</v>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="8">
         <v>39083</v>
       </c>
       <c r="C69" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D69" s="7" t="str">
+      <c r="D69" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E69" s="11">
         <v>74000</v>
       </c>
-      <c r="G69" s="3">
+      <c r="G69" s="11">
         <v>193000</v>
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="13">
+      <c r="A70" s="8">
         <v>39083</v>
       </c>
-      <c r="B70" s="13">
+      <c r="B70" s="8">
         <v>39114</v>
       </c>
       <c r="C70" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D70" s="7" t="str">
+      <c r="D70" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E70" s="3">
+      <c r="E70" s="11">
         <v>199000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="G70" s="11">
         <v>74000</v>
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="13">
+      <c r="A71" s="8">
         <v>39114</v>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="8">
         <v>39142</v>
       </c>
       <c r="C71" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D71" s="7" t="str">
+      <c r="D71" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E71" s="11">
         <v>153000</v>
       </c>
-      <c r="G71" s="3">
+      <c r="G71" s="11">
         <v>199000</v>
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="13">
+      <c r="A72" s="8">
         <v>39142</v>
       </c>
-      <c r="B72" s="13">
+      <c r="B72" s="8">
         <v>39173</v>
       </c>
       <c r="C72" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D72" s="7" t="str">
+      <c r="D72" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="11">
         <v>127000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="11">
         <v>153000</v>
       </c>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="13">
+      <c r="A73" s="8">
         <v>39173</v>
       </c>
-      <c r="B73" s="13">
+      <c r="B73" s="8">
         <v>39203</v>
       </c>
       <c r="C73" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D73" s="7" t="str">
+      <c r="D73" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E73" s="11">
         <v>137000</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G73" s="11">
         <v>127000</v>
       </c>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="13">
+      <c r="A74" s="8">
         <v>39203</v>
       </c>
-      <c r="B74" s="13">
+      <c r="B74" s="8">
         <v>39234</v>
       </c>
       <c r="C74" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D74" s="7" t="str">
+      <c r="D74" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E74" s="3">
+      <c r="E74" s="11">
         <v>59000</v>
       </c>
-      <c r="G74" s="3">
+      <c r="G74" s="11">
         <v>137000</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="13">
+      <c r="A75" s="8">
         <v>39234</v>
       </c>
-      <c r="B75" s="13">
+      <c r="B75" s="8">
         <v>39264</v>
       </c>
       <c r="C75" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D75" s="7" t="str">
+      <c r="D75" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E75" s="11">
         <v>97000</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75" s="11">
         <v>59000</v>
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="13">
+      <c r="A76" s="8">
         <v>39264</v>
       </c>
-      <c r="B76" s="13">
+      <c r="B76" s="8">
         <v>39295</v>
       </c>
       <c r="C76" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D76" s="7" t="str">
+      <c r="D76" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E76" s="3">
+      <c r="E76" s="11">
         <v>-18000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G76" s="11">
         <v>97000</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="13">
+      <c r="A77" s="8">
         <v>39295</v>
       </c>
-      <c r="B77" s="13">
+      <c r="B77" s="8">
         <v>39326</v>
       </c>
       <c r="C77" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D77" s="7" t="str">
+      <c r="D77" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E77" s="3">
+      <c r="E77" s="11">
         <v>31000</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G77" s="11">
         <v>-18000</v>
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="13">
+      <c r="A78" s="8">
         <v>39326</v>
       </c>
-      <c r="B78" s="13">
+      <c r="B78" s="8">
         <v>39356</v>
       </c>
       <c r="C78" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D78" s="7" t="str">
+      <c r="D78" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E78" s="3">
+      <c r="E78" s="11">
         <v>-3000</v>
       </c>
-      <c r="G78" s="3">
+      <c r="G78" s="11">
         <v>31000</v>
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="13">
+      <c r="A79" s="8">
         <v>39356</v>
       </c>
-      <c r="B79" s="13">
+      <c r="B79" s="8">
         <v>39387</v>
       </c>
       <c r="C79" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D79" s="7" t="str">
+      <c r="D79" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E79" s="3">
+      <c r="E79" s="11">
         <v>-8000</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G79" s="11">
         <v>-3000</v>
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="13">
+      <c r="A80" s="8">
         <v>39387</v>
       </c>
-      <c r="B80" s="13">
+      <c r="B80" s="8">
         <v>39417</v>
       </c>
       <c r="C80" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D80" s="7" t="str">
+      <c r="D80" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E80" s="3">
+      <c r="E80" s="11">
         <v>66000</v>
       </c>
-      <c r="G80" s="3">
+      <c r="G80" s="11">
         <v>-8000</v>
       </c>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="13">
+      <c r="A81" s="8">
         <v>39417</v>
       </c>
-      <c r="B81" s="13">
+      <c r="B81" s="8">
         <v>39448</v>
       </c>
       <c r="C81" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D81" s="7" t="str">
+      <c r="D81" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E81" s="3">
+      <c r="E81" s="11">
         <v>0</v>
       </c>
-      <c r="G81" s="3">
+      <c r="G81" s="11">
         <v>66000</v>
       </c>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="13">
+      <c r="A82" s="8">
         <v>39448</v>
       </c>
-      <c r="B82" s="13">
+      <c r="B82" s="8">
         <v>39479</v>
       </c>
       <c r="C82" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D82" s="7" t="str">
+      <c r="D82" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E82" s="3">
+      <c r="E82" s="11">
         <v>42000</v>
       </c>
-      <c r="G82" s="3">
+      <c r="G82" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="13">
+      <c r="A83" s="8">
         <v>39479</v>
       </c>
-      <c r="B83" s="13">
+      <c r="B83" s="8">
         <v>39512</v>
       </c>
       <c r="C83" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D83" s="7" t="str">
+      <c r="D83" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="11">
         <v>-23000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="11">
         <v>10000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="11">
         <v>126000</v>
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="13">
+      <c r="A84" s="8">
         <v>39508</v>
       </c>
-      <c r="B84" s="13">
+      <c r="B84" s="8">
         <v>39540</v>
       </c>
       <c r="C84" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D84" s="7" t="str">
+      <c r="D84" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E84" s="3">
+      <c r="E84" s="11">
         <v>8000</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F84" s="11">
         <v>-40000</v>
       </c>
-      <c r="G84" s="3">
+      <c r="G84" s="11">
         <v>-23000</v>
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="13">
+      <c r="A85" s="8">
         <v>39539</v>
       </c>
-      <c r="B85" s="13">
+      <c r="B85" s="8">
         <v>39568</v>
       </c>
       <c r="C85" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D85" s="7" t="str">
+      <c r="D85" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E85" s="3">
+      <c r="E85" s="11">
         <v>10000</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85" s="11">
         <v>-60000</v>
       </c>
-      <c r="G85" s="3">
+      <c r="G85" s="11">
         <v>8000</v>
       </c>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="13">
+      <c r="A86" s="8">
         <v>39569</v>
       </c>
-      <c r="B86" s="13">
+      <c r="B86" s="8">
         <v>39603</v>
       </c>
       <c r="C86" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D86" s="7" t="str">
+      <c r="D86" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E86" s="3">
+      <c r="E86" s="11">
         <v>40000</v>
       </c>
-      <c r="F86" s="3">
+      <c r="F86" s="11">
         <v>-30000</v>
       </c>
-      <c r="G86" s="3">
+      <c r="G86" s="11">
         <v>13000</v>
       </c>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="13">
+      <c r="A87" s="8">
         <v>39600</v>
       </c>
-      <c r="B87" s="13">
+      <c r="B87" s="8">
         <v>39631</v>
       </c>
       <c r="C87" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D87" s="7" t="str">
+      <c r="D87" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E87" s="3">
+      <c r="E87" s="11">
         <v>-79000</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F87" s="11">
         <v>-20000</v>
       </c>
-      <c r="G87" s="3">
+      <c r="G87" s="11">
         <v>40000</v>
       </c>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="13">
+      <c r="A88" s="8">
         <v>39630</v>
       </c>
-      <c r="B88" s="13">
+      <c r="B88" s="8">
         <v>39659</v>
       </c>
       <c r="C88" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D88" s="7" t="str">
+      <c r="D88" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E88" s="3">
+      <c r="E88" s="11">
         <v>9000</v>
       </c>
-      <c r="F88" s="3">
+      <c r="F88" s="11">
         <v>-58000</v>
       </c>
-      <c r="G88" s="3">
+      <c r="G88" s="11">
         <v>-79000</v>
       </c>
     </row>
     <row r="89" spans="1:7">
-      <c r="A89" s="13">
+      <c r="A89" s="8">
         <v>39661</v>
       </c>
-      <c r="B89" s="13">
+      <c r="B89" s="8">
         <v>39695</v>
       </c>
       <c r="C89" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D89" s="7" t="str">
+      <c r="D89" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="11">
         <v>-33000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="11">
         <v>-30000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="11">
         <v>9000</v>
       </c>
     </row>
     <row r="90" spans="1:7">
-      <c r="A90" s="13">
+      <c r="A90" s="8">
         <v>39692</v>
       </c>
-      <c r="B90" s="13">
+      <c r="B90" s="8">
         <v>39722</v>
       </c>
       <c r="C90" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D90" s="7" t="str">
+      <c r="D90" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E90" s="3">
+      <c r="E90" s="11">
         <v>-8000</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F90" s="11">
         <v>-55000</v>
       </c>
-      <c r="G90" s="3">
+      <c r="G90" s="11">
         <v>-33000</v>
       </c>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="13">
+      <c r="A91" s="8">
         <v>39722</v>
       </c>
-      <c r="B91" s="13">
+      <c r="B91" s="8">
         <v>39757</v>
       </c>
       <c r="C91" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D91" s="7" t="str">
+      <c r="D91" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="11">
         <v>-157000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="11">
         <v>-100000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="11">
         <v>-8000</v>
       </c>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="13">
+      <c r="A92" s="8">
         <v>39753</v>
       </c>
-      <c r="B92" s="13">
+      <c r="B92" s="8">
         <v>39785</v>
       </c>
       <c r="C92" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D92" s="7" t="str">
+      <c r="D92" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E92" s="3">
+      <c r="E92" s="11">
         <v>-250000</v>
       </c>
-      <c r="F92" s="3">
+      <c r="F92" s="11">
         <v>-200000</v>
       </c>
-      <c r="G92" s="3">
+      <c r="G92" s="11">
         <v>-157000</v>
       </c>
     </row>
     <row r="93" spans="1:7">
-      <c r="A93" s="13">
+      <c r="A93" s="8">
         <v>39783</v>
       </c>
-      <c r="B93" s="13">
+      <c r="B93" s="8">
         <v>39820</v>
       </c>
       <c r="C93" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D93" s="7" t="str">
+      <c r="D93" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E93" s="3">
+      <c r="E93" s="11">
         <v>-693000</v>
       </c>
-      <c r="F93" s="3">
+      <c r="F93" s="11">
         <v>-450000</v>
       </c>
-      <c r="G93" s="3">
+      <c r="G93" s="11">
         <v>-476000</v>
       </c>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="13">
+      <c r="A94" s="8">
         <v>39814</v>
       </c>
-      <c r="B94" s="13">
+      <c r="B94" s="8">
         <v>39848</v>
       </c>
       <c r="C94" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D94" s="7" t="str">
+      <c r="D94" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="11">
         <v>-522000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="11">
         <v>-528000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="11">
         <v>-693000</v>
       </c>
     </row>
     <row r="95" spans="1:7">
-      <c r="A95" s="13">
+      <c r="A95" s="8">
         <v>39845</v>
       </c>
-      <c r="B95" s="13">
+      <c r="B95" s="8">
         <v>39876</v>
       </c>
       <c r="C95" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D95" s="7" t="str">
+      <c r="D95" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E95" s="3">
+      <c r="E95" s="11">
         <v>-697000</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F95" s="11">
         <v>-565000</v>
       </c>
-      <c r="G95" s="3">
+      <c r="G95" s="11">
         <v>-614000</v>
       </c>
     </row>
     <row r="96" spans="1:7">
-      <c r="A96" s="13">
+      <c r="A96" s="8">
         <v>39873</v>
       </c>
-      <c r="B96" s="13">
+      <c r="B96" s="8">
         <v>39904</v>
       </c>
       <c r="C96" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D96" s="7" t="str">
+      <c r="D96" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="11">
         <v>-742000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="11">
         <v>-660000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96" s="11">
         <v>-706000</v>
       </c>
     </row>
     <row r="97" spans="1:7">
-      <c r="A97" s="13">
+      <c r="A97" s="8">
         <v>39904</v>
       </c>
-      <c r="B97" s="13">
+      <c r="B97" s="8">
         <v>39939</v>
       </c>
       <c r="C97" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D97" s="7" t="str">
+      <c r="D97" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E97" s="3">
+      <c r="E97" s="11">
         <v>-491000</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F97" s="11">
         <v>-644000</v>
       </c>
-      <c r="G97" s="3">
+      <c r="G97" s="11">
         <v>-708000</v>
       </c>
     </row>
     <row r="98" spans="1:7">
-      <c r="A98" s="13">
+      <c r="A98" s="8">
         <v>39934</v>
       </c>
-      <c r="B98" s="13">
+      <c r="B98" s="8">
         <v>39967</v>
       </c>
       <c r="C98" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D98" s="7" t="str">
+      <c r="D98" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E98" s="3">
+      <c r="E98" s="11">
         <v>-532000</v>
       </c>
-      <c r="F98" s="3">
+      <c r="F98" s="11">
         <v>-532000</v>
       </c>
-      <c r="G98" s="3">
+      <c r="G98" s="11">
         <v>-545000</v>
       </c>
     </row>
     <row r="99" spans="1:7">
-      <c r="A99" s="13">
+      <c r="A99" s="8">
         <v>39965</v>
       </c>
-      <c r="B99" s="13">
+      <c r="B99" s="8">
         <v>39995</v>
       </c>
       <c r="C99" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D99" s="7" t="str">
+      <c r="D99" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E99" s="3">
+      <c r="E99" s="11">
         <v>-473000</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99" s="11">
         <v>-410000</v>
       </c>
-      <c r="G99" s="3">
+      <c r="G99" s="11">
         <v>-485000</v>
       </c>
     </row>
     <row r="100" spans="1:7">
-      <c r="A100" s="13">
+      <c r="A100" s="8">
         <v>39995</v>
       </c>
-      <c r="B100" s="13">
+      <c r="B100" s="8">
         <v>40030</v>
       </c>
       <c r="C100" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D100" s="7" t="str">
+      <c r="D100" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="11">
         <v>-371000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="11">
         <v>-340000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="11">
         <v>-463000</v>
       </c>
     </row>
     <row r="101" spans="1:7">
-      <c r="A101" s="13">
+      <c r="A101" s="8">
         <v>40026</v>
       </c>
-      <c r="B101" s="13">
+      <c r="B101" s="8">
         <v>40058</v>
       </c>
       <c r="C101" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D101" s="7" t="str">
+      <c r="D101" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E101" s="3">
+      <c r="E101" s="11">
         <v>-298000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="11">
         <v>-250000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="11">
         <v>-360000</v>
       </c>
     </row>
     <row r="102" spans="1:7">
-      <c r="A102" s="13">
+      <c r="A102" s="8">
         <v>40057</v>
       </c>
-      <c r="B102" s="13">
+      <c r="B102" s="8">
         <v>40086</v>
       </c>
       <c r="C102" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D102" s="7" t="str">
+      <c r="D102" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E102" s="3">
+      <c r="E102" s="11">
         <v>-254000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F102" s="11">
         <v>-200000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G102" s="11">
         <v>-277000</v>
       </c>
     </row>
     <row r="103" spans="1:7">
-      <c r="A103" s="13">
+      <c r="A103" s="8">
         <v>40087</v>
       </c>
-      <c r="B103" s="13">
+      <c r="B103" s="8">
         <v>40121</v>
       </c>
       <c r="C103" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D103" s="7" t="str">
+      <c r="D103" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E103" s="3">
+      <c r="E103" s="11">
         <v>-203000</v>
       </c>
-      <c r="F103" s="3">
+      <c r="F103" s="11">
         <v>-190000</v>
       </c>
-      <c r="G103" s="3">
+      <c r="G103" s="11">
         <v>-227000</v>
       </c>
     </row>
     <row r="104" spans="1:7">
-      <c r="A104" s="13">
+      <c r="A104" s="8">
         <v>40118</v>
       </c>
-      <c r="B104" s="13">
+      <c r="B104" s="8">
         <v>40149</v>
       </c>
       <c r="C104" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D104" s="7" t="str">
+      <c r="D104" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E104" s="3">
+      <c r="E104" s="11">
         <v>-169000</v>
       </c>
-      <c r="F104" s="3">
+      <c r="F104" s="11">
         <v>-148000</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G104" s="11">
         <v>-195000</v>
       </c>
     </row>
     <row r="105" spans="1:7">
-      <c r="A105" s="13">
+      <c r="A105" s="8">
         <v>40148</v>
       </c>
-      <c r="B105" s="13">
+      <c r="B105" s="8">
         <v>40184</v>
       </c>
       <c r="C105" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D105" s="7" t="str">
+      <c r="D105" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E105" s="3">
+      <c r="E105" s="11">
         <v>-84000</v>
       </c>
-      <c r="F105" s="3">
+      <c r="F105" s="11">
         <v>-75000</v>
       </c>
-      <c r="G105" s="3">
+      <c r="G105" s="11">
         <v>-145000</v>
       </c>
     </row>
     <row r="106" spans="1:7">
-      <c r="A106" s="13">
+      <c r="A106" s="8">
         <v>40179</v>
       </c>
-      <c r="B106" s="13">
+      <c r="B106" s="8">
         <v>40212</v>
       </c>
       <c r="C106" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D106" s="7" t="str">
+      <c r="D106" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E106" s="3">
+      <c r="E106" s="11">
         <v>-22000</v>
       </c>
-      <c r="F106" s="3">
+      <c r="F106" s="11">
         <v>-40000</v>
       </c>
-      <c r="G106" s="3">
+      <c r="G106" s="11">
         <v>-61000</v>
       </c>
     </row>
     <row r="107" spans="1:7">
-      <c r="A107" s="13">
+      <c r="A107" s="8">
         <v>40210</v>
       </c>
-      <c r="B107" s="13">
+      <c r="B107" s="8">
         <v>40240</v>
       </c>
       <c r="C107" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D107" s="7" t="str">
+      <c r="D107" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E107" s="3">
+      <c r="E107" s="11">
         <v>-20000</v>
       </c>
-      <c r="F107" s="3">
+      <c r="F107" s="11">
         <v>-10000</v>
       </c>
-      <c r="G107" s="3">
+      <c r="G107" s="11">
         <v>-60000</v>
       </c>
     </row>
     <row r="108" spans="1:7">
-      <c r="A108" s="13">
+      <c r="A108" s="8">
         <v>40238</v>
       </c>
-      <c r="B108" s="13">
+      <c r="B108" s="8">
         <v>40268</v>
       </c>
       <c r="C108" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D108" s="7" t="str">
+      <c r="D108" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E108" s="3">
+      <c r="E108" s="11">
         <v>-23000</v>
       </c>
-      <c r="F108" s="3">
+      <c r="F108" s="11">
         <v>40000</v>
       </c>
-      <c r="G108" s="3">
+      <c r="G108" s="11">
         <v>-24000</v>
       </c>
     </row>
     <row r="109" spans="1:7">
-      <c r="A109" s="13">
+      <c r="A109" s="8">
         <v>40269</v>
       </c>
-      <c r="B109" s="13">
+      <c r="B109" s="8">
         <v>40303</v>
       </c>
       <c r="C109" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D109" s="7" t="str">
+      <c r="D109" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E109" s="3">
+      <c r="E109" s="11">
         <v>32000</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F109" s="11">
         <v>30000</v>
       </c>
-      <c r="G109" s="3">
+      <c r="G109" s="11">
         <v>19000</v>
       </c>
     </row>
     <row r="110" spans="1:7">
-      <c r="A110" s="13">
+      <c r="A110" s="8">
         <v>40299</v>
       </c>
-      <c r="B110" s="13">
+      <c r="B110" s="8">
         <v>40332</v>
       </c>
       <c r="C110" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D110" s="7" t="str">
+      <c r="D110" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E110" s="3">
+      <c r="E110" s="11">
         <v>55000</v>
       </c>
-      <c r="F110" s="3">
+      <c r="F110" s="11">
         <v>56000</v>
       </c>
-      <c r="G110" s="3">
+      <c r="G110" s="11">
         <v>65000</v>
       </c>
     </row>
     <row r="111" spans="1:7">
-      <c r="A111" s="13">
+      <c r="A111" s="8">
         <v>40330</v>
       </c>
-      <c r="B111" s="13">
+      <c r="B111" s="8">
         <v>40359</v>
       </c>
       <c r="C111" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D111" s="7" t="str">
+      <c r="D111" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E111" s="3">
+      <c r="E111" s="11">
         <v>13000</v>
       </c>
-      <c r="F111" s="3">
+      <c r="F111" s="11">
         <v>58000</v>
       </c>
-      <c r="G111" s="3">
+      <c r="G111" s="11">
         <v>57000</v>
       </c>
     </row>
     <row r="112" spans="1:7">
-      <c r="A112" s="13">
+      <c r="A112" s="8">
         <v>40360</v>
       </c>
-      <c r="B112" s="13">
+      <c r="B112" s="8">
         <v>40394</v>
       </c>
       <c r="C112" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D112" s="7" t="str">
+      <c r="D112" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E112" s="3">
+      <c r="E112" s="11">
         <v>42000</v>
       </c>
-      <c r="F112" s="3">
+      <c r="F112" s="11">
         <v>25000</v>
       </c>
-      <c r="G112" s="3">
+      <c r="G112" s="11">
         <v>19000</v>
       </c>
     </row>
     <row r="113" spans="1:7">
-      <c r="A113" s="13">
+      <c r="A113" s="8">
         <v>40391</v>
       </c>
-      <c r="B113" s="13">
+      <c r="B113" s="8">
         <v>40422</v>
       </c>
       <c r="C113" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D113" s="7" t="str">
+      <c r="D113" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E113" s="3">
+      <c r="E113" s="11">
         <v>-10000</v>
       </c>
-      <c r="F113" s="3">
+      <c r="F113" s="11">
         <v>13000</v>
       </c>
-      <c r="G113" s="3">
+      <c r="G113" s="11">
         <v>37000</v>
       </c>
     </row>
     <row r="114" spans="1:7">
-      <c r="A114" s="13">
+      <c r="A114" s="8">
         <v>40422</v>
       </c>
-      <c r="B114" s="13">
+      <c r="B114" s="8">
         <v>40457</v>
       </c>
       <c r="C114" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D114" s="7" t="str">
+      <c r="D114" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E114" s="3">
+      <c r="E114" s="11">
         <v>-39000</v>
       </c>
-      <c r="F114" s="3">
+      <c r="F114" s="11">
         <v>18000</v>
       </c>
-      <c r="G114" s="3">
+      <c r="G114" s="11">
         <v>10000</v>
       </c>
     </row>
     <row r="115" spans="1:7">
-      <c r="A115" s="13">
+      <c r="A115" s="8">
         <v>40452</v>
       </c>
-      <c r="B115" s="13">
+      <c r="B115" s="8">
         <v>40485</v>
       </c>
       <c r="C115" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D115" s="7" t="str">
+      <c r="D115" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E115" s="3">
+      <c r="E115" s="11">
         <v>43000</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F115" s="11">
         <v>25000</v>
       </c>
-      <c r="G115" s="3">
+      <c r="G115" s="11">
         <v>-2000</v>
       </c>
     </row>
     <row r="116" spans="1:7">
-      <c r="A116" s="13">
+      <c r="A116" s="8">
         <v>40483</v>
       </c>
-      <c r="B116" s="13">
+      <c r="B116" s="8">
         <v>40513</v>
       </c>
       <c r="C116" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D116" s="7" t="str">
+      <c r="D116" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E116" s="3">
+      <c r="E116" s="11">
         <v>93000</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F116" s="11">
         <v>65000</v>
       </c>
-      <c r="G116" s="3">
+      <c r="G116" s="11">
         <v>82000</v>
       </c>
     </row>
     <row r="117" spans="1:7">
-      <c r="A117" s="13">
+      <c r="A117" s="8">
         <v>40513</v>
       </c>
-      <c r="B117" s="13">
+      <c r="B117" s="8">
         <v>40548</v>
       </c>
       <c r="C117" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D117" s="7" t="str">
+      <c r="D117" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E117" s="3">
+      <c r="E117" s="11">
         <v>297000</v>
       </c>
-      <c r="F117" s="3">
+      <c r="F117" s="11">
         <v>100000</v>
       </c>
-      <c r="G117" s="3">
+      <c r="G117" s="11">
         <v>92000</v>
       </c>
     </row>
     <row r="118" spans="1:7">
-      <c r="A118" s="13">
+      <c r="A118" s="8">
         <v>40544</v>
       </c>
-      <c r="B118" s="13">
+      <c r="B118" s="8">
         <v>40576</v>
       </c>
       <c r="C118" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D118" s="7" t="str">
+      <c r="D118" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E118" s="3">
+      <c r="E118" s="11">
         <v>187000</v>
       </c>
-      <c r="F118" s="3">
+      <c r="F118" s="11">
         <v>150000</v>
       </c>
-      <c r="G118" s="3">
+      <c r="G118" s="11">
         <v>247000</v>
       </c>
     </row>
     <row r="119" spans="1:7">
-      <c r="A119" s="13">
+      <c r="A119" s="8">
         <v>40575</v>
       </c>
-      <c r="B119" s="13">
+      <c r="B119" s="8">
         <v>40604</v>
       </c>
       <c r="C119" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D119" s="7" t="str">
+      <c r="D119" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E119" s="3">
+      <c r="E119" s="11">
         <v>217000</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119" s="11">
         <v>175000</v>
       </c>
-      <c r="G119" s="3">
+      <c r="G119" s="11">
         <v>189000</v>
       </c>
     </row>
     <row r="120" spans="1:7">
-      <c r="A120" s="13">
+      <c r="A120" s="8">
         <v>40603</v>
       </c>
-      <c r="B120" s="13">
+      <c r="B120" s="8">
         <v>40632</v>
       </c>
       <c r="C120" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D120" s="7" t="str">
+      <c r="D120" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E120" s="3">
+      <c r="E120" s="11">
         <v>201000</v>
       </c>
-      <c r="F120" s="3">
+      <c r="F120" s="11">
         <v>210000</v>
       </c>
-      <c r="G120" s="3">
+      <c r="G120" s="11">
         <v>208000</v>
       </c>
     </row>
     <row r="121" spans="1:7">
-      <c r="A121" s="13">
+      <c r="A121" s="8">
         <v>40634</v>
       </c>
-      <c r="B121" s="13">
+      <c r="B121" s="8">
         <v>40667</v>
       </c>
       <c r="C121" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D121" s="7" t="str">
+      <c r="D121" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E121" s="3">
+      <c r="E121" s="11">
         <v>179000</v>
       </c>
-      <c r="F121" s="3">
+      <c r="F121" s="11">
         <v>200000</v>
       </c>
-      <c r="G121" s="3">
+      <c r="G121" s="11">
         <v>207000</v>
       </c>
     </row>
     <row r="122" spans="1:7">
-      <c r="A122" s="13">
+      <c r="A122" s="8">
         <v>40664</v>
       </c>
-      <c r="B122" s="13">
+      <c r="B122" s="8">
         <v>40695</v>
       </c>
       <c r="C122" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D122" s="7" t="str">
+      <c r="D122" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E122" s="3">
+      <c r="E122" s="11">
         <v>38000</v>
       </c>
-      <c r="F122" s="3">
+      <c r="F122" s="11">
         <v>178000</v>
       </c>
-      <c r="G122" s="3">
+      <c r="G122" s="11">
         <v>177000</v>
       </c>
     </row>
     <row r="123" spans="1:7">
-      <c r="A123" s="13">
+      <c r="A123" s="8">
         <v>40695</v>
       </c>
-      <c r="B123" s="13">
+      <c r="B123" s="8">
         <v>40731</v>
       </c>
       <c r="C123" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D123" s="7" t="str">
+      <c r="D123" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E123" s="3">
+      <c r="E123" s="11">
         <v>157000</v>
       </c>
-      <c r="F123" s="3">
+      <c r="F123" s="11">
         <v>60000</v>
       </c>
-      <c r="G123" s="3">
+      <c r="G123" s="11">
         <v>36000</v>
       </c>
     </row>
     <row r="124" spans="1:7">
-      <c r="A124" s="13">
+      <c r="A124" s="8">
         <v>40725</v>
       </c>
-      <c r="B124" s="13">
+      <c r="B124" s="8">
         <v>40758</v>
       </c>
       <c r="C124" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D124" s="7" t="str">
+      <c r="D124" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E124" s="3">
+      <c r="E124" s="11">
         <v>114000</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124" s="11">
         <v>100000</v>
       </c>
-      <c r="G124" s="3">
+      <c r="G124" s="11">
         <v>145000</v>
       </c>
     </row>
     <row r="125" spans="1:7">
-      <c r="A125" s="13">
+      <c r="A125" s="8">
         <v>40756</v>
       </c>
-      <c r="B125" s="13">
+      <c r="B125" s="8">
         <v>40786</v>
       </c>
       <c r="C125" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D125" s="7" t="str">
+      <c r="D125" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E125" s="3">
+      <c r="E125" s="11">
         <v>91000</v>
       </c>
-      <c r="F125" s="3">
+      <c r="F125" s="11">
         <v>103000</v>
       </c>
-      <c r="G125" s="3">
+      <c r="G125" s="11">
         <v>109000</v>
       </c>
     </row>
     <row r="126" spans="1:7">
-      <c r="A126" s="13">
+      <c r="A126" s="8">
         <v>40787</v>
       </c>
-      <c r="B126" s="13">
+      <c r="B126" s="8">
         <v>40821</v>
       </c>
       <c r="C126" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D126" s="7" t="str">
+      <c r="D126" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E126" s="3">
+      <c r="E126" s="11">
         <v>91000</v>
       </c>
-      <c r="F126" s="3">
+      <c r="F126" s="11">
         <v>70000</v>
       </c>
-      <c r="G126" s="3">
+      <c r="G126" s="11">
         <v>89000</v>
       </c>
     </row>
     <row r="127" spans="1:7">
-      <c r="A127" s="13">
+      <c r="A127" s="8">
         <v>40817</v>
       </c>
-      <c r="B127" s="13">
+      <c r="B127" s="8">
         <v>40849</v>
       </c>
       <c r="C127" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D127" s="7" t="str">
+      <c r="D127" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-4</v>
       </c>
-      <c r="E127" s="3">
+      <c r="E127" s="11">
         <v>110000</v>
       </c>
-      <c r="F127" s="3">
+      <c r="F127" s="11">
         <v>100000</v>
       </c>
-      <c r="G127" s="3">
+      <c r="G127" s="11">
         <v>116000</v>
       </c>
     </row>
     <row r="128" spans="1:7">
-      <c r="A128" s="13">
+      <c r="A128" s="8">
         <v>40848</v>
       </c>
-      <c r="B128" s="13">
+      <c r="B128" s="8">
         <v>40877</v>
       </c>
       <c r="C128" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D128" s="7" t="str">
+      <c r="D128" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E128" s="3">
+      <c r="E128" s="11">
         <v>206000</v>
       </c>
-      <c r="F128" s="3">
+      <c r="F128" s="11">
         <v>130000</v>
       </c>
-      <c r="G128" s="3">
+      <c r="G128" s="11">
         <v>130000</v>
       </c>
     </row>
     <row r="129" spans="1:7">
-      <c r="A129" s="13">
+      <c r="A129" s="8">
         <v>40878</v>
       </c>
-      <c r="B129" s="13">
+      <c r="B129" s="8">
         <v>40913</v>
       </c>
       <c r="C129" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D129" s="7" t="str">
+      <c r="D129" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E129" s="3">
+      <c r="E129" s="11">
         <v>325000</v>
       </c>
-      <c r="F129" s="3">
+      <c r="F129" s="11">
         <v>175000</v>
       </c>
-      <c r="G129" s="3">
+      <c r="G129" s="11">
         <v>204000</v>
       </c>
     </row>
     <row r="130" spans="1:7">
-      <c r="A130" s="13">
+      <c r="A130" s="8">
         <v>40909</v>
       </c>
-      <c r="B130" s="13">
+      <c r="B130" s="8">
         <v>40940</v>
       </c>
       <c r="C130" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D130" s="7" t="str">
+      <c r="D130" s="10" t="str">
         <f t="shared" si="1"/>
         <v>UTC-5</v>
       </c>
-      <c r="E130" s="3">
+      <c r="E130" s="11">
         <v>170000</v>
       </c>
-      <c r="F130" s="3">
+      <c r="F130" s="11">
         <v>190000</v>
       </c>
-      <c r="G130" s="3">
+      <c r="G130" s="11">
         <v>292000</v>
       </c>
     </row>
     <row r="131" spans="1:7">
-      <c r="A131" s="13">
+      <c r="A131" s="8">
         <v>40940</v>
       </c>
-      <c r="B131" s="13">
+      <c r="B131" s="8">
         <v>40975</v>
       </c>
       <c r="C131" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D131" s="7" t="str">
+      <c r="D131" s="10" t="str">
         <f t="shared" ref="D131:D194" si="2">IF(
  AND(
   B131 &gt;= IF(
@@ -6101,1539 +6096,1539 @@
 )</f>
         <v>UTC-5</v>
       </c>
-      <c r="E131" s="3">
+      <c r="E131" s="11">
         <v>216000</v>
       </c>
-      <c r="F131" s="3">
+      <c r="F131" s="11">
         <v>205000</v>
       </c>
-      <c r="G131" s="3">
+      <c r="G131" s="11">
         <v>173000</v>
       </c>
     </row>
     <row r="132" spans="1:7">
-      <c r="A132" s="13">
+      <c r="A132" s="8">
         <v>40969</v>
       </c>
-      <c r="B132" s="13">
+      <c r="B132" s="8">
         <v>41003</v>
       </c>
       <c r="C132" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D132" s="7" t="str">
+      <c r="D132" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E132" s="3">
+      <c r="E132" s="11">
         <v>209000</v>
       </c>
-      <c r="F132" s="3">
+      <c r="F132" s="11">
         <v>200000</v>
       </c>
-      <c r="G132" s="3">
+      <c r="G132" s="11">
         <v>230000</v>
       </c>
     </row>
     <row r="133" spans="1:7">
-      <c r="A133" s="13">
+      <c r="A133" s="8">
         <v>41000</v>
       </c>
-      <c r="B133" s="13">
+      <c r="B133" s="8">
         <v>41031</v>
       </c>
       <c r="C133" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D133" s="7" t="str">
+      <c r="D133" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E133" s="3">
+      <c r="E133" s="11">
         <v>119000</v>
       </c>
-      <c r="F133" s="3">
+      <c r="F133" s="11">
         <v>177000</v>
       </c>
-      <c r="G133" s="3">
+      <c r="G133" s="11">
         <v>201000</v>
       </c>
     </row>
     <row r="134" spans="1:7">
-      <c r="A134" s="13">
+      <c r="A134" s="8">
         <v>41030</v>
       </c>
-      <c r="B134" s="13">
+      <c r="B134" s="8">
         <v>41060</v>
       </c>
       <c r="C134" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D134" s="7" t="str">
+      <c r="D134" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E134" s="3">
+      <c r="E134" s="11">
         <v>133000</v>
       </c>
-      <c r="F134" s="3">
+      <c r="F134" s="11">
         <v>148000</v>
       </c>
-      <c r="G134" s="3">
+      <c r="G134" s="11">
         <v>113000</v>
       </c>
     </row>
     <row r="135" spans="1:7">
-      <c r="A135" s="13">
+      <c r="A135" s="8">
         <v>41061</v>
       </c>
-      <c r="B135" s="13">
+      <c r="B135" s="8">
         <v>41095</v>
       </c>
       <c r="C135" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D135" s="7" t="str">
+      <c r="D135" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E135" s="3">
+      <c r="E135" s="11">
         <v>176000</v>
       </c>
-      <c r="F135" s="3">
+      <c r="F135" s="11">
         <v>105000</v>
       </c>
-      <c r="G135" s="3">
+      <c r="G135" s="11">
         <v>136000</v>
       </c>
     </row>
     <row r="136" spans="1:7">
-      <c r="A136" s="13">
+      <c r="A136" s="8">
         <v>41091</v>
       </c>
-      <c r="B136" s="13">
+      <c r="B136" s="8">
         <v>41122</v>
       </c>
       <c r="C136" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D136" s="7" t="str">
+      <c r="D136" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E136" s="3">
+      <c r="E136" s="11">
         <v>163000</v>
       </c>
-      <c r="F136" s="3">
+      <c r="F136" s="11">
         <v>120000</v>
       </c>
-      <c r="G136" s="3">
+      <c r="G136" s="11">
         <v>172000</v>
       </c>
     </row>
     <row r="137" spans="1:7">
-      <c r="A137" s="13">
+      <c r="A137" s="8">
         <v>41122</v>
       </c>
-      <c r="B137" s="13">
+      <c r="B137" s="8">
         <v>41158</v>
       </c>
       <c r="C137" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D137" s="7" t="str">
+      <c r="D137" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E137" s="3">
+      <c r="E137" s="11">
         <v>201000</v>
       </c>
-      <c r="F137" s="3">
+      <c r="F137" s="11">
         <v>140000</v>
       </c>
-      <c r="G137" s="3">
+      <c r="G137" s="11">
         <v>173000</v>
       </c>
     </row>
     <row r="138" spans="1:7">
-      <c r="A138" s="13">
+      <c r="A138" s="8">
         <v>41153</v>
       </c>
-      <c r="B138" s="13">
+      <c r="B138" s="8">
         <v>41185</v>
       </c>
       <c r="C138" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D138" s="7" t="str">
+      <c r="D138" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E138" s="3">
+      <c r="E138" s="11">
         <v>162000</v>
       </c>
-      <c r="F138" s="3">
+      <c r="F138" s="11">
         <v>143000</v>
       </c>
-      <c r="G138" s="3">
+      <c r="G138" s="11">
         <v>189000</v>
       </c>
     </row>
     <row r="139" spans="1:7">
-      <c r="A139" s="13">
+      <c r="A139" s="8">
         <v>41183</v>
       </c>
-      <c r="B139" s="13">
+      <c r="B139" s="8">
         <v>41214</v>
       </c>
       <c r="C139" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D139" s="7" t="str">
+      <c r="D139" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E139" s="3">
+      <c r="E139" s="11">
         <v>158000</v>
       </c>
-      <c r="F139" s="3">
+      <c r="F139" s="11">
         <v>135000</v>
       </c>
-      <c r="G139" s="3">
+      <c r="G139" s="11">
         <v>114000</v>
       </c>
     </row>
     <row r="140" spans="1:7">
-      <c r="A140" s="13">
+      <c r="A140" s="8">
         <v>41214</v>
       </c>
-      <c r="B140" s="13">
+      <c r="B140" s="8">
         <v>41248</v>
       </c>
       <c r="C140" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D140" s="7" t="str">
+      <c r="D140" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E140" s="3">
+      <c r="E140" s="11">
         <v>118000</v>
       </c>
-      <c r="F140" s="3">
+      <c r="F140" s="11">
         <v>125000</v>
       </c>
-      <c r="G140" s="3">
+      <c r="G140" s="11">
         <v>157000</v>
       </c>
     </row>
     <row r="141" spans="1:7">
-      <c r="A141" s="13">
+      <c r="A141" s="8">
         <v>41244</v>
       </c>
-      <c r="B141" s="13">
+      <c r="B141" s="8">
         <v>41277</v>
       </c>
       <c r="C141" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D141" s="7" t="str">
+      <c r="D141" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E141" s="3">
+      <c r="E141" s="11">
         <v>215000</v>
       </c>
-      <c r="F141" s="3">
+      <c r="F141" s="11">
         <v>133000</v>
       </c>
-      <c r="G141" s="3">
+      <c r="G141" s="11">
         <v>148000</v>
       </c>
     </row>
     <row r="142" spans="1:7">
-      <c r="A142" s="13">
+      <c r="A142" s="8">
         <v>41275</v>
       </c>
-      <c r="B142" s="13">
+      <c r="B142" s="8">
         <v>41304</v>
       </c>
       <c r="C142" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D142" s="7" t="str">
+      <c r="D142" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E142" s="3">
+      <c r="E142" s="11">
         <v>192000</v>
       </c>
-      <c r="F142" s="3">
+      <c r="F142" s="11">
         <v>165000</v>
       </c>
-      <c r="G142" s="3">
+      <c r="G142" s="11">
         <v>185000</v>
       </c>
     </row>
     <row r="143" spans="1:7">
-      <c r="A143" s="13">
+      <c r="A143" s="8">
         <v>41306</v>
       </c>
-      <c r="B143" s="13">
+      <c r="B143" s="8">
         <v>41339</v>
       </c>
       <c r="C143" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D143" s="7" t="str">
+      <c r="D143" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E143" s="3">
+      <c r="E143" s="11">
         <v>198000</v>
       </c>
-      <c r="F143" s="3">
+      <c r="F143" s="11">
         <v>170000</v>
       </c>
-      <c r="G143" s="3">
+      <c r="G143" s="11">
         <v>215000</v>
       </c>
     </row>
     <row r="144" spans="1:7">
-      <c r="A144" s="13">
+      <c r="A144" s="8">
         <v>41334</v>
       </c>
-      <c r="B144" s="13">
+      <c r="B144" s="8">
         <v>41367</v>
       </c>
       <c r="C144" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D144" s="7" t="str">
+      <c r="D144" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E144" s="3">
+      <c r="E144" s="11">
         <v>158000</v>
       </c>
-      <c r="F144" s="3">
+      <c r="F144" s="11">
         <v>200000</v>
       </c>
-      <c r="G144" s="3">
+      <c r="G144" s="11">
         <v>237000</v>
       </c>
     </row>
     <row r="145" spans="1:7">
-      <c r="A145" s="13">
+      <c r="A145" s="8">
         <v>41365</v>
       </c>
-      <c r="B145" s="13">
+      <c r="B145" s="8">
         <v>41395</v>
       </c>
       <c r="C145" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D145" s="7" t="str">
+      <c r="D145" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E145" s="3">
+      <c r="E145" s="11">
         <v>119000</v>
       </c>
-      <c r="F145" s="3">
+      <c r="F145" s="11">
         <v>150000</v>
       </c>
-      <c r="G145" s="3">
+      <c r="G145" s="11">
         <v>131000</v>
       </c>
     </row>
     <row r="146" spans="1:7">
-      <c r="A146" s="13">
+      <c r="A146" s="8">
         <v>41395</v>
       </c>
-      <c r="B146" s="13">
+      <c r="B146" s="8">
         <v>41430</v>
       </c>
       <c r="C146" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D146" s="7" t="str">
+      <c r="D146" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E146" s="3">
+      <c r="E146" s="11">
         <v>135000</v>
       </c>
-      <c r="F146" s="3">
+      <c r="F146" s="11">
         <v>165000</v>
       </c>
-      <c r="G146" s="3">
+      <c r="G146" s="11">
         <v>113000</v>
       </c>
     </row>
     <row r="147" spans="1:7">
-      <c r="A147" s="13">
+      <c r="A147" s="8">
         <v>41426</v>
       </c>
-      <c r="B147" s="13">
+      <c r="B147" s="8">
         <v>41458</v>
       </c>
       <c r="C147" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D147" s="7" t="str">
+      <c r="D147" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E147" s="3">
+      <c r="E147" s="11">
         <v>188000</v>
       </c>
-      <c r="F147" s="3">
+      <c r="F147" s="11">
         <v>160000</v>
       </c>
-      <c r="G147" s="3">
+      <c r="G147" s="11">
         <v>134000</v>
       </c>
     </row>
     <row r="148" spans="1:7">
-      <c r="A148" s="13">
+      <c r="A148" s="8">
         <v>41456</v>
       </c>
-      <c r="B148" s="13">
+      <c r="B148" s="8">
         <v>41486</v>
       </c>
       <c r="C148" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D148" s="7" t="str">
+      <c r="D148" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E148" s="3">
+      <c r="E148" s="11">
         <v>200000</v>
       </c>
-      <c r="F148" s="3">
+      <c r="F148" s="11">
         <v>180000</v>
       </c>
-      <c r="G148" s="3">
+      <c r="G148" s="11">
         <v>198000</v>
       </c>
     </row>
     <row r="149" spans="1:7">
-      <c r="A149" s="13">
+      <c r="A149" s="8">
         <v>41487</v>
       </c>
-      <c r="B149" s="13">
+      <c r="B149" s="8">
         <v>41522</v>
       </c>
       <c r="C149" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D149" s="7" t="str">
+      <c r="D149" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E149" s="3">
+      <c r="E149" s="11">
         <v>176000</v>
       </c>
-      <c r="F149" s="3">
+      <c r="F149" s="11">
         <v>180000</v>
       </c>
-      <c r="G149" s="3">
+      <c r="G149" s="11">
         <v>198000</v>
       </c>
     </row>
     <row r="150" spans="1:7">
-      <c r="A150" s="13">
+      <c r="A150" s="8">
         <v>41518</v>
       </c>
-      <c r="B150" s="13">
+      <c r="B150" s="8">
         <v>41549</v>
       </c>
       <c r="C150" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D150" s="7" t="str">
+      <c r="D150" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E150" s="3">
+      <c r="E150" s="11">
         <v>166000</v>
       </c>
-      <c r="F150" s="3">
+      <c r="F150" s="11">
         <v>180000</v>
       </c>
-      <c r="G150" s="3">
+      <c r="G150" s="11">
         <v>159000</v>
       </c>
     </row>
     <row r="151" spans="1:7">
-      <c r="A151" s="13">
+      <c r="A151" s="8">
         <v>41548</v>
       </c>
-      <c r="B151" s="13">
+      <c r="B151" s="8">
         <v>41577</v>
       </c>
       <c r="C151" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D151" s="7" t="str">
+      <c r="D151" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E151" s="3">
+      <c r="E151" s="11">
         <v>130000</v>
       </c>
-      <c r="F151" s="3">
+      <c r="F151" s="11">
         <v>150000</v>
       </c>
-      <c r="G151" s="3">
+      <c r="G151" s="11">
         <v>145000</v>
       </c>
     </row>
     <row r="152" spans="1:7">
-      <c r="A152" s="13">
+      <c r="A152" s="8">
         <v>41579</v>
       </c>
-      <c r="B152" s="13">
+      <c r="B152" s="8">
         <v>41612</v>
       </c>
       <c r="C152" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D152" s="7" t="str">
+      <c r="D152" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E152" s="3">
+      <c r="E152" s="11">
         <v>215000</v>
       </c>
-      <c r="F152" s="3">
+      <c r="F152" s="11">
         <v>173000</v>
       </c>
-      <c r="G152" s="3">
+      <c r="G152" s="11">
         <v>184000</v>
       </c>
     </row>
     <row r="153" spans="1:7">
-      <c r="A153" s="13">
+      <c r="A153" s="8">
         <v>41609</v>
       </c>
-      <c r="B153" s="13">
+      <c r="B153" s="8">
         <v>41647</v>
       </c>
       <c r="C153" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D153" s="7" t="str">
+      <c r="D153" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E153" s="3">
+      <c r="E153" s="11">
         <v>238000</v>
       </c>
-      <c r="F153" s="3">
+      <c r="F153" s="11">
         <v>200000</v>
       </c>
-      <c r="G153" s="3">
+      <c r="G153" s="11">
         <v>229000</v>
       </c>
     </row>
     <row r="154" spans="1:7">
-      <c r="A154" s="13">
+      <c r="A154" s="8">
         <v>41640</v>
       </c>
-      <c r="B154" s="13">
+      <c r="B154" s="8">
         <v>41675</v>
       </c>
       <c r="C154" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D154" s="7" t="str">
+      <c r="D154" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E154" s="3">
+      <c r="E154" s="11">
         <v>175000</v>
       </c>
-      <c r="F154" s="3">
+      <c r="F154" s="11">
         <v>180000</v>
       </c>
-      <c r="G154" s="3">
+      <c r="G154" s="11">
         <v>227000</v>
       </c>
     </row>
     <row r="155" spans="1:7">
-      <c r="A155" s="13">
+      <c r="A155" s="8">
         <v>41671</v>
       </c>
-      <c r="B155" s="13">
+      <c r="B155" s="8">
         <v>41703</v>
       </c>
       <c r="C155" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D155" s="7" t="str">
+      <c r="D155" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E155" s="3">
+      <c r="E155" s="11">
         <v>139000</v>
       </c>
-      <c r="F155" s="3">
+      <c r="F155" s="11">
         <v>160000</v>
       </c>
-      <c r="G155" s="3">
+      <c r="G155" s="11">
         <v>127000</v>
       </c>
     </row>
     <row r="156" spans="1:7">
-      <c r="A156" s="13">
+      <c r="A156" s="8">
         <v>41699</v>
       </c>
-      <c r="B156" s="13">
+      <c r="B156" s="8">
         <v>41731</v>
       </c>
       <c r="C156" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D156" s="7" t="str">
+      <c r="D156" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E156" s="3">
+      <c r="E156" s="11">
         <v>191000</v>
       </c>
-      <c r="F156" s="3">
+      <c r="F156" s="11">
         <v>195000</v>
       </c>
-      <c r="G156" s="3">
+      <c r="G156" s="11">
         <v>178000</v>
       </c>
     </row>
     <row r="157" spans="1:7">
-      <c r="A157" s="13">
+      <c r="A157" s="8">
         <v>41730</v>
       </c>
-      <c r="B157" s="13">
+      <c r="B157" s="8">
         <v>41759</v>
       </c>
       <c r="C157" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D157" s="7" t="str">
+      <c r="D157" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E157" s="3">
+      <c r="E157" s="11">
         <v>220000</v>
       </c>
-      <c r="F157" s="3">
+      <c r="F157" s="11">
         <v>210000</v>
       </c>
-      <c r="G157" s="3">
+      <c r="G157" s="11">
         <v>209000</v>
       </c>
     </row>
     <row r="158" spans="1:7">
-      <c r="A158" s="13">
+      <c r="A158" s="8">
         <v>41760</v>
       </c>
-      <c r="B158" s="13">
+      <c r="B158" s="8">
         <v>41794</v>
       </c>
       <c r="C158" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D158" s="7" t="str">
+      <c r="D158" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E158" s="3">
+      <c r="E158" s="11">
         <v>179000</v>
       </c>
-      <c r="F158" s="3">
+      <c r="F158" s="11">
         <v>210000</v>
       </c>
-      <c r="G158" s="3">
+      <c r="G158" s="11">
         <v>215000</v>
       </c>
     </row>
     <row r="159" spans="1:7">
-      <c r="A159" s="13">
+      <c r="A159" s="8">
         <v>41791</v>
       </c>
-      <c r="B159" s="13">
+      <c r="B159" s="8">
         <v>41822</v>
       </c>
       <c r="C159" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D159" s="7" t="str">
+      <c r="D159" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E159" s="3">
+      <c r="E159" s="11">
         <v>281000</v>
       </c>
-      <c r="F159" s="3">
+      <c r="F159" s="11">
         <v>200000</v>
       </c>
-      <c r="G159" s="3">
+      <c r="G159" s="11">
         <v>179000</v>
       </c>
     </row>
     <row r="160" spans="1:7">
-      <c r="A160" s="13">
+      <c r="A160" s="8">
         <v>41821</v>
       </c>
-      <c r="B160" s="13">
+      <c r="B160" s="8">
         <v>41850</v>
       </c>
       <c r="C160" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D160" s="7" t="str">
+      <c r="D160" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E160" s="3">
+      <c r="E160" s="11">
         <v>218000</v>
       </c>
-      <c r="F160" s="3">
+      <c r="F160" s="11">
         <v>230000</v>
       </c>
-      <c r="G160" s="3">
+      <c r="G160" s="11">
         <v>281000</v>
       </c>
     </row>
     <row r="161" spans="1:7">
-      <c r="A161" s="13">
+      <c r="A161" s="8">
         <v>41852</v>
       </c>
-      <c r="B161" s="13">
+      <c r="B161" s="8">
         <v>41886</v>
       </c>
       <c r="C161" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D161" s="7" t="str">
+      <c r="D161" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E161" s="3">
+      <c r="E161" s="11">
         <v>204000</v>
       </c>
-      <c r="F161" s="3">
+      <c r="F161" s="11">
         <v>220000</v>
       </c>
-      <c r="G161" s="3">
+      <c r="G161" s="11">
         <v>212000</v>
       </c>
     </row>
     <row r="162" spans="1:7">
-      <c r="A162" s="13">
+      <c r="A162" s="8">
         <v>41883</v>
       </c>
-      <c r="B162" s="13">
+      <c r="B162" s="8">
         <v>41913</v>
       </c>
       <c r="C162" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D162" s="7" t="str">
+      <c r="D162" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E162" s="3">
+      <c r="E162" s="11">
         <v>213000</v>
       </c>
-      <c r="F162" s="3">
+      <c r="F162" s="11">
         <v>210000</v>
       </c>
-      <c r="G162" s="3">
+      <c r="G162" s="11">
         <v>202000</v>
       </c>
     </row>
     <row r="163" spans="1:7">
-      <c r="A163" s="13">
+      <c r="A163" s="8">
         <v>41913</v>
       </c>
-      <c r="B163" s="13">
+      <c r="B163" s="8">
         <v>41948</v>
       </c>
       <c r="C163" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D163" s="7" t="str">
+      <c r="D163" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E163" s="3">
+      <c r="E163" s="11">
         <v>230000</v>
       </c>
-      <c r="F163" s="3">
+      <c r="F163" s="11">
         <v>220000</v>
       </c>
-      <c r="G163" s="3">
+      <c r="G163" s="11">
         <v>225000</v>
       </c>
     </row>
     <row r="164" spans="1:7">
-      <c r="A164" s="13">
+      <c r="A164" s="8">
         <v>41944</v>
       </c>
-      <c r="B164" s="13">
+      <c r="B164" s="8">
         <v>41976</v>
       </c>
       <c r="C164" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D164" s="7" t="str">
+      <c r="D164" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E164" s="3">
+      <c r="E164" s="11">
         <v>208000</v>
       </c>
-      <c r="F164" s="3">
+      <c r="F164" s="11">
         <v>223000</v>
       </c>
-      <c r="G164" s="3">
+      <c r="G164" s="11">
         <v>233000</v>
       </c>
     </row>
     <row r="165" spans="1:7">
-      <c r="A165" s="13">
+      <c r="A165" s="8">
         <v>41974</v>
       </c>
-      <c r="B165" s="13">
+      <c r="B165" s="8">
         <v>42011</v>
       </c>
       <c r="C165" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D165" s="7" t="str">
+      <c r="D165" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E165" s="3">
+      <c r="E165" s="11">
         <v>241000</v>
       </c>
-      <c r="F165" s="3">
+      <c r="F165" s="11">
         <v>226000</v>
       </c>
-      <c r="G165" s="3">
+      <c r="G165" s="11">
         <v>227000</v>
       </c>
     </row>
     <row r="166" spans="1:7">
-      <c r="A166" s="13">
+      <c r="A166" s="8">
         <v>42005</v>
       </c>
-      <c r="B166" s="13">
+      <c r="B166" s="8">
         <v>42039</v>
       </c>
       <c r="C166" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D166" s="7" t="str">
+      <c r="D166" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E166" s="3">
+      <c r="E166" s="11">
         <v>213000</v>
       </c>
-      <c r="F166" s="3">
+      <c r="F166" s="11">
         <v>225000</v>
       </c>
-      <c r="G166" s="3">
+      <c r="G166" s="11">
         <v>253000</v>
       </c>
     </row>
     <row r="167" spans="1:7">
-      <c r="A167" s="13">
+      <c r="A167" s="8">
         <v>42036</v>
       </c>
-      <c r="B167" s="13">
+      <c r="B167" s="8">
         <v>42067</v>
       </c>
       <c r="C167" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D167" s="7" t="str">
+      <c r="D167" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E167" s="3">
+      <c r="E167" s="11">
         <v>212000</v>
       </c>
-      <c r="F167" s="3">
+      <c r="F167" s="11">
         <v>220000</v>
       </c>
-      <c r="G167" s="3">
+      <c r="G167" s="11">
         <v>250000</v>
       </c>
     </row>
     <row r="168" spans="1:7">
-      <c r="A168" s="13">
+      <c r="A168" s="8">
         <v>42064</v>
       </c>
-      <c r="B168" s="13">
+      <c r="B168" s="8">
         <v>42095</v>
       </c>
       <c r="C168" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D168" s="7" t="str">
+      <c r="D168" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E168" s="3">
+      <c r="E168" s="11">
         <v>189000</v>
       </c>
-      <c r="F168" s="3">
+      <c r="F168" s="11">
         <v>225000</v>
       </c>
-      <c r="G168" s="3">
+      <c r="G168" s="11">
         <v>214000</v>
       </c>
     </row>
     <row r="169" spans="1:7">
-      <c r="A169" s="13">
+      <c r="A169" s="8">
         <v>42095</v>
       </c>
-      <c r="B169" s="13">
+      <c r="B169" s="8">
         <v>42130</v>
       </c>
       <c r="C169" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D169" s="7" t="str">
+      <c r="D169" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E169" s="3">
+      <c r="E169" s="11">
         <v>169000</v>
       </c>
-      <c r="F169" s="3">
+      <c r="F169" s="11">
         <v>200000</v>
       </c>
-      <c r="G169" s="3">
+      <c r="G169" s="11">
         <v>175000</v>
       </c>
     </row>
     <row r="170" spans="1:7">
-      <c r="A170" s="13">
+      <c r="A170" s="8">
         <v>42125</v>
       </c>
-      <c r="B170" s="13">
+      <c r="B170" s="8">
         <v>42158</v>
       </c>
       <c r="C170" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D170" s="7" t="str">
+      <c r="D170" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E170" s="3">
+      <c r="E170" s="11">
         <v>201000</v>
       </c>
-      <c r="F170" s="3">
+      <c r="F170" s="11">
         <v>200000</v>
       </c>
-      <c r="G170" s="3">
+      <c r="G170" s="11">
         <v>165000</v>
       </c>
     </row>
     <row r="171" spans="1:7">
-      <c r="A171" s="13">
+      <c r="A171" s="8">
         <v>42156</v>
       </c>
-      <c r="B171" s="13">
+      <c r="B171" s="8">
         <v>42186</v>
       </c>
       <c r="C171" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D171" s="7" t="str">
+      <c r="D171" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E171" s="3">
+      <c r="E171" s="11">
         <v>237000</v>
       </c>
-      <c r="F171" s="3">
+      <c r="F171" s="11">
         <v>218000</v>
       </c>
-      <c r="G171" s="3">
+      <c r="G171" s="11">
         <v>203000</v>
       </c>
     </row>
     <row r="172" spans="1:7">
-      <c r="A172" s="13">
+      <c r="A172" s="8">
         <v>42186</v>
       </c>
-      <c r="B172" s="13">
+      <c r="B172" s="8">
         <v>42221</v>
       </c>
       <c r="C172" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D172" s="7" t="str">
+      <c r="D172" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E172" s="3">
+      <c r="E172" s="11">
         <v>185000</v>
       </c>
-      <c r="F172" s="3">
+      <c r="F172" s="11">
         <v>215000</v>
       </c>
-      <c r="G172" s="3">
+      <c r="G172" s="11">
         <v>229000</v>
       </c>
     </row>
     <row r="173" spans="1:7">
-      <c r="A173" s="13">
+      <c r="A173" s="8">
         <v>42217</v>
       </c>
-      <c r="B173" s="13">
+      <c r="B173" s="8">
         <v>42249</v>
       </c>
       <c r="C173" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D173" s="7" t="str">
+      <c r="D173" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E173" s="3">
+      <c r="E173" s="11">
         <v>190000</v>
       </c>
-      <c r="F173" s="3">
+      <c r="F173" s="11">
         <v>201000</v>
       </c>
-      <c r="G173" s="3">
+      <c r="G173" s="11">
         <v>177000</v>
       </c>
     </row>
     <row r="174" spans="1:7">
-      <c r="A174" s="13">
+      <c r="A174" s="8">
         <v>42248</v>
       </c>
-      <c r="B174" s="13">
+      <c r="B174" s="8">
         <v>42277</v>
       </c>
       <c r="C174" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D174" s="7" t="str">
+      <c r="D174" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E174" s="3">
+      <c r="E174" s="11">
         <v>200000</v>
       </c>
-      <c r="F174" s="3">
+      <c r="F174" s="11">
         <v>194000</v>
       </c>
-      <c r="G174" s="3">
+      <c r="G174" s="11">
         <v>186000</v>
       </c>
     </row>
     <row r="175" spans="1:7">
-      <c r="A175" s="13">
+      <c r="A175" s="8">
         <v>42278</v>
       </c>
-      <c r="B175" s="13">
+      <c r="B175" s="8">
         <v>42312</v>
       </c>
       <c r="C175" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D175" s="7" t="str">
+      <c r="D175" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E175" s="3">
+      <c r="E175" s="11">
         <v>182000</v>
       </c>
-      <c r="F175" s="3">
+      <c r="F175" s="11">
         <v>180000</v>
       </c>
-      <c r="G175" s="3">
+      <c r="G175" s="11">
         <v>190000</v>
       </c>
     </row>
     <row r="176" spans="1:7">
-      <c r="A176" s="13">
+      <c r="A176" s="8">
         <v>42309</v>
       </c>
-      <c r="B176" s="13">
+      <c r="B176" s="8">
         <v>42340</v>
       </c>
       <c r="C176" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D176" s="7" t="str">
+      <c r="D176" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E176" s="3">
+      <c r="E176" s="11">
         <v>217000</v>
       </c>
-      <c r="F176" s="3">
+      <c r="F176" s="11">
         <v>190000</v>
       </c>
-      <c r="G176" s="3">
+      <c r="G176" s="11">
         <v>196000</v>
       </c>
     </row>
     <row r="177" spans="1:7">
-      <c r="A177" s="13">
+      <c r="A177" s="8">
         <v>42339</v>
       </c>
-      <c r="B177" s="13">
+      <c r="B177" s="8">
         <v>42375</v>
       </c>
       <c r="C177" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D177" s="7" t="str">
+      <c r="D177" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E177" s="3">
+      <c r="E177" s="11">
         <v>257000</v>
       </c>
-      <c r="F177" s="3">
+      <c r="F177" s="11">
         <v>192000</v>
       </c>
-      <c r="G177" s="3">
+      <c r="G177" s="11">
         <v>211000</v>
       </c>
     </row>
     <row r="178" spans="1:7">
-      <c r="A178" s="13">
+      <c r="A178" s="8">
         <v>42370</v>
       </c>
-      <c r="B178" s="13">
+      <c r="B178" s="8">
         <v>42403</v>
       </c>
       <c r="C178" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D178" s="7" t="str">
+      <c r="D178" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E178" s="3">
+      <c r="E178" s="11">
         <v>205000</v>
       </c>
-      <c r="F178" s="3">
+      <c r="F178" s="11">
         <v>195000</v>
       </c>
-      <c r="G178" s="3">
+      <c r="G178" s="11">
         <v>267000</v>
       </c>
     </row>
     <row r="179" spans="1:7">
-      <c r="A179" s="13">
+      <c r="A179" s="8">
         <v>42401</v>
       </c>
-      <c r="B179" s="13">
+      <c r="B179" s="8">
         <v>42431</v>
       </c>
       <c r="C179" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D179" s="7" t="str">
+      <c r="D179" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E179" s="3">
+      <c r="E179" s="11">
         <v>214000</v>
       </c>
-      <c r="F179" s="3">
+      <c r="F179" s="11">
         <v>190000</v>
       </c>
-      <c r="G179" s="3">
+      <c r="G179" s="11">
         <v>193000</v>
       </c>
     </row>
     <row r="180" spans="1:7">
-      <c r="A180" s="13">
+      <c r="A180" s="8">
         <v>42430</v>
       </c>
-      <c r="B180" s="13">
+      <c r="B180" s="8">
         <v>42459</v>
       </c>
       <c r="C180" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D180" s="7" t="str">
+      <c r="D180" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E180" s="3">
+      <c r="E180" s="11">
         <v>200000</v>
       </c>
-      <c r="F180" s="3">
+      <c r="F180" s="11">
         <v>194000</v>
       </c>
-      <c r="G180" s="3">
+      <c r="G180" s="11">
         <v>205000</v>
       </c>
     </row>
     <row r="181" spans="1:7">
-      <c r="A181" s="13">
+      <c r="A181" s="8">
         <v>42461</v>
       </c>
-      <c r="B181" s="13">
+      <c r="B181" s="8">
         <v>42494</v>
       </c>
       <c r="C181" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D181" s="7" t="str">
+      <c r="D181" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E181" s="3">
+      <c r="E181" s="11">
         <v>156000</v>
       </c>
-      <c r="F181" s="3">
+      <c r="F181" s="11">
         <v>196000</v>
       </c>
-      <c r="G181" s="3">
+      <c r="G181" s="11">
         <v>194000</v>
       </c>
     </row>
     <row r="182" spans="1:7">
-      <c r="A182" s="13">
+      <c r="A182" s="8">
         <v>42491</v>
       </c>
-      <c r="B182" s="13">
+      <c r="B182" s="8">
         <v>42523</v>
       </c>
       <c r="C182" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D182" s="7" t="str">
+      <c r="D182" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E182" s="3">
+      <c r="E182" s="11">
         <v>173000</v>
       </c>
-      <c r="F182" s="3">
+      <c r="F182" s="11">
         <v>175000</v>
       </c>
-      <c r="G182" s="3">
+      <c r="G182" s="11">
         <v>166000</v>
       </c>
     </row>
     <row r="183" spans="1:7">
-      <c r="A183" s="13">
+      <c r="A183" s="8">
         <v>42522</v>
       </c>
-      <c r="B183" s="13">
+      <c r="B183" s="8">
         <v>42558</v>
       </c>
       <c r="C183" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D183" s="7" t="str">
+      <c r="D183" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E183" s="3">
+      <c r="E183" s="11">
         <v>172000</v>
       </c>
-      <c r="F183" s="3">
+      <c r="F183" s="11">
         <v>159000</v>
       </c>
-      <c r="G183" s="3">
+      <c r="G183" s="11">
         <v>168000</v>
       </c>
     </row>
     <row r="184" spans="1:7">
-      <c r="A184" s="13">
+      <c r="A184" s="8">
         <v>42552</v>
       </c>
-      <c r="B184" s="13">
+      <c r="B184" s="8">
         <v>42585</v>
       </c>
       <c r="C184" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D184" s="7" t="str">
+      <c r="D184" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E184" s="3">
+      <c r="E184" s="11">
         <v>179000</v>
       </c>
-      <c r="F184" s="3">
+      <c r="F184" s="11">
         <v>170000</v>
       </c>
-      <c r="G184" s="3">
+      <c r="G184" s="11">
         <v>176000</v>
       </c>
     </row>
     <row r="185" spans="1:7">
-      <c r="A185" s="13">
+      <c r="A185" s="8">
         <v>42583</v>
       </c>
-      <c r="B185" s="13">
+      <c r="B185" s="8">
         <v>42613</v>
       </c>
       <c r="C185" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D185" s="7" t="str">
+      <c r="D185" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E185" s="3">
+      <c r="E185" s="11">
         <v>177000</v>
       </c>
-      <c r="F185" s="3">
+      <c r="F185" s="11">
         <v>175000</v>
       </c>
-      <c r="G185" s="3">
+      <c r="G185" s="11">
         <v>194000</v>
       </c>
     </row>
     <row r="186" spans="1:7">
-      <c r="A186" s="13">
+      <c r="A186" s="8">
         <v>42614</v>
       </c>
-      <c r="B186" s="13">
+      <c r="B186" s="8">
         <v>42648</v>
       </c>
       <c r="C186" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D186" s="7" t="str">
+      <c r="D186" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E186" s="3">
+      <c r="E186" s="11">
         <v>154000</v>
       </c>
-      <c r="F186" s="3">
+      <c r="F186" s="11">
         <v>166000</v>
       </c>
-      <c r="G186" s="3">
+      <c r="G186" s="11">
         <v>175000</v>
       </c>
     </row>
     <row r="187" spans="1:7">
-      <c r="A187" s="13">
+      <c r="A187" s="8">
         <v>42644</v>
       </c>
-      <c r="B187" s="13">
+      <c r="B187" s="8">
         <v>42676</v>
       </c>
       <c r="C187" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D187" s="7" t="str">
+      <c r="D187" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E187" s="3">
+      <c r="E187" s="11">
         <v>147000</v>
       </c>
-      <c r="F187" s="3">
+      <c r="F187" s="11">
         <v>165000</v>
       </c>
-      <c r="G187" s="3">
+      <c r="G187" s="11">
         <v>202000</v>
       </c>
     </row>
     <row r="188" spans="1:7">
-      <c r="A188" s="13">
+      <c r="A188" s="8">
         <v>42675</v>
       </c>
-      <c r="B188" s="13">
+      <c r="B188" s="8">
         <v>42704</v>
       </c>
       <c r="C188" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D188" s="7" t="str">
+      <c r="D188" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E188" s="3">
+      <c r="E188" s="11">
         <v>216000</v>
       </c>
-      <c r="F188" s="3">
+      <c r="F188" s="11">
         <v>165000</v>
       </c>
-      <c r="G188" s="3">
+      <c r="G188" s="11">
         <v>119000</v>
       </c>
     </row>
     <row r="189" spans="1:7">
-      <c r="A189" s="13">
+      <c r="A189" s="8">
         <v>42705</v>
       </c>
-      <c r="B189" s="13">
+      <c r="B189" s="8">
         <v>42740</v>
       </c>
       <c r="C189" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D189" s="7" t="str">
+      <c r="D189" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E189" s="3">
+      <c r="E189" s="11">
         <v>153000</v>
       </c>
-      <c r="F189" s="3">
+      <c r="F189" s="11">
         <v>170000</v>
       </c>
-      <c r="G189" s="3">
+      <c r="G189" s="11">
         <v>215000</v>
       </c>
     </row>
     <row r="190" spans="1:7">
-      <c r="A190" s="13">
+      <c r="A190" s="8">
         <v>42736</v>
       </c>
-      <c r="B190" s="13">
+      <c r="B190" s="8">
         <v>42767</v>
       </c>
       <c r="C190" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D190" s="7" t="str">
+      <c r="D190" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E190" s="3">
+      <c r="E190" s="11">
         <v>246000</v>
       </c>
-      <c r="F190" s="3">
+      <c r="F190" s="11">
         <v>165000</v>
       </c>
-      <c r="G190" s="3">
+      <c r="G190" s="11">
         <v>151000</v>
       </c>
     </row>
     <row r="191" spans="1:7">
-      <c r="A191" s="13">
+      <c r="A191" s="8">
         <v>42767</v>
       </c>
-      <c r="B191" s="13">
+      <c r="B191" s="8">
         <v>42802</v>
       </c>
       <c r="C191" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D191" s="7" t="str">
+      <c r="D191" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
-      <c r="E191" s="3">
+      <c r="E191" s="11">
         <v>298000</v>
       </c>
-      <c r="F191" s="3">
+      <c r="F191" s="11">
         <v>190000</v>
       </c>
-      <c r="G191" s="3">
+      <c r="G191" s="11">
         <v>261000</v>
       </c>
     </row>
     <row r="192" spans="1:7">
-      <c r="A192" s="13">
+      <c r="A192" s="8">
         <v>42795</v>
       </c>
-      <c r="B192" s="13">
+      <c r="B192" s="8">
         <v>42830</v>
       </c>
       <c r="C192" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D192" s="7" t="str">
+      <c r="D192" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E192" s="3">
+      <c r="E192" s="11">
         <v>263000</v>
       </c>
-      <c r="F192" s="3">
+      <c r="F192" s="11">
         <v>187000</v>
       </c>
-      <c r="G192" s="3">
+      <c r="G192" s="11">
         <v>245000</v>
       </c>
     </row>
     <row r="193" spans="1:7">
-      <c r="A193" s="13">
+      <c r="A193" s="8">
         <v>42826</v>
       </c>
-      <c r="B193" s="13">
+      <c r="B193" s="8">
         <v>42858</v>
       </c>
       <c r="C193" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D193" s="7" t="str">
+      <c r="D193" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E193" s="3">
+      <c r="E193" s="11">
         <v>177000</v>
       </c>
-      <c r="F193" s="3">
+      <c r="F193" s="11">
         <v>175000</v>
       </c>
-      <c r="G193" s="3">
+      <c r="G193" s="11">
         <v>255000</v>
       </c>
     </row>
     <row r="194" spans="1:7">
-      <c r="A194" s="13">
+      <c r="A194" s="8">
         <v>42856</v>
       </c>
-      <c r="B194" s="13">
+      <c r="B194" s="8">
         <v>42887</v>
       </c>
       <c r="C194" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D194" s="7" t="str">
+      <c r="D194" s="10" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
-      <c r="E194" s="3">
+      <c r="E194" s="11">
         <v>253000</v>
       </c>
-      <c r="F194" s="3">
+      <c r="F194" s="11">
         <v>185000</v>
       </c>
-      <c r="G194" s="3">
+      <c r="G194" s="11">
         <v>174000</v>
       </c>
     </row>
     <row r="195" spans="1:7">
-      <c r="A195" s="13">
+      <c r="A195" s="8">
         <v>42887</v>
       </c>
-      <c r="B195" s="13">
+      <c r="B195" s="8">
         <v>42922</v>
       </c>
       <c r="C195" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D195" s="7" t="str">
+      <c r="D195" s="10" t="str">
         <f t="shared" ref="D195:D258" si="3">IF(
  AND(
   B195 &gt;= IF(
@@ -7652,1539 +7647,1539 @@
 )</f>
         <v>UTC-4</v>
       </c>
-      <c r="E195" s="3">
+      <c r="E195" s="11">
         <v>158000</v>
       </c>
-      <c r="F195" s="3">
+      <c r="F195" s="11">
         <v>185000</v>
       </c>
-      <c r="G195" s="3">
+      <c r="G195" s="11">
         <v>230000</v>
       </c>
     </row>
     <row r="196" spans="1:7">
-      <c r="A196" s="13">
+      <c r="A196" s="8">
         <v>42917</v>
       </c>
-      <c r="B196" s="13">
+      <c r="B196" s="8">
         <v>42949</v>
       </c>
       <c r="C196" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D196" s="7" t="str">
+      <c r="D196" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E196" s="3">
+      <c r="E196" s="11">
         <v>178000</v>
       </c>
-      <c r="F196" s="3">
+      <c r="F196" s="11">
         <v>185000</v>
       </c>
-      <c r="G196" s="3">
+      <c r="G196" s="11">
         <v>191000</v>
       </c>
     </row>
     <row r="197" spans="1:7">
-      <c r="A197" s="13">
+      <c r="A197" s="8">
         <v>42948</v>
       </c>
-      <c r="B197" s="13">
+      <c r="B197" s="8">
         <v>42977</v>
       </c>
       <c r="C197" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D197" s="7" t="str">
+      <c r="D197" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E197" s="3">
+      <c r="E197" s="11">
         <v>237000</v>
       </c>
-      <c r="F197" s="3">
+      <c r="F197" s="11">
         <v>183000</v>
       </c>
-      <c r="G197" s="3">
+      <c r="G197" s="11">
         <v>201000</v>
       </c>
     </row>
     <row r="198" spans="1:7">
-      <c r="A198" s="13">
+      <c r="A198" s="8">
         <v>42979</v>
       </c>
-      <c r="B198" s="13">
+      <c r="B198" s="8">
         <v>43012</v>
       </c>
       <c r="C198" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D198" s="7" t="str">
+      <c r="D198" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E198" s="3">
+      <c r="E198" s="11">
         <v>135000</v>
       </c>
-      <c r="F198" s="3">
+      <c r="F198" s="11">
         <v>125000</v>
       </c>
-      <c r="G198" s="3">
+      <c r="G198" s="11">
         <v>228000</v>
       </c>
     </row>
     <row r="199" spans="1:7">
-      <c r="A199" s="13">
+      <c r="A199" s="8">
         <v>43009</v>
       </c>
-      <c r="B199" s="13">
+      <c r="B199" s="8">
         <v>43040</v>
       </c>
       <c r="C199" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D199" s="7" t="str">
+      <c r="D199" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E199" s="3">
+      <c r="E199" s="11">
         <v>235000</v>
       </c>
-      <c r="F199" s="3">
+      <c r="F199" s="11">
         <v>200000</v>
       </c>
-      <c r="G199" s="3">
+      <c r="G199" s="11">
         <v>110000</v>
       </c>
     </row>
     <row r="200" spans="1:7">
-      <c r="A200" s="13">
+      <c r="A200" s="8">
         <v>43040</v>
       </c>
-      <c r="B200" s="13">
+      <c r="B200" s="8">
         <v>43075</v>
       </c>
       <c r="C200" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D200" s="7" t="str">
+      <c r="D200" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E200" s="3">
+      <c r="E200" s="11">
         <v>190000</v>
       </c>
-      <c r="F200" s="3">
+      <c r="F200" s="11">
         <v>185000</v>
       </c>
-      <c r="G200" s="3">
+      <c r="G200" s="11">
         <v>235000</v>
       </c>
     </row>
     <row r="201" spans="1:7">
-      <c r="A201" s="13">
+      <c r="A201" s="8">
         <v>43070</v>
       </c>
-      <c r="B201" s="13">
+      <c r="B201" s="8">
         <v>43104</v>
       </c>
       <c r="C201" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D201" s="7" t="str">
+      <c r="D201" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E201" s="3">
+      <c r="E201" s="11">
         <v>250000</v>
       </c>
-      <c r="F201" s="3">
+      <c r="F201" s="11">
         <v>191000</v>
       </c>
-      <c r="G201" s="3">
+      <c r="G201" s="11">
         <v>185000</v>
       </c>
     </row>
     <row r="202" spans="1:7">
-      <c r="A202" s="13">
+      <c r="A202" s="8">
         <v>43101</v>
       </c>
-      <c r="B202" s="13">
+      <c r="B202" s="8">
         <v>43131</v>
       </c>
       <c r="C202" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D202" s="7" t="str">
+      <c r="D202" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E202" s="3">
+      <c r="E202" s="11">
         <v>234000</v>
       </c>
-      <c r="F202" s="3">
+      <c r="F202" s="11">
         <v>186000</v>
       </c>
-      <c r="G202" s="3">
+      <c r="G202" s="11">
         <v>242000</v>
       </c>
     </row>
     <row r="203" spans="1:7">
-      <c r="A203" s="13">
+      <c r="A203" s="8">
         <v>43132</v>
       </c>
-      <c r="B203" s="13">
+      <c r="B203" s="8">
         <v>43166</v>
       </c>
       <c r="C203" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D203" s="7" t="str">
+      <c r="D203" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E203" s="3">
+      <c r="E203" s="11">
         <v>235000</v>
       </c>
-      <c r="F203" s="3">
+      <c r="F203" s="11">
         <v>195000</v>
       </c>
-      <c r="G203" s="3">
+      <c r="G203" s="11">
         <v>244000</v>
       </c>
     </row>
     <row r="204" spans="1:7">
-      <c r="A204" s="13">
+      <c r="A204" s="8">
         <v>43160</v>
       </c>
-      <c r="B204" s="13">
+      <c r="B204" s="8">
         <v>43194</v>
       </c>
       <c r="C204" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D204" s="7" t="str">
+      <c r="D204" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E204" s="3">
+      <c r="E204" s="11">
         <v>241000</v>
       </c>
-      <c r="F204" s="3">
+      <c r="F204" s="11">
         <v>208000</v>
       </c>
-      <c r="G204" s="3">
+      <c r="G204" s="11">
         <v>246000</v>
       </c>
     </row>
     <row r="205" spans="1:7">
-      <c r="A205" s="13">
+      <c r="A205" s="8">
         <v>43191</v>
       </c>
-      <c r="B205" s="13">
+      <c r="B205" s="8">
         <v>43222</v>
       </c>
       <c r="C205" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D205" s="7" t="str">
+      <c r="D205" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E205" s="3">
+      <c r="E205" s="11">
         <v>204000</v>
       </c>
-      <c r="F205" s="3">
+      <c r="F205" s="11">
         <v>200000</v>
       </c>
-      <c r="G205" s="3">
+      <c r="G205" s="11">
         <v>228000</v>
       </c>
     </row>
     <row r="206" spans="1:7">
-      <c r="A206" s="13">
+      <c r="A206" s="8">
         <v>43221</v>
       </c>
-      <c r="B206" s="13">
+      <c r="B206" s="8">
         <v>43250</v>
       </c>
       <c r="C206" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D206" s="7" t="str">
+      <c r="D206" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E206" s="3">
+      <c r="E206" s="11">
         <v>178000</v>
       </c>
-      <c r="F206" s="3">
+      <c r="F206" s="11">
         <v>186000</v>
       </c>
-      <c r="G206" s="3">
+      <c r="G206" s="11">
         <v>163000</v>
       </c>
     </row>
     <row r="207" spans="1:7">
-      <c r="A207" s="13">
+      <c r="A207" s="8">
         <v>43252</v>
       </c>
-      <c r="B207" s="13">
+      <c r="B207" s="8">
         <v>43286</v>
       </c>
       <c r="C207" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D207" s="7" t="str">
+      <c r="D207" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E207" s="3">
+      <c r="E207" s="11">
         <v>177000</v>
       </c>
-      <c r="F207" s="3">
+      <c r="F207" s="11">
         <v>190000</v>
       </c>
-      <c r="G207" s="3">
+      <c r="G207" s="11">
         <v>189000</v>
       </c>
     </row>
     <row r="208" spans="1:7">
-      <c r="A208" s="13">
+      <c r="A208" s="8">
         <v>43282</v>
       </c>
-      <c r="B208" s="13">
+      <c r="B208" s="8">
         <v>43313</v>
       </c>
       <c r="C208" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D208" s="7" t="str">
+      <c r="D208" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E208" s="3">
+      <c r="E208" s="11">
         <v>219000</v>
       </c>
-      <c r="F208" s="3">
+      <c r="F208" s="11">
         <v>186000</v>
       </c>
-      <c r="G208" s="3">
+      <c r="G208" s="11">
         <v>181000</v>
       </c>
     </row>
     <row r="209" spans="1:7">
-      <c r="A209" s="13">
+      <c r="A209" s="8">
         <v>43313</v>
       </c>
-      <c r="B209" s="13">
+      <c r="B209" s="8">
         <v>43349</v>
       </c>
       <c r="C209" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D209" s="7" t="str">
+      <c r="D209" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E209" s="3">
+      <c r="E209" s="11">
         <v>163000</v>
       </c>
-      <c r="F209" s="3">
+      <c r="F209" s="11">
         <v>188000</v>
       </c>
-      <c r="G209" s="3">
+      <c r="G209" s="11">
         <v>217000</v>
       </c>
     </row>
     <row r="210" spans="1:7">
-      <c r="A210" s="13">
+      <c r="A210" s="8">
         <v>43344</v>
       </c>
-      <c r="B210" s="13">
+      <c r="B210" s="8">
         <v>43376</v>
       </c>
       <c r="C210" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D210" s="7" t="str">
+      <c r="D210" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E210" s="3">
+      <c r="E210" s="11">
         <v>230000</v>
       </c>
-      <c r="F210" s="3">
+      <c r="F210" s="11">
         <v>187000</v>
       </c>
-      <c r="G210" s="3">
+      <c r="G210" s="11">
         <v>168000</v>
       </c>
     </row>
     <row r="211" spans="1:7">
-      <c r="A211" s="13">
+      <c r="A211" s="8">
         <v>43374</v>
       </c>
-      <c r="B211" s="13">
+      <c r="B211" s="8">
         <v>43404</v>
       </c>
       <c r="C211" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D211" s="7" t="str">
+      <c r="D211" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E211" s="3">
+      <c r="E211" s="11">
         <v>227000</v>
       </c>
-      <c r="F211" s="3">
+      <c r="F211" s="11">
         <v>189000</v>
       </c>
-      <c r="G211" s="3">
+      <c r="G211" s="11">
         <v>218000</v>
       </c>
     </row>
     <row r="212" spans="1:7">
-      <c r="A212" s="13">
+      <c r="A212" s="8">
         <v>43405</v>
       </c>
-      <c r="B212" s="13">
+      <c r="B212" s="8">
         <v>43440</v>
       </c>
       <c r="C212" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D212" s="7" t="str">
+      <c r="D212" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E212" s="3">
+      <c r="E212" s="11">
         <v>179000</v>
       </c>
-      <c r="F212" s="3">
+      <c r="F212" s="11">
         <v>196000</v>
       </c>
-      <c r="G212" s="3">
+      <c r="G212" s="11">
         <v>225000</v>
       </c>
     </row>
     <row r="213" spans="1:7">
-      <c r="A213" s="13">
+      <c r="A213" s="8">
         <v>43435</v>
       </c>
-      <c r="B213" s="13">
+      <c r="B213" s="8">
         <v>43468</v>
       </c>
       <c r="C213" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D213" s="7" t="str">
+      <c r="D213" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E213" s="3">
+      <c r="E213" s="11">
         <v>271000</v>
       </c>
-      <c r="F213" s="3">
+      <c r="F213" s="11">
         <v>179000</v>
       </c>
-      <c r="G213" s="3">
+      <c r="G213" s="11">
         <v>157000</v>
       </c>
     </row>
     <row r="214" spans="1:7">
-      <c r="A214" s="13">
+      <c r="A214" s="8">
         <v>43466</v>
       </c>
-      <c r="B214" s="13">
+      <c r="B214" s="8">
         <v>43495</v>
       </c>
       <c r="C214" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D214" s="7" t="str">
+      <c r="D214" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E214" s="3">
+      <c r="E214" s="11">
         <v>213000</v>
       </c>
-      <c r="F214" s="3">
+      <c r="F214" s="11">
         <v>180000</v>
       </c>
-      <c r="G214" s="3">
+      <c r="G214" s="11">
         <v>263000</v>
       </c>
     </row>
     <row r="215" spans="1:7">
-      <c r="A215" s="13">
+      <c r="A215" s="8">
         <v>43497</v>
       </c>
-      <c r="B215" s="13">
+      <c r="B215" s="8">
         <v>43530</v>
       </c>
       <c r="C215" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D215" s="7" t="str">
+      <c r="D215" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E215" s="3">
+      <c r="E215" s="11">
         <v>183000</v>
       </c>
-      <c r="F215" s="3">
+      <c r="F215" s="11">
         <v>189000</v>
       </c>
-      <c r="G215" s="3">
+      <c r="G215" s="11">
         <v>300000</v>
       </c>
     </row>
     <row r="216" spans="1:7">
-      <c r="A216" s="13">
+      <c r="A216" s="8">
         <v>43525</v>
       </c>
-      <c r="B216" s="13">
+      <c r="B216" s="8">
         <v>43558</v>
       </c>
       <c r="C216" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D216" s="7" t="str">
+      <c r="D216" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E216" s="3">
+      <c r="E216" s="11">
         <v>129000</v>
       </c>
-      <c r="F216" s="3">
+      <c r="F216" s="11">
         <v>184000</v>
       </c>
-      <c r="G216" s="3">
+      <c r="G216" s="11">
         <v>197000</v>
       </c>
     </row>
     <row r="217" spans="1:7">
-      <c r="A217" s="13">
+      <c r="A217" s="8">
         <v>43556</v>
       </c>
-      <c r="B217" s="13">
+      <c r="B217" s="8">
         <v>43586</v>
       </c>
       <c r="C217" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D217" s="7" t="str">
+      <c r="D217" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E217" s="3">
+      <c r="E217" s="11">
         <v>275000</v>
       </c>
-      <c r="F217" s="3">
+      <c r="F217" s="11">
         <v>181000</v>
       </c>
-      <c r="G217" s="3">
+      <c r="G217" s="11">
         <v>151000</v>
       </c>
     </row>
     <row r="218" spans="1:7">
-      <c r="A218" s="13">
+      <c r="A218" s="8">
         <v>43586</v>
       </c>
-      <c r="B218" s="13">
+      <c r="B218" s="8">
         <v>43621</v>
       </c>
       <c r="C218" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D218" s="7" t="str">
+      <c r="D218" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E218" s="3">
+      <c r="E218" s="11">
         <v>27000</v>
       </c>
-      <c r="F218" s="3">
+      <c r="F218" s="11">
         <v>180000</v>
       </c>
-      <c r="G218" s="3">
+      <c r="G218" s="11">
         <v>271000</v>
       </c>
     </row>
     <row r="219" spans="1:7">
-      <c r="A219" s="13">
+      <c r="A219" s="8">
         <v>43617</v>
       </c>
-      <c r="B219" s="13">
+      <c r="B219" s="8">
         <v>43649</v>
       </c>
       <c r="C219" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D219" s="7" t="str">
+      <c r="D219" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E219" s="3">
+      <c r="E219" s="11">
         <v>102000</v>
       </c>
-      <c r="F219" s="3">
+      <c r="F219" s="11">
         <v>140000</v>
       </c>
-      <c r="G219" s="3">
+      <c r="G219" s="11">
         <v>41000</v>
       </c>
     </row>
     <row r="220" spans="1:7">
-      <c r="A220" s="13">
+      <c r="A220" s="8">
         <v>43647</v>
       </c>
-      <c r="B220" s="13">
+      <c r="B220" s="8">
         <v>43677</v>
       </c>
       <c r="C220" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D220" s="7" t="str">
+      <c r="D220" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E220" s="3">
+      <c r="E220" s="11">
         <v>156000</v>
       </c>
-      <c r="F220" s="3">
+      <c r="F220" s="11">
         <v>150000</v>
       </c>
-      <c r="G220" s="3">
+      <c r="G220" s="11">
         <v>112000</v>
       </c>
     </row>
     <row r="221" spans="1:7">
-      <c r="A221" s="13">
+      <c r="A221" s="8">
         <v>43678</v>
       </c>
-      <c r="B221" s="13">
+      <c r="B221" s="8">
         <v>43713</v>
       </c>
       <c r="C221" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D221" s="7" t="str">
+      <c r="D221" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E221" s="3">
+      <c r="E221" s="11">
         <v>195000</v>
       </c>
-      <c r="F221" s="3">
+      <c r="F221" s="11">
         <v>148000</v>
       </c>
-      <c r="G221" s="3">
+      <c r="G221" s="11">
         <v>142000</v>
       </c>
     </row>
     <row r="222" spans="1:7">
-      <c r="A222" s="13">
+      <c r="A222" s="8">
         <v>43709</v>
       </c>
-      <c r="B222" s="13">
+      <c r="B222" s="8">
         <v>43740</v>
       </c>
       <c r="C222" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D222" s="7" t="str">
+      <c r="D222" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E222" s="3">
+      <c r="E222" s="11">
         <v>135000</v>
       </c>
-      <c r="F222" s="3">
+      <c r="F222" s="11">
         <v>140000</v>
       </c>
-      <c r="G222" s="3">
+      <c r="G222" s="11">
         <v>157000</v>
       </c>
     </row>
     <row r="223" spans="1:7">
-      <c r="A223" s="13">
+      <c r="A223" s="8">
         <v>43739</v>
       </c>
-      <c r="B223" s="13">
+      <c r="B223" s="8">
         <v>43768</v>
       </c>
       <c r="C223" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D223" s="7" t="str">
+      <c r="D223" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E223" s="3">
+      <c r="E223" s="11">
         <v>125000</v>
       </c>
-      <c r="F223" s="3">
+      <c r="F223" s="11">
         <v>120000</v>
       </c>
-      <c r="G223" s="3">
+      <c r="G223" s="11">
         <v>93000</v>
       </c>
     </row>
     <row r="224" spans="1:7">
-      <c r="A224" s="13">
+      <c r="A224" s="8">
         <v>43770</v>
       </c>
-      <c r="B224" s="13">
+      <c r="B224" s="8">
         <v>43803</v>
       </c>
       <c r="C224" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D224" s="7" t="str">
+      <c r="D224" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E224" s="3">
+      <c r="E224" s="11">
         <v>67000</v>
       </c>
-      <c r="F224" s="3">
+      <c r="F224" s="11">
         <v>140000</v>
       </c>
-      <c r="G224" s="3">
+      <c r="G224" s="11">
         <v>121000</v>
       </c>
     </row>
     <row r="225" spans="1:7">
-      <c r="A225" s="13">
+      <c r="A225" s="8">
         <v>43800</v>
       </c>
-      <c r="B225" s="13">
+      <c r="B225" s="8">
         <v>43838</v>
       </c>
       <c r="C225" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D225" s="7" t="str">
+      <c r="D225" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E225" s="3">
+      <c r="E225" s="11">
         <v>202000</v>
       </c>
-      <c r="F225" s="3">
+      <c r="F225" s="11">
         <v>160000</v>
       </c>
-      <c r="G225" s="3">
+      <c r="G225" s="11">
         <v>124000</v>
       </c>
     </row>
     <row r="226" spans="1:7">
-      <c r="A226" s="13">
+      <c r="A226" s="8">
         <v>43831</v>
       </c>
-      <c r="B226" s="13">
+      <c r="B226" s="8">
         <v>43866</v>
       </c>
       <c r="C226" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D226" s="7" t="str">
+      <c r="D226" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E226" s="3">
+      <c r="E226" s="11">
         <v>291000</v>
       </c>
-      <c r="F226" s="3">
+      <c r="F226" s="11">
         <v>156000</v>
       </c>
-      <c r="G226" s="3">
+      <c r="G226" s="11">
         <v>199000</v>
       </c>
     </row>
     <row r="227" spans="1:7">
-      <c r="A227" s="13">
+      <c r="A227" s="8">
         <v>43862</v>
       </c>
-      <c r="B227" s="13">
+      <c r="B227" s="8">
         <v>43894</v>
       </c>
       <c r="C227" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D227" s="7" t="str">
+      <c r="D227" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E227" s="3">
+      <c r="E227" s="11">
         <v>183000</v>
       </c>
-      <c r="F227" s="3">
+      <c r="F227" s="11">
         <v>170000</v>
       </c>
-      <c r="G227" s="3">
+      <c r="G227" s="11">
         <v>209000</v>
       </c>
     </row>
     <row r="228" spans="1:7">
-      <c r="A228" s="13">
+      <c r="A228" s="8">
         <v>43891</v>
       </c>
-      <c r="B228" s="13">
+      <c r="B228" s="8">
         <v>43922</v>
       </c>
       <c r="C228" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D228" s="7" t="str">
+      <c r="D228" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E228" s="3">
+      <c r="E228" s="11">
         <v>-27000</v>
       </c>
-      <c r="F228" s="3">
+      <c r="F228" s="11">
         <v>-150000</v>
       </c>
-      <c r="G228" s="3">
+      <c r="G228" s="11">
         <v>183000</v>
       </c>
     </row>
     <row r="229" spans="1:7">
-      <c r="A229" s="13">
+      <c r="A229" s="8">
         <v>43922</v>
       </c>
-      <c r="B229" s="13">
+      <c r="B229" s="8">
         <v>43957</v>
       </c>
       <c r="C229" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D229" s="7" t="str">
+      <c r="D229" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E229" s="3">
+      <c r="E229" s="11">
         <v>-20236000</v>
       </c>
-      <c r="F229" s="3">
+      <c r="F229" s="11">
         <v>-20050000</v>
       </c>
-      <c r="G229" s="3">
+      <c r="G229" s="11">
         <v>-149000</v>
       </c>
     </row>
     <row r="230" spans="1:7">
-      <c r="A230" s="13">
+      <c r="A230" s="8">
         <v>43952</v>
       </c>
-      <c r="B230" s="13">
+      <c r="B230" s="8">
         <v>43985</v>
       </c>
       <c r="C230" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D230" s="7" t="str">
+      <c r="D230" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E230" s="3">
+      <c r="E230" s="11">
         <v>-2760000</v>
       </c>
-      <c r="F230" s="3">
+      <c r="F230" s="11">
         <v>-9000000</v>
       </c>
-      <c r="G230" s="3">
+      <c r="G230" s="11">
         <v>-19557000</v>
       </c>
     </row>
     <row r="231" spans="1:7">
-      <c r="A231" s="13">
+      <c r="A231" s="8">
         <v>43983</v>
       </c>
-      <c r="B231" s="13">
+      <c r="B231" s="8">
         <v>44013</v>
       </c>
       <c r="C231" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D231" s="7" t="str">
+      <c r="D231" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E231" s="3">
+      <c r="E231" s="11">
         <v>2369000</v>
       </c>
-      <c r="F231" s="3">
+      <c r="F231" s="11">
         <v>3000000</v>
       </c>
-      <c r="G231" s="3">
+      <c r="G231" s="11">
         <v>3065000</v>
       </c>
     </row>
     <row r="232" spans="1:7">
-      <c r="A232" s="13">
+      <c r="A232" s="8">
         <v>44013</v>
       </c>
-      <c r="B232" s="13">
+      <c r="B232" s="8">
         <v>44048</v>
       </c>
       <c r="C232" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D232" s="7" t="str">
+      <c r="D232" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E232" s="3">
+      <c r="E232" s="11">
         <v>167000</v>
       </c>
-      <c r="F232" s="3">
+      <c r="F232" s="11">
         <v>1500000</v>
       </c>
-      <c r="G232" s="3">
+      <c r="G232" s="11">
         <v>4314000</v>
       </c>
     </row>
     <row r="233" spans="1:7">
-      <c r="A233" s="13">
+      <c r="A233" s="8">
         <v>44044</v>
       </c>
-      <c r="B233" s="13">
+      <c r="B233" s="8">
         <v>44076</v>
       </c>
       <c r="C233" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D233" s="7" t="str">
+      <c r="D233" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E233" s="3">
+      <c r="E233" s="11">
         <v>428000</v>
       </c>
-      <c r="F233" s="3">
+      <c r="F233" s="11">
         <v>950000</v>
       </c>
-      <c r="G233" s="3">
+      <c r="G233" s="11">
         <v>212000</v>
       </c>
     </row>
     <row r="234" spans="1:7">
-      <c r="A234" s="13">
+      <c r="A234" s="8">
         <v>44075</v>
       </c>
-      <c r="B234" s="13">
+      <c r="B234" s="8">
         <v>44104</v>
       </c>
       <c r="C234" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D234" s="7" t="str">
+      <c r="D234" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E234" s="3">
+      <c r="E234" s="11">
         <v>749000</v>
       </c>
-      <c r="F234" s="3">
+      <c r="F234" s="11">
         <v>650000</v>
       </c>
-      <c r="G234" s="3">
+      <c r="G234" s="11">
         <v>481000</v>
       </c>
     </row>
     <row r="235" spans="1:7">
-      <c r="A235" s="13">
+      <c r="A235" s="8">
         <v>44105</v>
       </c>
-      <c r="B235" s="13">
+      <c r="B235" s="8">
         <v>44139</v>
       </c>
       <c r="C235" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D235" s="7" t="str">
+      <c r="D235" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E235" s="3">
+      <c r="E235" s="11">
         <v>365000</v>
       </c>
-      <c r="F235" s="3">
+      <c r="F235" s="11">
         <v>650000</v>
       </c>
-      <c r="G235" s="3">
+      <c r="G235" s="11">
         <v>749000</v>
       </c>
     </row>
     <row r="236" spans="1:7">
-      <c r="A236" s="13">
+      <c r="A236" s="8">
         <v>44136</v>
       </c>
-      <c r="B236" s="13">
+      <c r="B236" s="8">
         <v>44167</v>
       </c>
       <c r="C236" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D236" s="7" t="str">
+      <c r="D236" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E236" s="3">
+      <c r="E236" s="11">
         <v>307000</v>
       </c>
-      <c r="F236" s="3">
+      <c r="F236" s="11">
         <v>410000</v>
       </c>
-      <c r="G236" s="3">
+      <c r="G236" s="11">
         <v>404000</v>
       </c>
     </row>
     <row r="237" spans="1:7">
-      <c r="A237" s="13">
+      <c r="A237" s="8">
         <v>44166</v>
       </c>
-      <c r="B237" s="13">
+      <c r="B237" s="8">
         <v>44202</v>
       </c>
       <c r="C237" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D237" s="7" t="str">
+      <c r="D237" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E237" s="3">
+      <c r="E237" s="11">
         <v>-123000</v>
       </c>
-      <c r="F237" s="3">
+      <c r="F237" s="11">
         <v>88000</v>
       </c>
-      <c r="G237" s="3">
+      <c r="G237" s="11">
         <v>304000</v>
       </c>
     </row>
     <row r="238" spans="1:7">
-      <c r="A238" s="13">
+      <c r="A238" s="8">
         <v>44197</v>
       </c>
-      <c r="B238" s="13">
+      <c r="B238" s="8">
         <v>44230</v>
       </c>
       <c r="C238" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D238" s="7" t="str">
+      <c r="D238" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E238" s="3">
+      <c r="E238" s="11">
         <v>174000</v>
       </c>
-      <c r="F238" s="3">
+      <c r="F238" s="11">
         <v>49000</v>
       </c>
-      <c r="G238" s="3">
+      <c r="G238" s="11">
         <v>-78000</v>
       </c>
     </row>
     <row r="239" spans="1:7">
-      <c r="A239" s="13">
+      <c r="A239" s="8">
         <v>44228</v>
       </c>
-      <c r="B239" s="13">
+      <c r="B239" s="8">
         <v>44258</v>
       </c>
       <c r="C239" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D239" s="7" t="str">
+      <c r="D239" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E239" s="3">
+      <c r="E239" s="11">
         <v>117000</v>
       </c>
-      <c r="F239" s="3">
+      <c r="F239" s="11">
         <v>177000</v>
       </c>
-      <c r="G239" s="3">
+      <c r="G239" s="11">
         <v>195000</v>
       </c>
     </row>
     <row r="240" spans="1:7">
-      <c r="A240" s="13">
+      <c r="A240" s="8">
         <v>44256</v>
       </c>
-      <c r="B240" s="13">
+      <c r="B240" s="8">
         <v>44286</v>
       </c>
       <c r="C240" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D240" s="7" t="str">
+      <c r="D240" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E240" s="3">
+      <c r="E240" s="11">
         <v>517000</v>
       </c>
-      <c r="F240" s="3">
+      <c r="F240" s="11">
         <v>550000</v>
       </c>
-      <c r="G240" s="3">
+      <c r="G240" s="11">
         <v>176000</v>
       </c>
     </row>
     <row r="241" spans="1:7">
-      <c r="A241" s="13">
+      <c r="A241" s="8">
         <v>44287</v>
       </c>
-      <c r="B241" s="13">
+      <c r="B241" s="8">
         <v>44321</v>
       </c>
       <c r="C241" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D241" s="7" t="str">
+      <c r="D241" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E241" s="3">
+      <c r="E241" s="11">
         <v>742000</v>
       </c>
-      <c r="F241" s="3">
+      <c r="F241" s="11">
         <v>800000</v>
       </c>
-      <c r="G241" s="3">
+      <c r="G241" s="11">
         <v>565000</v>
       </c>
     </row>
     <row r="242" spans="1:7">
-      <c r="A242" s="13">
+      <c r="A242" s="8">
         <v>44317</v>
       </c>
-      <c r="B242" s="13">
+      <c r="B242" s="8">
         <v>44350</v>
       </c>
       <c r="C242" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D242" s="7" t="str">
+      <c r="D242" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E242" s="3">
+      <c r="E242" s="11">
         <v>978000</v>
       </c>
-      <c r="F242" s="3">
+      <c r="F242" s="11">
         <v>650000</v>
       </c>
-      <c r="G242" s="3">
+      <c r="G242" s="11">
         <v>654000</v>
       </c>
     </row>
     <row r="243" spans="1:7">
-      <c r="A243" s="13">
+      <c r="A243" s="8">
         <v>44348</v>
       </c>
-      <c r="B243" s="13">
+      <c r="B243" s="8">
         <v>44377</v>
       </c>
       <c r="C243" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D243" s="7" t="str">
+      <c r="D243" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E243" s="3">
+      <c r="E243" s="11">
         <v>692000</v>
       </c>
-      <c r="F243" s="3">
+      <c r="F243" s="11">
         <v>600000</v>
       </c>
-      <c r="G243" s="3">
+      <c r="G243" s="11">
         <v>886000</v>
       </c>
     </row>
     <row r="244" spans="1:7">
-      <c r="A244" s="13">
+      <c r="A244" s="8">
         <v>44378</v>
       </c>
-      <c r="B244" s="13">
+      <c r="B244" s="8">
         <v>44412</v>
       </c>
       <c r="C244" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D244" s="7" t="str">
+      <c r="D244" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E244" s="3">
+      <c r="E244" s="11">
         <v>330000</v>
       </c>
-      <c r="F244" s="3">
+      <c r="F244" s="11">
         <v>695000</v>
       </c>
-      <c r="G244" s="3">
+      <c r="G244" s="11">
         <v>680000</v>
       </c>
     </row>
     <row r="245" spans="1:7">
-      <c r="A245" s="13">
+      <c r="A245" s="8">
         <v>44409</v>
       </c>
-      <c r="B245" s="13">
+      <c r="B245" s="8">
         <v>44440</v>
       </c>
       <c r="C245" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D245" s="7" t="str">
+      <c r="D245" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E245" s="3">
+      <c r="E245" s="11">
         <v>374000</v>
       </c>
-      <c r="F245" s="3">
+      <c r="F245" s="11">
         <v>613000</v>
       </c>
-      <c r="G245" s="3">
+      <c r="G245" s="11">
         <v>326000</v>
       </c>
     </row>
     <row r="246" spans="1:7">
-      <c r="A246" s="13">
+      <c r="A246" s="8">
         <v>44440</v>
       </c>
-      <c r="B246" s="13">
+      <c r="B246" s="8">
         <v>44475</v>
       </c>
       <c r="C246" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D246" s="7" t="str">
+      <c r="D246" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E246" s="3">
+      <c r="E246" s="11">
         <v>568000</v>
       </c>
-      <c r="F246" s="3">
+      <c r="F246" s="11">
         <v>428000</v>
       </c>
-      <c r="G246" s="3">
+      <c r="G246" s="11">
         <v>340000</v>
       </c>
     </row>
     <row r="247" spans="1:7">
-      <c r="A247" s="13">
+      <c r="A247" s="8">
         <v>44470</v>
       </c>
-      <c r="B247" s="13">
+      <c r="B247" s="8">
         <v>44503</v>
       </c>
       <c r="C247" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D247" s="7" t="str">
+      <c r="D247" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E247" s="3">
+      <c r="E247" s="11">
         <v>571000</v>
       </c>
-      <c r="F247" s="3">
+      <c r="F247" s="11">
         <v>400000</v>
       </c>
-      <c r="G247" s="3">
+      <c r="G247" s="11">
         <v>523000</v>
       </c>
     </row>
     <row r="248" spans="1:7">
-      <c r="A248" s="13">
+      <c r="A248" s="8">
         <v>44501</v>
       </c>
-      <c r="B248" s="13">
+      <c r="B248" s="8">
         <v>44531</v>
       </c>
       <c r="C248" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D248" s="7" t="str">
+      <c r="D248" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E248" s="3">
+      <c r="E248" s="11">
         <v>534000</v>
       </c>
-      <c r="F248" s="3">
+      <c r="F248" s="11">
         <v>525000</v>
       </c>
-      <c r="G248" s="3">
+      <c r="G248" s="11">
         <v>570000</v>
       </c>
     </row>
     <row r="249" spans="1:7">
-      <c r="A249" s="13">
+      <c r="A249" s="8">
         <v>44531</v>
       </c>
-      <c r="B249" s="13">
+      <c r="B249" s="8">
         <v>44566</v>
       </c>
       <c r="C249" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D249" s="7" t="str">
+      <c r="D249" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E249" s="3">
+      <c r="E249" s="11">
         <v>807000</v>
       </c>
-      <c r="F249" s="3">
+      <c r="F249" s="11">
         <v>400000</v>
       </c>
-      <c r="G249" s="3">
+      <c r="G249" s="11">
         <v>505000</v>
       </c>
     </row>
     <row r="250" spans="1:7">
-      <c r="A250" s="13">
+      <c r="A250" s="8">
         <v>44562</v>
       </c>
-      <c r="B250" s="13">
+      <c r="B250" s="8">
         <v>44594</v>
       </c>
       <c r="C250" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D250" s="7" t="str">
+      <c r="D250" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E250" s="3">
+      <c r="E250" s="11">
         <v>-301000</v>
       </c>
-      <c r="F250" s="3">
+      <c r="F250" s="11">
         <v>207000</v>
       </c>
-      <c r="G250" s="3">
+      <c r="G250" s="11">
         <v>776000</v>
       </c>
     </row>
     <row r="251" spans="1:7">
-      <c r="A251" s="13">
+      <c r="A251" s="8">
         <v>44593</v>
       </c>
-      <c r="B251" s="13">
+      <c r="B251" s="8">
         <v>44622</v>
       </c>
       <c r="C251" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D251" s="7" t="str">
+      <c r="D251" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E251" s="3">
+      <c r="E251" s="11">
         <v>475000</v>
       </c>
-      <c r="F251" s="3">
+      <c r="F251" s="11">
         <v>378000</v>
       </c>
-      <c r="G251" s="3">
+      <c r="G251" s="11">
         <v>509000</v>
       </c>
     </row>
     <row r="252" spans="1:7">
-      <c r="A252" s="13">
+      <c r="A252" s="8">
         <v>44621</v>
       </c>
-      <c r="B252" s="13">
+      <c r="B252" s="8">
         <v>44650</v>
       </c>
       <c r="C252" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D252" s="7" t="str">
+      <c r="D252" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E252" s="3">
+      <c r="E252" s="11">
         <v>455000</v>
       </c>
-      <c r="F252" s="3">
+      <c r="F252" s="11">
         <v>450000</v>
       </c>
-      <c r="G252" s="3">
+      <c r="G252" s="11">
         <v>486000</v>
       </c>
     </row>
     <row r="253" spans="1:7">
-      <c r="A253" s="13">
+      <c r="A253" s="8">
         <v>44652</v>
       </c>
-      <c r="B253" s="13">
+      <c r="B253" s="8">
         <v>44685</v>
       </c>
       <c r="C253" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D253" s="7" t="str">
+      <c r="D253" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E253" s="3">
+      <c r="E253" s="11">
         <v>247000</v>
       </c>
-      <c r="F253" s="3">
+      <c r="F253" s="11">
         <v>395000</v>
       </c>
-      <c r="G253" s="3">
+      <c r="G253" s="11">
         <v>479000</v>
       </c>
     </row>
     <row r="254" spans="1:7">
-      <c r="A254" s="13">
+      <c r="A254" s="8">
         <v>44682</v>
       </c>
-      <c r="B254" s="13">
+      <c r="B254" s="8">
         <v>44714</v>
       </c>
       <c r="C254" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D254" s="7" t="str">
+      <c r="D254" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E254" s="3">
+      <c r="E254" s="11">
         <v>128000</v>
       </c>
-      <c r="F254" s="3">
+      <c r="F254" s="11">
         <v>300000</v>
       </c>
-      <c r="G254" s="3">
+      <c r="G254" s="11">
         <v>202000</v>
       </c>
     </row>
     <row r="255" spans="1:7">
-      <c r="A255" s="13">
+      <c r="A255" s="8">
         <v>44774</v>
       </c>
-      <c r="B255" s="13">
+      <c r="B255" s="8">
         <v>44804</v>
       </c>
       <c r="C255" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D255" s="7" t="str">
+      <c r="D255" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E255" s="3">
+      <c r="E255" s="11">
         <v>132000</v>
       </c>
-      <c r="F255" s="3">
+      <c r="F255" s="11">
         <v>300000</v>
       </c>
-      <c r="G255" s="3">
+      <c r="G255" s="11">
         <v>268000</v>
       </c>
     </row>
     <row r="256" spans="1:7">
-      <c r="A256" s="13">
+      <c r="A256" s="8">
         <v>44805</v>
       </c>
-      <c r="B256" s="13">
+      <c r="B256" s="8">
         <v>44839</v>
       </c>
       <c r="C256" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D256" s="7" t="str">
+      <c r="D256" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E256" s="3">
+      <c r="E256" s="11">
         <v>208000</v>
       </c>
-      <c r="F256" s="3">
+      <c r="F256" s="11">
         <v>200000</v>
       </c>
-      <c r="G256" s="3">
+      <c r="G256" s="11">
         <v>185000</v>
       </c>
     </row>
     <row r="257" spans="1:7">
-      <c r="A257" s="13">
+      <c r="A257" s="8">
         <v>44835</v>
       </c>
-      <c r="B257" s="13">
+      <c r="B257" s="8">
         <v>44867</v>
       </c>
       <c r="C257" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D257" s="7" t="str">
+      <c r="D257" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
       </c>
-      <c r="E257" s="3">
+      <c r="E257" s="11">
         <v>239000</v>
       </c>
-      <c r="F257" s="3">
+      <c r="F257" s="11">
         <v>195000</v>
       </c>
-      <c r="G257" s="3">
+      <c r="G257" s="11">
         <v>192000</v>
       </c>
     </row>
     <row r="258" spans="1:7">
-      <c r="A258" s="13">
+      <c r="A258" s="8">
         <v>44866</v>
       </c>
-      <c r="B258" s="13">
+      <c r="B258" s="8">
         <v>44895</v>
       </c>
       <c r="C258" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D258" s="7" t="str">
+      <c r="D258" s="10" t="str">
         <f t="shared" si="3"/>
         <v>UTC-5</v>
       </c>
-      <c r="E258" s="3">
+      <c r="E258" s="11">
         <v>127000</v>
       </c>
-      <c r="F258" s="3">
+      <c r="F258" s="11">
         <v>200000</v>
       </c>
-      <c r="G258" s="3">
+      <c r="G258" s="11">
         <v>239000</v>
       </c>
     </row>
     <row r="259" spans="1:7">
-      <c r="A259" s="13">
+      <c r="A259" s="8">
         <v>44896</v>
       </c>
-      <c r="B259" s="13">
+      <c r="B259" s="8">
         <v>44931</v>
       </c>
       <c r="C259" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D259" s="7" t="str">
+      <c r="D259" s="10" t="str">
         <f t="shared" ref="D259:D299" si="4">IF(
  AND(
   B259 &gt;= IF(
@@ -9203,973 +9198,973 @@
 )</f>
         <v>UTC-5</v>
       </c>
-      <c r="E259" s="3">
+      <c r="E259" s="11">
         <v>235000</v>
       </c>
-      <c r="F259" s="3">
+      <c r="F259" s="11">
         <v>150000</v>
       </c>
-      <c r="G259" s="3">
+      <c r="G259" s="11">
         <v>182000</v>
       </c>
     </row>
     <row r="260" spans="1:7">
-      <c r="A260" s="13">
+      <c r="A260" s="8">
         <v>44927</v>
       </c>
-      <c r="B260" s="13">
+      <c r="B260" s="8">
         <v>44958</v>
       </c>
       <c r="C260" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D260" s="7" t="str">
+      <c r="D260" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E260" s="3">
+      <c r="E260" s="11">
         <v>106000</v>
       </c>
-      <c r="F260" s="3">
+      <c r="F260" s="11">
         <v>178000</v>
       </c>
-      <c r="G260" s="3">
+      <c r="G260" s="11">
         <v>253000</v>
       </c>
     </row>
     <row r="261" spans="1:7">
-      <c r="A261" s="13">
+      <c r="A261" s="8">
         <v>44958</v>
       </c>
-      <c r="B261" s="13">
+      <c r="B261" s="8">
         <v>44993</v>
       </c>
       <c r="C261" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D261" s="7" t="str">
+      <c r="D261" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E261" s="3">
+      <c r="E261" s="11">
         <v>242000</v>
       </c>
-      <c r="F261" s="3">
+      <c r="F261" s="11">
         <v>200000</v>
       </c>
-      <c r="G261" s="3">
+      <c r="G261" s="11">
         <v>119000</v>
       </c>
     </row>
     <row r="262" spans="1:7">
-      <c r="A262" s="13">
+      <c r="A262" s="8">
         <v>44986</v>
       </c>
-      <c r="B262" s="13">
+      <c r="B262" s="8">
         <v>45021</v>
       </c>
       <c r="C262" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D262" s="7" t="str">
+      <c r="D262" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E262" s="3">
+      <c r="E262" s="11">
         <v>-53000</v>
       </c>
-      <c r="F262" s="3">
+      <c r="F262" s="11">
         <v>200000</v>
       </c>
-      <c r="G262" s="3">
+      <c r="G262" s="11">
         <v>261000</v>
       </c>
     </row>
     <row r="263" spans="1:7">
-      <c r="A263" s="13">
+      <c r="A263" s="8">
         <v>45017</v>
       </c>
-      <c r="B263" s="13">
+      <c r="B263" s="8">
         <v>45049</v>
       </c>
       <c r="C263" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D263" s="7" t="str">
+      <c r="D263" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E263" s="3">
+      <c r="E263" s="11">
         <v>296000</v>
       </c>
-      <c r="F263" s="3">
+      <c r="F263" s="11">
         <v>148000</v>
       </c>
-      <c r="G263" s="3">
+      <c r="G263" s="11">
         <v>142000</v>
       </c>
     </row>
     <row r="264" spans="1:7">
-      <c r="A264" s="13">
+      <c r="A264" s="8">
         <v>45047</v>
       </c>
-      <c r="B264" s="13">
+      <c r="B264" s="8">
         <v>45078</v>
       </c>
       <c r="C264" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D264" s="7" t="str">
+      <c r="D264" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E264" s="3">
+      <c r="E264" s="11">
         <v>278000</v>
       </c>
-      <c r="F264" s="3">
+      <c r="F264" s="11">
         <v>170000</v>
       </c>
-      <c r="G264" s="3">
+      <c r="G264" s="11">
         <v>291000</v>
       </c>
     </row>
     <row r="265" spans="1:7">
-      <c r="A265" s="13">
+      <c r="A265" s="8">
         <v>45078</v>
       </c>
-      <c r="B265" s="13">
+      <c r="B265" s="8">
         <v>45113</v>
       </c>
       <c r="C265" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D265" s="7" t="str">
+      <c r="D265" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E265" s="3">
+      <c r="E265" s="11">
         <v>497000</v>
       </c>
-      <c r="F265" s="3">
+      <c r="F265" s="11">
         <v>228000</v>
       </c>
-      <c r="G265" s="3">
+      <c r="G265" s="11">
         <v>267000</v>
       </c>
     </row>
     <row r="266" spans="1:7">
-      <c r="A266" s="13">
+      <c r="A266" s="8">
         <v>45108</v>
       </c>
-      <c r="B266" s="13">
+      <c r="B266" s="8">
         <v>45140</v>
       </c>
       <c r="C266" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D266" s="7" t="str">
+      <c r="D266" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E266" s="3">
+      <c r="E266" s="11">
         <v>324000</v>
       </c>
-      <c r="F266" s="3">
+      <c r="F266" s="11">
         <v>189000</v>
       </c>
-      <c r="G266" s="3">
+      <c r="G266" s="11">
         <v>455000</v>
       </c>
     </row>
     <row r="267" spans="1:7">
-      <c r="A267" s="13">
+      <c r="A267" s="8">
         <v>45139</v>
       </c>
-      <c r="B267" s="13">
+      <c r="B267" s="8">
         <v>45168</v>
       </c>
       <c r="C267" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D267" s="7" t="str">
+      <c r="D267" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E267" s="3">
+      <c r="E267" s="11">
         <v>177000</v>
       </c>
-      <c r="F267" s="3">
+      <c r="F267" s="11">
         <v>195000</v>
       </c>
-      <c r="G267" s="3">
+      <c r="G267" s="11">
         <v>371000</v>
       </c>
     </row>
     <row r="268" spans="1:7">
-      <c r="A268" s="13">
+      <c r="A268" s="8">
         <v>45170</v>
       </c>
-      <c r="B268" s="13">
+      <c r="B268" s="8">
         <v>45203</v>
       </c>
       <c r="C268" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D268" s="7" t="str">
+      <c r="D268" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E268" s="3">
+      <c r="E268" s="11">
         <v>89000</v>
       </c>
-      <c r="F268" s="3">
+      <c r="F268" s="11">
         <v>153000</v>
       </c>
-      <c r="G268" s="3">
+      <c r="G268" s="11">
         <v>180000</v>
       </c>
     </row>
     <row r="269" spans="1:7">
-      <c r="A269" s="13">
+      <c r="A269" s="8">
         <v>45200</v>
       </c>
-      <c r="B269" s="13">
+      <c r="B269" s="8">
         <v>45231</v>
       </c>
       <c r="C269" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D269" s="7" t="str">
+      <c r="D269" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E269" s="3">
+      <c r="E269" s="11">
         <v>113000</v>
       </c>
-      <c r="F269" s="3">
+      <c r="F269" s="11">
         <v>150000</v>
       </c>
-      <c r="G269" s="3">
+      <c r="G269" s="11">
         <v>89000</v>
       </c>
     </row>
     <row r="270" spans="1:7">
-      <c r="A270" s="13">
+      <c r="A270" s="8">
         <v>45231</v>
       </c>
-      <c r="B270" s="13">
+      <c r="B270" s="8">
         <v>45266</v>
       </c>
       <c r="C270" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D270" s="7" t="str">
+      <c r="D270" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E270" s="3">
+      <c r="E270" s="11">
         <v>103000</v>
       </c>
-      <c r="F270" s="3">
+      <c r="F270" s="11">
         <v>130000</v>
       </c>
-      <c r="G270" s="3">
+      <c r="G270" s="11">
         <v>106000</v>
       </c>
     </row>
     <row r="271" spans="1:7">
-      <c r="A271" s="13">
+      <c r="A271" s="8">
         <v>45261</v>
       </c>
-      <c r="B271" s="13">
+      <c r="B271" s="8">
         <v>45295</v>
       </c>
       <c r="C271" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D271" s="7" t="str">
+      <c r="D271" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E271" s="3">
+      <c r="E271" s="11">
         <v>164000</v>
       </c>
-      <c r="F271" s="3">
+      <c r="F271" s="11">
         <v>115000</v>
       </c>
-      <c r="G271" s="3">
+      <c r="G271" s="11">
         <v>101000</v>
       </c>
     </row>
     <row r="272" spans="1:7">
-      <c r="A272" s="13">
+      <c r="A272" s="8">
         <v>45292</v>
       </c>
-      <c r="B272" s="13">
+      <c r="B272" s="8">
         <v>45322</v>
       </c>
       <c r="C272" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D272" s="7" t="str">
+      <c r="D272" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E272" s="3">
+      <c r="E272" s="11">
         <v>107000</v>
       </c>
-      <c r="F272" s="3">
+      <c r="F272" s="11">
         <v>145000</v>
       </c>
-      <c r="G272" s="3">
+      <c r="G272" s="11">
         <v>158000</v>
       </c>
     </row>
     <row r="273" spans="1:7">
-      <c r="A273" s="13">
+      <c r="A273" s="8">
         <v>45323</v>
       </c>
-      <c r="B273" s="13">
+      <c r="B273" s="8">
         <v>45357</v>
       </c>
       <c r="C273" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D273" s="7" t="str">
+      <c r="D273" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E273" s="3">
+      <c r="E273" s="11">
         <v>140000</v>
       </c>
-      <c r="F273" s="3">
+      <c r="F273" s="11">
         <v>149000</v>
       </c>
-      <c r="G273" s="3">
+      <c r="G273" s="11">
         <v>111000</v>
       </c>
     </row>
     <row r="274" spans="1:7">
-      <c r="A274" s="13">
+      <c r="A274" s="8">
         <v>45352</v>
       </c>
-      <c r="B274" s="13">
+      <c r="B274" s="8">
         <v>45385</v>
       </c>
       <c r="C274" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D274" s="7" t="str">
+      <c r="D274" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E274" s="3">
+      <c r="E274" s="11">
         <v>184000</v>
       </c>
-      <c r="F274" s="3">
+      <c r="F274" s="11">
         <v>148000</v>
       </c>
-      <c r="G274" s="3">
+      <c r="G274" s="11">
         <v>155000</v>
       </c>
     </row>
     <row r="275" spans="1:7">
-      <c r="A275" s="13">
+      <c r="A275" s="8">
         <v>45383</v>
       </c>
-      <c r="B275" s="13">
+      <c r="B275" s="8">
         <v>45413</v>
       </c>
       <c r="C275" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D275" s="7" t="str">
+      <c r="D275" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E275" s="3">
+      <c r="E275" s="11">
         <v>192000</v>
       </c>
-      <c r="F275" s="3">
+      <c r="F275" s="11">
         <v>179000</v>
       </c>
-      <c r="G275" s="3">
+      <c r="G275" s="11">
         <v>208000</v>
       </c>
     </row>
     <row r="276" spans="1:7">
-      <c r="A276" s="13">
+      <c r="A276" s="8">
         <v>45413</v>
       </c>
-      <c r="B276" s="13">
+      <c r="B276" s="8">
         <v>45448</v>
       </c>
       <c r="C276" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D276" s="7" t="str">
+      <c r="D276" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E276" s="3">
+      <c r="E276" s="11">
         <v>152000</v>
       </c>
-      <c r="F276" s="3">
+      <c r="F276" s="11">
         <v>173000</v>
       </c>
-      <c r="G276" s="3">
+      <c r="G276" s="11">
         <v>188000</v>
       </c>
     </row>
     <row r="277" spans="1:7">
-      <c r="A277" s="13">
+      <c r="A277" s="8">
         <v>45444</v>
       </c>
-      <c r="B277" s="13">
+      <c r="B277" s="8">
         <v>45476</v>
       </c>
       <c r="C277" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D277" s="7" t="str">
+      <c r="D277" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E277" s="3">
+      <c r="E277" s="11">
         <v>150000</v>
       </c>
-      <c r="F277" s="3">
+      <c r="F277" s="11">
         <v>163000</v>
       </c>
-      <c r="G277" s="3">
+      <c r="G277" s="11">
         <v>157000</v>
       </c>
     </row>
     <row r="278" spans="1:7">
-      <c r="A278" s="13">
+      <c r="A278" s="8">
         <v>45474</v>
       </c>
-      <c r="B278" s="13">
+      <c r="B278" s="8">
         <v>45504</v>
       </c>
       <c r="C278" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D278" s="7" t="str">
+      <c r="D278" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E278" s="3">
+      <c r="E278" s="11">
         <v>122000</v>
       </c>
-      <c r="F278" s="3">
+      <c r="F278" s="11">
         <v>147000</v>
       </c>
-      <c r="G278" s="3">
+      <c r="G278" s="11">
         <v>155000</v>
       </c>
     </row>
     <row r="279" spans="1:7">
-      <c r="A279" s="13">
+      <c r="A279" s="8">
         <v>45505</v>
       </c>
-      <c r="B279" s="13">
+      <c r="B279" s="8">
         <v>45540</v>
       </c>
       <c r="C279" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D279" s="7" t="str">
+      <c r="D279" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E279" s="3">
+      <c r="E279" s="11">
         <v>99000</v>
       </c>
-      <c r="F279" s="3">
+      <c r="F279" s="11">
         <v>144000</v>
       </c>
-      <c r="G279" s="3">
+      <c r="G279" s="11">
         <v>111000</v>
       </c>
     </row>
     <row r="280" spans="1:7">
-      <c r="A280" s="13">
+      <c r="A280" s="8">
         <v>45536</v>
       </c>
-      <c r="B280" s="13">
+      <c r="B280" s="8">
         <v>45567</v>
       </c>
       <c r="C280" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D280" s="7" t="str">
+      <c r="D280" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E280" s="3">
+      <c r="E280" s="11">
         <v>143000</v>
       </c>
-      <c r="F280" s="3">
+      <c r="F280" s="11">
         <v>124000</v>
       </c>
-      <c r="G280" s="3">
+      <c r="G280" s="11">
         <v>103000</v>
       </c>
     </row>
     <row r="281" spans="1:7">
-      <c r="A281" s="13">
+      <c r="A281" s="8">
         <v>45566</v>
       </c>
-      <c r="B281" s="13">
+      <c r="B281" s="8">
         <v>45595</v>
       </c>
       <c r="C281" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D281" s="7" t="str">
+      <c r="D281" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E281" s="3">
+      <c r="E281" s="11">
         <v>233000</v>
       </c>
-      <c r="F281" s="3">
+      <c r="F281" s="11">
         <v>110000</v>
       </c>
-      <c r="G281" s="3">
+      <c r="G281" s="11">
         <v>159000</v>
       </c>
     </row>
     <row r="282" spans="1:7">
-      <c r="A282" s="13">
+      <c r="A282" s="8">
         <v>45597</v>
       </c>
-      <c r="B282" s="13">
+      <c r="B282" s="8">
         <v>45630</v>
       </c>
       <c r="C282" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D282" s="7" t="str">
+      <c r="D282" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E282" s="3">
+      <c r="E282" s="11">
         <v>146000</v>
       </c>
-      <c r="F282" s="3">
+      <c r="F282" s="11">
         <v>166000</v>
       </c>
-      <c r="G282" s="3">
+      <c r="G282" s="11">
         <v>184000</v>
       </c>
     </row>
     <row r="283" spans="1:7">
-      <c r="A283" s="13">
+      <c r="A283" s="8">
         <v>45627</v>
       </c>
-      <c r="B283" s="13">
+      <c r="B283" s="8">
         <v>45665</v>
       </c>
       <c r="C283" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D283" s="7" t="str">
+      <c r="D283" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E283" s="3">
+      <c r="E283" s="11">
         <v>122000</v>
       </c>
-      <c r="F283" s="3">
+      <c r="F283" s="11">
         <v>139000</v>
       </c>
-      <c r="G283" s="3">
+      <c r="G283" s="11">
         <v>146000</v>
       </c>
     </row>
     <row r="284" spans="1:7">
-      <c r="A284" s="13">
+      <c r="A284" s="8">
         <v>45658</v>
       </c>
-      <c r="B284" s="13">
+      <c r="B284" s="8">
         <v>45693</v>
       </c>
       <c r="C284" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D284" s="7" t="str">
+      <c r="D284" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E284" s="3">
+      <c r="E284" s="11">
         <v>183000</v>
       </c>
-      <c r="F284" s="3">
+      <c r="F284" s="11">
         <v>148000</v>
       </c>
-      <c r="G284" s="3">
+      <c r="G284" s="11">
         <v>176000</v>
       </c>
     </row>
     <row r="285" spans="1:7">
-      <c r="A285" s="13">
+      <c r="A285" s="8">
         <v>45689</v>
       </c>
-      <c r="B285" s="13">
+      <c r="B285" s="8">
         <v>45721</v>
       </c>
       <c r="C285" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D285" s="7" t="str">
+      <c r="D285" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E285" s="3">
+      <c r="E285" s="11">
         <v>77000</v>
       </c>
-      <c r="F285" s="3">
+      <c r="F285" s="11">
         <v>141000</v>
       </c>
-      <c r="G285" s="3">
+      <c r="G285" s="11">
         <v>186000</v>
       </c>
     </row>
     <row r="286" spans="1:7">
-      <c r="A286" s="13">
+      <c r="A286" s="8">
         <v>45717</v>
       </c>
-      <c r="B286" s="13">
+      <c r="B286" s="8">
         <v>45749</v>
       </c>
       <c r="C286" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D286" s="7" t="str">
+      <c r="D286" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E286" s="3">
+      <c r="E286" s="11">
         <v>155000</v>
       </c>
-      <c r="F286" s="3">
+      <c r="F286" s="11">
         <v>118000</v>
       </c>
-      <c r="G286" s="3">
+      <c r="G286" s="11">
         <v>84000</v>
       </c>
     </row>
     <row r="287" spans="1:7">
-      <c r="A287" s="13">
+      <c r="A287" s="8">
         <v>45748</v>
       </c>
-      <c r="B287" s="13">
+      <c r="B287" s="8">
         <v>45777</v>
       </c>
       <c r="C287" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D287" s="7" t="str">
+      <c r="D287" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E287" s="3">
+      <c r="E287" s="11">
         <v>62000</v>
       </c>
-      <c r="F287" s="3">
+      <c r="F287" s="11">
         <v>114000</v>
       </c>
-      <c r="G287" s="3">
+      <c r="G287" s="11">
         <v>147000</v>
       </c>
     </row>
     <row r="288" spans="1:7">
-      <c r="A288" s="13">
+      <c r="A288" s="8">
         <v>45778</v>
       </c>
-      <c r="B288" s="13">
+      <c r="B288" s="8">
         <v>45812</v>
       </c>
       <c r="C288" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D288" s="7" t="str">
+      <c r="D288" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E288" s="3">
+      <c r="E288" s="11">
         <v>37000</v>
       </c>
-      <c r="F288" s="3">
+      <c r="F288" s="11">
         <v>111000</v>
       </c>
-      <c r="G288" s="3">
+      <c r="G288" s="11">
         <v>60000</v>
       </c>
     </row>
     <row r="289" spans="1:7">
-      <c r="A289" s="13">
+      <c r="A289" s="8">
         <v>45809</v>
       </c>
-      <c r="B289" s="13">
+      <c r="B289" s="8">
         <v>45840</v>
       </c>
       <c r="C289" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D289" s="7" t="str">
+      <c r="D289" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E289" s="3">
+      <c r="E289" s="11">
         <v>-33000</v>
       </c>
-      <c r="F289" s="3">
+      <c r="F289" s="11">
         <v>99000</v>
       </c>
-      <c r="G289" s="3">
+      <c r="G289" s="11">
         <v>29000</v>
       </c>
     </row>
     <row r="290" spans="1:7">
-      <c r="A290" s="13">
+      <c r="A290" s="8">
         <v>45839</v>
       </c>
-      <c r="B290" s="13">
+      <c r="B290" s="8">
         <v>45868</v>
       </c>
       <c r="C290" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D290" s="7" t="str">
+      <c r="D290" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E290" s="3">
+      <c r="E290" s="11">
         <v>104000</v>
       </c>
-      <c r="F290" s="3">
+      <c r="F290" s="11">
         <v>77000</v>
       </c>
-      <c r="G290" s="3">
+      <c r="G290" s="11">
         <v>-23000</v>
       </c>
     </row>
     <row r="291" spans="1:7">
-      <c r="A291" s="13">
+      <c r="A291" s="8">
         <v>45870</v>
       </c>
-      <c r="B291" s="13">
+      <c r="B291" s="8">
         <v>45904</v>
       </c>
       <c r="C291" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D291" s="7" t="str">
+      <c r="D291" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E291" s="3">
+      <c r="E291" s="11">
         <v>54000</v>
       </c>
-      <c r="F291" s="3">
+      <c r="F291" s="11">
         <v>73000</v>
       </c>
-      <c r="G291" s="3">
+      <c r="G291" s="11">
         <v>106000</v>
       </c>
     </row>
     <row r="292" spans="1:7">
-      <c r="A292" s="13">
+      <c r="A292" s="8">
         <v>45901</v>
       </c>
-      <c r="B292" s="13">
+      <c r="B292" s="8">
         <v>45931</v>
       </c>
       <c r="C292" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D292" s="7" t="str">
+      <c r="D292" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E292" s="3">
+      <c r="E292" s="11">
         <v>-32000</v>
       </c>
-      <c r="F292" s="3">
+      <c r="F292" s="11">
         <v>52000</v>
       </c>
-      <c r="G292" s="3">
+      <c r="G292" s="11">
         <v>-3000</v>
       </c>
     </row>
     <row r="293" spans="1:7">
-      <c r="A293" s="13">
+      <c r="A293" s="8">
         <v>45931</v>
       </c>
-      <c r="B293" s="13">
+      <c r="B293" s="8">
         <v>45966</v>
       </c>
       <c r="C293" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D293" s="7" t="str">
+      <c r="D293" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E293" s="3">
+      <c r="E293" s="11">
         <v>42000</v>
       </c>
-      <c r="F293" s="3">
+      <c r="F293" s="11">
         <v>32000</v>
       </c>
-      <c r="G293" s="3">
+      <c r="G293" s="11">
         <v>-29000</v>
       </c>
     </row>
     <row r="294" spans="1:7">
-      <c r="A294" s="13">
+      <c r="A294" s="8">
         <v>45962</v>
       </c>
-      <c r="B294" s="13">
+      <c r="B294" s="8">
         <v>45994</v>
       </c>
       <c r="C294" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D294" s="7" t="str">
+      <c r="D294" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E294" s="3">
+      <c r="E294" s="11">
         <v>-32000</v>
       </c>
-      <c r="F294" s="3">
+      <c r="F294" s="11">
         <v>5000</v>
       </c>
-      <c r="G294" s="3">
+      <c r="G294" s="11">
         <v>47000</v>
       </c>
     </row>
     <row r="295" spans="1:7">
-      <c r="A295" s="13">
+      <c r="A295" s="8">
         <v>45992</v>
       </c>
-      <c r="B295" s="13">
+      <c r="B295" s="8">
         <v>46029</v>
       </c>
       <c r="C295" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D295" s="7" t="str">
+      <c r="D295" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E295" s="3">
+      <c r="E295" s="11">
         <v>41000</v>
       </c>
-      <c r="F295" s="3">
+      <c r="F295" s="11">
         <v>49000</v>
       </c>
-      <c r="G295" s="3">
+      <c r="G295" s="11">
         <v>-29000</v>
       </c>
     </row>
     <row r="296" spans="1:7">
-      <c r="A296" s="13">
+      <c r="A296" s="8">
         <v>46023</v>
       </c>
-      <c r="B296" s="13">
+      <c r="B296" s="8">
         <v>46057</v>
       </c>
       <c r="C296" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D296" s="7" t="str">
+      <c r="D296" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E296" s="3">
+      <c r="E296" s="11">
         <v>22000</v>
       </c>
-      <c r="F296" s="3">
+      <c r="F296" s="11">
         <v>46000</v>
       </c>
-      <c r="G296" s="3">
+      <c r="G296" s="11">
         <v>37000</v>
       </c>
     </row>
     <row r="297" spans="1:7">
-      <c r="A297" s="13">
+      <c r="A297" s="8">
         <v>46054</v>
       </c>
-      <c r="B297" s="13">
+      <c r="B297" s="8">
         <v>46085</v>
       </c>
       <c r="C297" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D297" s="7" t="str">
+      <c r="D297" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-5</v>
       </c>
-      <c r="E297" s="3">
+      <c r="E297" s="11">
         <v>63000</v>
       </c>
-      <c r="F297" s="3">
+      <c r="F297" s="11">
         <v>50000</v>
       </c>
-      <c r="G297" s="3">
+      <c r="G297" s="11">
         <v>11000</v>
       </c>
     </row>
     <row r="298" spans="1:7">
-      <c r="A298" s="13">
+      <c r="A298" s="8">
         <v>46082</v>
       </c>
-      <c r="B298" s="13">
+      <c r="B298" s="8">
         <v>46113</v>
       </c>
       <c r="C298" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D298" s="7" t="str">
+      <c r="D298" s="10" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E298" s="3">
+      <c r="E298" s="11">
         <v>62000</v>
       </c>
-      <c r="F298" s="3">
+      <c r="F298" s="11">
         <v>41000</v>
       </c>
-      <c r="G298" s="3">
+      <c r="G298" s="11">
         <v>66000</v>
       </c>
     </row>
     <row r="299" spans="1:7">
-      <c r="A299" s="13">
+      <c r="A299" s="8">
         <v>46113</v>
       </c>
-      <c r="B299" s="13">
+      <c r="B299" s="8">
         <v>46148</v>
       </c>
       <c r="C299" s="9">
         <v>0.34375</v>
       </c>
-      <c r="D299" s="6" t="str">
+      <c r="D299" s="13" t="str">
         <f t="shared" si="4"/>
         <v>UTC-4</v>
       </c>
-      <c r="E299" s="3">
+      <c r="E299" s="11">
         <v>109000</v>
       </c>
-      <c r="F299" s="3">
+      <c r="F299" s="11">
         <v>118000</v>
       </c>
-      <c r="G299" s="3">
+      <c r="G299" s="11">
         <v>61000</v>
       </c>
     </row>
@@ -10204,15 +10199,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
